--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -28,10 +28,10 @@
     <t>U. x Caja</t>
   </si>
   <si>
-    <t>Stock VES</t>
-  </si>
-  <si>
-    <t>Alerta</t>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>Estado</t>
   </si>
   <si>
     <t>85005</t>
@@ -43,7 +43,7 @@
     <t>LIGAS N° 18 - 80 MM X 2 MM X 1 LBS - NATURAL - ALLEANZA</t>
   </si>
   <si>
-    <t>🟢</t>
+    <t>✓ OK</t>
   </si>
   <si>
     <t>85007</t>
@@ -100,7 +100,7 @@
     <t>CUCHILLLA DE ARTE AK-5/5B</t>
   </si>
   <si>
-    <t>🔴</t>
+    <t>✗ AGOTADO</t>
   </si>
   <si>
     <t>85166</t>
@@ -175,7 +175,7 @@
     <t>CUCHILLA HEAVY DUTY L-5 AL</t>
   </si>
   <si>
-    <t>🟡</t>
+    <t>⚠ BAJO</t>
   </si>
   <si>
     <t>85823</t>
@@ -1226,7 +1226,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1240,6 +1240,22 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF065F46"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFDC2626"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFD97706"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1282,7 +1298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1290,13 +1306,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1641,13 +1663,12 @@
   <dimension ref="A1:G197"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1899,7 +1920,7 @@
       <c r="F11" s="4">
         <v>0</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2172,10 +2193,10 @@
       <c r="E23">
         <v>60</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="6">
         <v>3</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="7" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2405,7 +2426,7 @@
       <c r="F33" s="4">
         <v>0</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2451,7 +2472,7 @@
       <c r="F35" s="4">
         <v>0</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2934,7 +2955,7 @@
       <c r="F56" s="4">
         <v>0</v>
       </c>
-      <c r="G56" s="3" t="s">
+      <c r="G56" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3003,7 +3024,7 @@
       <c r="F59" s="4">
         <v>0</v>
       </c>
-      <c r="G59" s="3" t="s">
+      <c r="G59" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3026,7 +3047,7 @@
       <c r="F60" s="4">
         <v>0</v>
       </c>
-      <c r="G60" s="3" t="s">
+      <c r="G60" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3187,7 +3208,7 @@
       <c r="F67" s="4">
         <v>0</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="G67" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3279,7 +3300,7 @@
       <c r="F71" s="4">
         <v>0</v>
       </c>
-      <c r="G71" s="3" t="s">
+      <c r="G71" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3394,7 +3415,7 @@
       <c r="F76" s="4">
         <v>0</v>
       </c>
-      <c r="G76" s="3" t="s">
+      <c r="G76" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3460,10 +3481,10 @@
       <c r="E79">
         <v>120</v>
       </c>
-      <c r="F79" s="5">
+      <c r="F79" s="6">
         <v>4</v>
       </c>
-      <c r="G79" s="3" t="s">
+      <c r="G79" s="7" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3555,7 +3576,7 @@
       <c r="F83" s="4">
         <v>0</v>
       </c>
-      <c r="G83" s="3" t="s">
+      <c r="G83" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3601,7 +3622,7 @@
       <c r="F85" s="4">
         <v>0</v>
       </c>
-      <c r="G85" s="3" t="s">
+      <c r="G85" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3624,7 +3645,7 @@
       <c r="F86" s="4">
         <v>0</v>
       </c>
-      <c r="G86" s="3" t="s">
+      <c r="G86" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3647,7 +3668,7 @@
       <c r="F87" s="4">
         <v>0</v>
       </c>
-      <c r="G87" s="3" t="s">
+      <c r="G87" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3670,7 +3691,7 @@
       <c r="F88" s="4">
         <v>0</v>
       </c>
-      <c r="G88" s="3" t="s">
+      <c r="G88" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3831,7 +3852,7 @@
       <c r="F95" s="4">
         <v>0</v>
       </c>
-      <c r="G95" s="3" t="s">
+      <c r="G95" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3854,7 +3875,7 @@
       <c r="F96" s="4">
         <v>0</v>
       </c>
-      <c r="G96" s="3" t="s">
+      <c r="G96" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3874,10 +3895,10 @@
       <c r="E97">
         <v>10</v>
       </c>
-      <c r="F97" s="5">
+      <c r="F97" s="6">
         <v>7</v>
       </c>
-      <c r="G97" s="3" t="s">
+      <c r="G97" s="7" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3900,7 +3921,7 @@
       <c r="F98" s="4">
         <v>0</v>
       </c>
-      <c r="G98" s="3" t="s">
+      <c r="G98" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3923,7 +3944,7 @@
       <c r="F99" s="4">
         <v>0</v>
       </c>
-      <c r="G99" s="3" t="s">
+      <c r="G99" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4035,10 +4056,10 @@
       <c r="E104">
         <v>200</v>
       </c>
-      <c r="F104" s="5">
+      <c r="F104" s="6">
         <v>4</v>
       </c>
-      <c r="G104" s="3" t="s">
+      <c r="G104" s="7" t="s">
         <v>54</v>
       </c>
     </row>
@@ -4104,10 +4125,10 @@
       <c r="E107">
         <v>120</v>
       </c>
-      <c r="F107" s="5">
+      <c r="F107" s="6">
         <v>1</v>
       </c>
-      <c r="G107" s="3" t="s">
+      <c r="G107" s="7" t="s">
         <v>54</v>
       </c>
     </row>
@@ -4153,7 +4174,7 @@
       <c r="F109" s="4">
         <v>0</v>
       </c>
-      <c r="G109" s="3" t="s">
+      <c r="G109" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4199,7 +4220,7 @@
       <c r="F111" s="4">
         <v>0</v>
       </c>
-      <c r="G111" s="3" t="s">
+      <c r="G111" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4222,7 +4243,7 @@
       <c r="F112" s="4">
         <v>0</v>
       </c>
-      <c r="G112" s="3" t="s">
+      <c r="G112" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4245,7 +4266,7 @@
       <c r="F113" s="4">
         <v>0</v>
       </c>
-      <c r="G113" s="3" t="s">
+      <c r="G113" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4314,7 +4335,7 @@
       <c r="F116" s="4">
         <v>0</v>
       </c>
-      <c r="G116" s="3" t="s">
+      <c r="G116" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4334,10 +4355,10 @@
       <c r="E117">
         <v>5</v>
       </c>
-      <c r="F117" s="5">
+      <c r="F117" s="6">
         <v>2</v>
       </c>
-      <c r="G117" s="3" t="s">
+      <c r="G117" s="7" t="s">
         <v>54</v>
       </c>
     </row>
@@ -4380,10 +4401,10 @@
       <c r="E119">
         <v>10</v>
       </c>
-      <c r="F119" s="5">
+      <c r="F119" s="6">
         <v>6</v>
       </c>
-      <c r="G119" s="3" t="s">
+      <c r="G119" s="7" t="s">
         <v>54</v>
       </c>
     </row>
@@ -4429,7 +4450,7 @@
       <c r="F121" s="4">
         <v>0</v>
       </c>
-      <c r="G121" s="3" t="s">
+      <c r="G121" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4452,7 +4473,7 @@
       <c r="F122" s="4">
         <v>0</v>
       </c>
-      <c r="G122" s="3" t="s">
+      <c r="G122" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4521,7 +4542,7 @@
       <c r="F125" s="4">
         <v>0</v>
       </c>
-      <c r="G125" s="3" t="s">
+      <c r="G125" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4610,10 +4631,10 @@
       <c r="E129">
         <v>1</v>
       </c>
-      <c r="F129" s="5">
+      <c r="F129" s="6">
         <v>4</v>
       </c>
-      <c r="G129" s="3" t="s">
+      <c r="G129" s="7" t="s">
         <v>54</v>
       </c>
     </row>
@@ -4633,10 +4654,10 @@
       <c r="E130">
         <v>60</v>
       </c>
-      <c r="F130" s="5">
+      <c r="F130" s="6">
         <v>3</v>
       </c>
-      <c r="G130" s="3" t="s">
+      <c r="G130" s="7" t="s">
         <v>54</v>
       </c>
     </row>
@@ -4958,7 +4979,7 @@
       <c r="F144" s="4">
         <v>0</v>
       </c>
-      <c r="G144" s="3" t="s">
+      <c r="G144" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5027,7 +5048,7 @@
       <c r="F147" s="4">
         <v>0</v>
       </c>
-      <c r="G147" s="3" t="s">
+      <c r="G147" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5139,10 +5160,10 @@
       <c r="E152">
         <v>20</v>
       </c>
-      <c r="F152" s="5">
-        <v>8</v>
-      </c>
-      <c r="G152" s="3" t="s">
+      <c r="F152" s="6">
+        <v>8</v>
+      </c>
+      <c r="G152" s="7" t="s">
         <v>54</v>
       </c>
     </row>
@@ -5234,7 +5255,7 @@
       <c r="F156" s="4">
         <v>0</v>
       </c>
-      <c r="G156" s="3" t="s">
+      <c r="G156" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5415,10 +5436,10 @@
       <c r="E164">
         <v>10</v>
       </c>
-      <c r="F164" s="5">
+      <c r="F164" s="6">
         <v>4</v>
       </c>
-      <c r="G164" s="3" t="s">
+      <c r="G164" s="7" t="s">
         <v>54</v>
       </c>
     </row>
@@ -5786,7 +5807,7 @@
       <c r="F180" s="4">
         <v>0</v>
       </c>
-      <c r="G180" s="3" t="s">
+      <c r="G180" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5806,10 +5827,10 @@
       <c r="E181">
         <v>12</v>
       </c>
-      <c r="F181" s="5">
+      <c r="F181" s="6">
         <v>4</v>
       </c>
-      <c r="G181" s="3" t="s">
+      <c r="G181" s="7" t="s">
         <v>54</v>
       </c>
     </row>
@@ -5829,10 +5850,10 @@
       <c r="E182">
         <v>6</v>
       </c>
-      <c r="F182" s="5">
+      <c r="F182" s="6">
         <v>6</v>
       </c>
-      <c r="G182" s="3" t="s">
+      <c r="G182" s="7" t="s">
         <v>54</v>
       </c>
     </row>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -91,16 +91,16 @@
     <t>CUCHILLA ARTE AK-1/5B</t>
   </si>
   <si>
+    <t>85164</t>
+  </si>
+  <si>
+    <t>091511400670</t>
+  </si>
+  <si>
+    <t>CUCHILLA ARTE AK-4</t>
+  </si>
+  <si>
     <t>⚠ BAJO</t>
-  </si>
-  <si>
-    <t>85164</t>
-  </si>
-  <si>
-    <t>091511400670</t>
-  </si>
-  <si>
-    <t>CUCHILLA ARTE AK-4</t>
   </si>
   <si>
     <t>85770</t>
@@ -2167,11 +2167,11 @@
       <c r="E7">
         <v>120</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="2">
         <v>1031</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>26</v>
+      <c r="G7" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2179,13 +2179,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
         <v>27</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
       </c>
       <c r="E8">
         <v>120</v>
@@ -2194,7 +2194,7 @@
         <v>268</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2217,7 +2217,7 @@
         <v>253</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2240,7 +2240,7 @@
         <v>59</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2286,7 +2286,7 @@
         <v>132</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2309,7 +2309,7 @@
         <v>191</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2332,7 +2332,7 @@
         <v>189</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2355,7 +2355,7 @@
         <v>84</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2374,11 +2374,11 @@
       <c r="E16">
         <v>120</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="2">
         <v>692</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>26</v>
+      <c r="G16" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2401,7 +2401,7 @@
         <v>257</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2420,11 +2420,11 @@
       <c r="E18">
         <v>120</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="2">
         <v>983</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>26</v>
+      <c r="G18" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2447,7 +2447,7 @@
         <v>195</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2470,7 +2470,7 @@
         <v>75</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2493,7 +2493,7 @@
         <v>439</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2539,7 +2539,7 @@
         <v>3</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2562,7 +2562,7 @@
         <v>113</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2585,7 +2585,7 @@
         <v>348</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2608,7 +2608,7 @@
         <v>123</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2631,7 +2631,7 @@
         <v>160</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2677,7 +2677,7 @@
         <v>94</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2700,7 +2700,7 @@
         <v>56</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2788,11 +2788,11 @@
       <c r="E34">
         <v>120</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="2">
         <v>907</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>26</v>
+      <c r="G34" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2838,7 +2838,7 @@
         <v>118</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2861,7 +2861,7 @@
         <v>944</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2884,7 +2884,7 @@
         <v>123</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2907,7 +2907,7 @@
         <v>278</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2930,7 +2930,7 @@
         <v>245</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2953,7 +2953,7 @@
         <v>107</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2976,7 +2976,7 @@
         <v>273</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3022,7 +3022,7 @@
         <v>1090</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3045,7 +3045,7 @@
         <v>163</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3068,7 +3068,7 @@
         <v>1475</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3091,7 +3091,7 @@
         <v>164</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3114,7 +3114,7 @@
         <v>140</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3137,7 +3137,7 @@
         <v>261</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3160,7 +3160,7 @@
         <v>291</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3183,7 +3183,7 @@
         <v>10</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3206,7 +3206,7 @@
         <v>82</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3229,7 +3229,7 @@
         <v>27</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3252,7 +3252,7 @@
         <v>2462</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3275,7 +3275,7 @@
         <v>208</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -3317,11 +3317,11 @@
       <c r="E57">
         <v>720</v>
       </c>
-      <c r="F57" s="4">
+      <c r="F57" s="2">
         <v>4873</v>
       </c>
-      <c r="G57" s="5" t="s">
-        <v>26</v>
+      <c r="G57" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -3344,7 +3344,7 @@
         <v>201</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3413,7 +3413,7 @@
         <v>300</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3436,7 +3436,7 @@
         <v>198</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3478,11 +3478,11 @@
       <c r="E64">
         <v>60</v>
       </c>
-      <c r="F64" s="4">
+      <c r="F64" s="2">
         <v>513</v>
       </c>
-      <c r="G64" s="5" t="s">
-        <v>26</v>
+      <c r="G64" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3505,7 +3505,7 @@
         <v>65</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3528,7 +3528,7 @@
         <v>69</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3574,7 +3574,7 @@
         <v>55</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3620,7 +3620,7 @@
         <v>130</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3666,7 +3666,7 @@
         <v>412</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3689,7 +3689,7 @@
         <v>500</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3708,11 +3708,11 @@
       <c r="E74">
         <v>240</v>
       </c>
-      <c r="F74" s="4">
+      <c r="F74" s="2">
         <v>1529</v>
       </c>
-      <c r="G74" s="5" t="s">
-        <v>26</v>
+      <c r="G74" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -3781,7 +3781,7 @@
         <v>539</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -3804,7 +3804,7 @@
         <v>114</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -3827,7 +3827,7 @@
         <v>4</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3850,7 +3850,7 @@
         <v>12</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3942,7 +3942,7 @@
         <v>80</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4099,11 +4099,11 @@
       <c r="E91">
         <v>10</v>
       </c>
-      <c r="F91" s="4">
+      <c r="F91" s="2">
         <v>68</v>
       </c>
-      <c r="G91" s="5" t="s">
-        <v>26</v>
+      <c r="G91" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4241,7 +4241,7 @@
         <v>7</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4402,7 +4402,7 @@
         <v>4</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -4421,11 +4421,11 @@
       <c r="E105">
         <v>56</v>
       </c>
-      <c r="F105" s="4">
+      <c r="F105" s="2">
         <v>354</v>
       </c>
-      <c r="G105" s="5" t="s">
-        <v>26</v>
+      <c r="G105" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -4448,7 +4448,7 @@
         <v>15</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4471,7 +4471,7 @@
         <v>1</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -4494,7 +4494,7 @@
         <v>79</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -4628,11 +4628,11 @@
       <c r="E114">
         <v>5</v>
       </c>
-      <c r="F114" s="4">
+      <c r="F114" s="2">
         <v>39</v>
       </c>
-      <c r="G114" s="5" t="s">
-        <v>26</v>
+      <c r="G114" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -4655,7 +4655,7 @@
         <v>312</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -4701,7 +4701,7 @@
         <v>2</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -4747,7 +4747,7 @@
         <v>6</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -4770,7 +4770,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -4839,7 +4839,7 @@
         <v>127</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -4858,11 +4858,11 @@
       <c r="E124">
         <v>4</v>
       </c>
-      <c r="F124" s="4">
+      <c r="F124" s="2">
         <v>37</v>
       </c>
-      <c r="G124" s="5" t="s">
-        <v>26</v>
+      <c r="G124" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -4908,7 +4908,7 @@
         <v>17</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -4927,11 +4927,11 @@
       <c r="E127">
         <v>4</v>
       </c>
-      <c r="F127" s="4">
+      <c r="F127" s="2">
         <v>24</v>
       </c>
-      <c r="G127" s="5" t="s">
-        <v>26</v>
+      <c r="G127" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -4954,7 +4954,7 @@
         <v>18</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -4977,7 +4977,7 @@
         <v>4</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -5000,7 +5000,7 @@
         <v>3</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5019,11 +5019,11 @@
       <c r="E131">
         <v>60</v>
       </c>
-      <c r="F131" s="4">
+      <c r="F131" s="2">
         <v>357</v>
       </c>
-      <c r="G131" s="5" t="s">
-        <v>26</v>
+      <c r="G131" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -5046,7 +5046,7 @@
         <v>58</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5069,7 +5069,7 @@
         <v>138</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5088,11 +5088,11 @@
       <c r="E134">
         <v>60</v>
       </c>
-      <c r="F134" s="4">
+      <c r="F134" s="2">
         <v>480</v>
       </c>
-      <c r="G134" s="5" t="s">
-        <v>26</v>
+      <c r="G134" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5111,11 +5111,11 @@
       <c r="E135">
         <v>60</v>
       </c>
-      <c r="F135" s="4">
+      <c r="F135" s="2">
         <v>521</v>
       </c>
-      <c r="G135" s="5" t="s">
-        <v>26</v>
+      <c r="G135" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -5134,11 +5134,11 @@
       <c r="E136">
         <v>60</v>
       </c>
-      <c r="F136" s="4">
+      <c r="F136" s="2">
         <v>480</v>
       </c>
-      <c r="G136" s="5" t="s">
-        <v>26</v>
+      <c r="G136" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -5203,11 +5203,11 @@
       <c r="E139">
         <v>63</v>
       </c>
-      <c r="F139" s="4">
+      <c r="F139" s="2">
         <v>566</v>
       </c>
-      <c r="G139" s="5" t="s">
-        <v>26</v>
+      <c r="G139" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -5253,7 +5253,7 @@
         <v>108</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -5276,7 +5276,7 @@
         <v>122</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -5299,7 +5299,7 @@
         <v>15</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -5345,7 +5345,7 @@
         <v>10</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -5368,7 +5368,7 @@
         <v>34</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -5410,11 +5410,11 @@
       <c r="E148">
         <v>5</v>
       </c>
-      <c r="F148" s="4">
+      <c r="F148" s="2">
         <v>30</v>
       </c>
-      <c r="G148" s="5" t="s">
-        <v>26</v>
+      <c r="G148" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -5506,7 +5506,7 @@
         <v>8</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -5529,7 +5529,7 @@
         <v>640</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -5552,7 +5552,7 @@
         <v>121</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -5621,7 +5621,7 @@
         <v>66</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -5644,7 +5644,7 @@
         <v>30</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5667,7 +5667,7 @@
         <v>83</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -5690,7 +5690,7 @@
         <v>10</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5713,7 +5713,7 @@
         <v>51</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5736,7 +5736,7 @@
         <v>74</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -5759,7 +5759,7 @@
         <v>11</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -5782,7 +5782,7 @@
         <v>4</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -5805,7 +5805,7 @@
         <v>35</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -5828,7 +5828,7 @@
         <v>62</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -5851,7 +5851,7 @@
         <v>28</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -5874,7 +5874,7 @@
         <v>920</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -5897,7 +5897,7 @@
         <v>102</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -5920,7 +5920,7 @@
         <v>211</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -5939,11 +5939,11 @@
       <c r="E171">
         <v>120</v>
       </c>
-      <c r="F171" s="4">
+      <c r="F171" s="2">
         <v>753</v>
       </c>
-      <c r="G171" s="5" t="s">
-        <v>26</v>
+      <c r="G171" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -5966,7 +5966,7 @@
         <v>31</v>
       </c>
       <c r="G172" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -5989,7 +5989,7 @@
         <v>93</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -6012,7 +6012,7 @@
         <v>378</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6035,7 +6035,7 @@
         <v>94</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6058,7 +6058,7 @@
         <v>103</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6081,7 +6081,7 @@
         <v>93</v>
       </c>
       <c r="G177" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6100,11 +6100,11 @@
       <c r="E178">
         <v>12</v>
       </c>
-      <c r="F178" s="4">
+      <c r="F178" s="2">
         <v>68</v>
       </c>
-      <c r="G178" s="5" t="s">
-        <v>26</v>
+      <c r="G178" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -6123,11 +6123,11 @@
       <c r="E179">
         <v>12</v>
       </c>
-      <c r="F179" s="4">
+      <c r="F179" s="2">
         <v>77</v>
       </c>
-      <c r="G179" s="5" t="s">
-        <v>26</v>
+      <c r="G179" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -6173,7 +6173,7 @@
         <v>4</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6196,7 +6196,7 @@
         <v>6</v>
       </c>
       <c r="G182" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6261,11 +6261,11 @@
       <c r="E185">
         <v>20</v>
       </c>
-      <c r="F185" s="4">
+      <c r="F185" s="2">
         <v>144</v>
       </c>
-      <c r="G185" s="5" t="s">
-        <v>26</v>
+      <c r="G185" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -6288,7 +6288,7 @@
         <v>40</v>
       </c>
       <c r="G186" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -6311,7 +6311,7 @@
         <v>20</v>
       </c>
       <c r="G187" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -6334,7 +6334,7 @@
         <v>17</v>
       </c>
       <c r="G188" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -6353,11 +6353,11 @@
       <c r="E189">
         <v>50</v>
       </c>
-      <c r="F189" s="4">
+      <c r="F189" s="2">
         <v>380</v>
       </c>
-      <c r="G189" s="5" t="s">
-        <v>26</v>
+      <c r="G189" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -6491,11 +6491,11 @@
       <c r="E195">
         <v>60</v>
       </c>
-      <c r="F195" s="4">
+      <c r="F195" s="2">
         <v>454</v>
       </c>
-      <c r="G195" s="5" t="s">
-        <v>26</v>
+      <c r="G195" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -6514,11 +6514,11 @@
       <c r="E196">
         <v>100</v>
       </c>
-      <c r="F196" s="4">
+      <c r="F196" s="2">
         <v>880</v>
       </c>
-      <c r="G196" s="5" t="s">
-        <v>26</v>
+      <c r="G196" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="515">
   <si>
     <t>#</t>
   </si>
@@ -43,7 +43,7 @@
     <t>LIGAS N° 18 - 80 MM X 2 MM X 1 LBS - NATURAL - ALLEANZA</t>
   </si>
   <si>
-    <t>✓ OK</t>
+    <t>✗ AGOTADO</t>
   </si>
   <si>
     <t>85007</t>
@@ -100,9 +100,6 @@
     <t>CUCHILLA ARTE AK-4</t>
   </si>
   <si>
-    <t>⚠ BAJO</t>
-  </si>
-  <si>
     <t>85770</t>
   </si>
   <si>
@@ -125,9 +122,6 @@
   </si>
   <si>
     <t>CUCHILLLA DE ARTE AK-5/5B</t>
-  </si>
-  <si>
-    <t>✗ AGOTADO</t>
   </si>
   <si>
     <t>85166</t>
@@ -1568,7 +1562,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1587,21 +1581,11 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF065F46"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFD97706"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b/>
       <color rgb="FFDC2626"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1611,16 +1595,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF13DAEC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -1641,7 +1615,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1650,18 +1624,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2054,7 +2016,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>6770</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2077,7 +2039,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>27406</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2100,7 +2062,7 @@
         <v>80</v>
       </c>
       <c r="F4" s="2">
-        <v>7881</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -2123,7 +2085,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>20889</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2146,7 +2108,7 @@
         <v>200</v>
       </c>
       <c r="F6" s="2">
-        <v>36483</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -2169,7 +2131,7 @@
         <v>120</v>
       </c>
       <c r="F7" s="2">
-        <v>1031</v>
+        <v>0</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -2191,11 +2153,11 @@
       <c r="E8">
         <v>120</v>
       </c>
-      <c r="F8" s="4">
-        <v>268</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>29</v>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2203,22 +2165,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
       </c>
       <c r="E9">
         <v>240</v>
       </c>
-      <c r="F9" s="4">
-        <v>253</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>29</v>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2226,22 +2188,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
         <v>33</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>35</v>
       </c>
       <c r="E10">
         <v>200</v>
       </c>
-      <c r="F10" s="4">
-        <v>59</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>29</v>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2249,22 +2211,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
         <v>36</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>37</v>
       </c>
       <c r="E11">
         <v>240</v>
       </c>
-      <c r="F11" s="6">
-        <v>0</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>38</v>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2272,22 +2234,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
         <v>39</v>
-      </c>
-      <c r="C12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" t="s">
-        <v>41</v>
       </c>
       <c r="E12">
         <v>60</v>
       </c>
-      <c r="F12" s="4">
-        <v>132</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>29</v>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2295,22 +2257,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
         <v>42</v>
-      </c>
-      <c r="C13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" t="s">
-        <v>44</v>
       </c>
       <c r="E13">
         <v>120</v>
       </c>
-      <c r="F13" s="4">
-        <v>191</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>29</v>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2318,22 +2280,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
         <v>45</v>
-      </c>
-      <c r="C14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" t="s">
-        <v>47</v>
       </c>
       <c r="E14">
         <v>120</v>
       </c>
-      <c r="F14" s="4">
-        <v>189</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>29</v>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2341,22 +2303,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
         <v>48</v>
-      </c>
-      <c r="C15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" t="s">
-        <v>50</v>
       </c>
       <c r="E15">
         <v>120</v>
       </c>
-      <c r="F15" s="4">
-        <v>84</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>29</v>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2364,19 +2326,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
         <v>51</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" t="s">
-        <v>53</v>
       </c>
       <c r="E16">
         <v>120</v>
       </c>
       <c r="F16" s="2">
-        <v>692</v>
+        <v>0</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -2387,22 +2349,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
         <v>54</v>
-      </c>
-      <c r="C17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" t="s">
-        <v>56</v>
       </c>
       <c r="E17">
         <v>120</v>
       </c>
-      <c r="F17" s="4">
-        <v>257</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>29</v>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2410,19 +2372,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" t="s">
         <v>57</v>
-      </c>
-      <c r="C18" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" t="s">
-        <v>59</v>
       </c>
       <c r="E18">
         <v>120</v>
       </c>
       <c r="F18" s="2">
-        <v>983</v>
+        <v>0</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -2433,22 +2395,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
         <v>60</v>
-      </c>
-      <c r="C19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" t="s">
-        <v>62</v>
       </c>
       <c r="E19">
         <v>120</v>
       </c>
-      <c r="F19" s="4">
-        <v>195</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>29</v>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2456,22 +2418,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" t="s">
         <v>63</v>
-      </c>
-      <c r="C20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" t="s">
-        <v>65</v>
       </c>
       <c r="E20">
         <v>120</v>
       </c>
-      <c r="F20" s="4">
-        <v>75</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>29</v>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2479,22 +2441,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" t="s">
         <v>66</v>
-      </c>
-      <c r="C21" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" t="s">
-        <v>68</v>
       </c>
       <c r="E21">
         <v>120</v>
       </c>
-      <c r="F21" s="4">
-        <v>439</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>29</v>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2502,19 +2464,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
         <v>69</v>
-      </c>
-      <c r="C22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" t="s">
-        <v>71</v>
       </c>
       <c r="E22">
         <v>120</v>
       </c>
       <c r="F22" s="2">
-        <v>2053</v>
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -2525,22 +2487,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" t="s">
         <v>72</v>
-      </c>
-      <c r="C23" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" t="s">
-        <v>74</v>
       </c>
       <c r="E23">
         <v>60</v>
       </c>
-      <c r="F23" s="4">
-        <v>3</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>29</v>
+      <c r="F23" s="2">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2548,22 +2510,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" t="s">
         <v>75</v>
-      </c>
-      <c r="C24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" t="s">
-        <v>77</v>
       </c>
       <c r="E24">
         <v>120</v>
       </c>
-      <c r="F24" s="4">
-        <v>113</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>29</v>
+      <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2571,22 +2533,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" t="s">
         <v>78</v>
-      </c>
-      <c r="C25" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" t="s">
-        <v>80</v>
       </c>
       <c r="E25">
         <v>120</v>
       </c>
-      <c r="F25" s="4">
-        <v>348</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>29</v>
+      <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2594,22 +2556,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" t="s">
         <v>81</v>
-      </c>
-      <c r="C26" t="s">
-        <v>82</v>
-      </c>
-      <c r="D26" t="s">
-        <v>83</v>
       </c>
       <c r="E26">
         <v>120</v>
       </c>
-      <c r="F26" s="4">
-        <v>123</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>29</v>
+      <c r="F26" s="2">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2617,22 +2579,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" t="s">
         <v>84</v>
-      </c>
-      <c r="C27" t="s">
-        <v>85</v>
-      </c>
-      <c r="D27" t="s">
-        <v>86</v>
       </c>
       <c r="E27">
         <v>120</v>
       </c>
-      <c r="F27" s="4">
-        <v>160</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>29</v>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2640,19 +2602,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28" t="s">
         <v>87</v>
-      </c>
-      <c r="C28" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" t="s">
-        <v>89</v>
       </c>
       <c r="E28">
         <v>120</v>
       </c>
       <c r="F28" s="2">
-        <v>9252</v>
+        <v>0</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -2663,22 +2625,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" t="s">
         <v>90</v>
-      </c>
-      <c r="C29" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" t="s">
-        <v>92</v>
       </c>
       <c r="E29">
         <v>72</v>
       </c>
-      <c r="F29" s="4">
-        <v>94</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>29</v>
+      <c r="F29" s="2">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2686,22 +2648,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" t="s">
         <v>93</v>
-      </c>
-      <c r="C30" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" t="s">
-        <v>95</v>
       </c>
       <c r="E30">
         <v>120</v>
       </c>
-      <c r="F30" s="4">
-        <v>56</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>29</v>
+      <c r="F30" s="2">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2709,19 +2671,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" t="s">
+        <v>95</v>
+      </c>
+      <c r="D31" t="s">
         <v>96</v>
-      </c>
-      <c r="C31" t="s">
-        <v>97</v>
-      </c>
-      <c r="D31" t="s">
-        <v>98</v>
       </c>
       <c r="E31">
         <v>120</v>
       </c>
       <c r="F31" s="2">
-        <v>3120</v>
+        <v>0</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -2732,19 +2694,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" t="s">
         <v>99</v>
-      </c>
-      <c r="C32" t="s">
-        <v>100</v>
-      </c>
-      <c r="D32" t="s">
-        <v>101</v>
       </c>
       <c r="E32">
         <v>120</v>
       </c>
       <c r="F32" s="2">
-        <v>1445</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -2755,22 +2717,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" t="s">
         <v>102</v>
-      </c>
-      <c r="C33" t="s">
-        <v>103</v>
-      </c>
-      <c r="D33" t="s">
-        <v>104</v>
       </c>
       <c r="E33">
         <v>144</v>
       </c>
-      <c r="F33" s="6">
-        <v>0</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>38</v>
+      <c r="F33" s="2">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2778,19 +2740,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34" t="s">
         <v>105</v>
-      </c>
-      <c r="C34" t="s">
-        <v>106</v>
-      </c>
-      <c r="D34" t="s">
-        <v>107</v>
       </c>
       <c r="E34">
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>907</v>
+        <v>0</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -2801,22 +2763,22 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>106</v>
+      </c>
+      <c r="C35" t="s">
+        <v>107</v>
+      </c>
+      <c r="D35" t="s">
         <v>108</v>
-      </c>
-      <c r="C35" t="s">
-        <v>109</v>
-      </c>
-      <c r="D35" t="s">
-        <v>110</v>
       </c>
       <c r="E35">
         <v>128</v>
       </c>
-      <c r="F35" s="6">
-        <v>0</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>38</v>
+      <c r="F35" s="2">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2824,22 +2786,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" t="s">
+        <v>110</v>
+      </c>
+      <c r="D36" t="s">
         <v>111</v>
-      </c>
-      <c r="C36" t="s">
-        <v>112</v>
-      </c>
-      <c r="D36" t="s">
-        <v>113</v>
       </c>
       <c r="E36">
         <v>120</v>
       </c>
-      <c r="F36" s="4">
-        <v>118</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>29</v>
+      <c r="F36" s="2">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2847,22 +2809,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" t="s">
+        <v>113</v>
+      </c>
+      <c r="D37" t="s">
         <v>114</v>
-      </c>
-      <c r="C37" t="s">
-        <v>115</v>
-      </c>
-      <c r="D37" t="s">
-        <v>116</v>
       </c>
       <c r="E37">
         <v>240</v>
       </c>
-      <c r="F37" s="4">
-        <v>944</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>29</v>
+      <c r="F37" s="2">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2870,22 +2832,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>115</v>
+      </c>
+      <c r="C38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D38" t="s">
         <v>117</v>
-      </c>
-      <c r="C38" t="s">
-        <v>118</v>
-      </c>
-      <c r="D38" t="s">
-        <v>119</v>
       </c>
       <c r="E38">
         <v>120</v>
       </c>
-      <c r="F38" s="4">
-        <v>123</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>29</v>
+      <c r="F38" s="2">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2893,22 +2855,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>118</v>
+      </c>
+      <c r="C39" t="s">
+        <v>119</v>
+      </c>
+      <c r="D39" t="s">
         <v>120</v>
-      </c>
-      <c r="C39" t="s">
-        <v>121</v>
-      </c>
-      <c r="D39" t="s">
-        <v>122</v>
       </c>
       <c r="E39">
         <v>240</v>
       </c>
-      <c r="F39" s="4">
-        <v>278</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>29</v>
+      <c r="F39" s="2">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2916,22 +2878,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>121</v>
+      </c>
+      <c r="C40" t="s">
+        <v>122</v>
+      </c>
+      <c r="D40" t="s">
         <v>123</v>
-      </c>
-      <c r="C40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D40" t="s">
-        <v>125</v>
       </c>
       <c r="E40">
         <v>240</v>
       </c>
-      <c r="F40" s="4">
-        <v>245</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>29</v>
+      <c r="F40" s="2">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2939,22 +2901,22 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
+        <v>124</v>
+      </c>
+      <c r="C41" t="s">
+        <v>125</v>
+      </c>
+      <c r="D41" t="s">
         <v>126</v>
-      </c>
-      <c r="C41" t="s">
-        <v>127</v>
-      </c>
-      <c r="D41" t="s">
-        <v>128</v>
       </c>
       <c r="E41">
         <v>240</v>
       </c>
-      <c r="F41" s="4">
-        <v>107</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>29</v>
+      <c r="F41" s="2">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2962,22 +2924,22 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D42" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E42">
         <v>240</v>
       </c>
-      <c r="F42" s="4">
-        <v>273</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>29</v>
+      <c r="F42" s="2">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2985,19 +2947,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>129</v>
+      </c>
+      <c r="C43" t="s">
+        <v>130</v>
+      </c>
+      <c r="D43" t="s">
         <v>131</v>
-      </c>
-      <c r="C43" t="s">
-        <v>132</v>
-      </c>
-      <c r="D43" t="s">
-        <v>133</v>
       </c>
       <c r="E43">
         <v>240</v>
       </c>
       <c r="F43" s="2">
-        <v>2865</v>
+        <v>0</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>10</v>
@@ -3008,22 +2970,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>132</v>
+      </c>
+      <c r="C44" t="s">
+        <v>133</v>
+      </c>
+      <c r="D44" t="s">
         <v>134</v>
-      </c>
-      <c r="C44" t="s">
-        <v>135</v>
-      </c>
-      <c r="D44" t="s">
-        <v>136</v>
       </c>
       <c r="E44">
         <v>480</v>
       </c>
-      <c r="F44" s="4">
-        <v>1090</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>29</v>
+      <c r="F44" s="2">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3031,22 +2993,22 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" t="s">
+        <v>136</v>
+      </c>
+      <c r="D45" t="s">
         <v>137</v>
-      </c>
-      <c r="C45" t="s">
-        <v>138</v>
-      </c>
-      <c r="D45" t="s">
-        <v>139</v>
       </c>
       <c r="E45">
         <v>240</v>
       </c>
-      <c r="F45" s="4">
-        <v>163</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>29</v>
+      <c r="F45" s="2">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3054,22 +3016,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>138</v>
+      </c>
+      <c r="C46" t="s">
+        <v>139</v>
+      </c>
+      <c r="D46" t="s">
         <v>140</v>
-      </c>
-      <c r="C46" t="s">
-        <v>141</v>
-      </c>
-      <c r="D46" t="s">
-        <v>142</v>
       </c>
       <c r="E46">
         <v>800</v>
       </c>
-      <c r="F46" s="4">
-        <v>1475</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>29</v>
+      <c r="F46" s="2">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3077,22 +3039,22 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>141</v>
+      </c>
+      <c r="C47" t="s">
+        <v>142</v>
+      </c>
+      <c r="D47" t="s">
         <v>143</v>
-      </c>
-      <c r="C47" t="s">
-        <v>144</v>
-      </c>
-      <c r="D47" t="s">
-        <v>145</v>
       </c>
       <c r="E47">
         <v>240</v>
       </c>
-      <c r="F47" s="4">
-        <v>164</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>29</v>
+      <c r="F47" s="2">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3100,22 +3062,22 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D48" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E48">
         <v>120</v>
       </c>
-      <c r="F48" s="4">
-        <v>140</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>29</v>
+      <c r="F48" s="2">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3123,22 +3085,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>146</v>
+      </c>
+      <c r="C49" t="s">
+        <v>147</v>
+      </c>
+      <c r="D49" t="s">
         <v>148</v>
-      </c>
-      <c r="C49" t="s">
-        <v>149</v>
-      </c>
-      <c r="D49" t="s">
-        <v>150</v>
       </c>
       <c r="E49">
         <v>120</v>
       </c>
-      <c r="F49" s="4">
-        <v>261</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>29</v>
+      <c r="F49" s="2">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3146,22 +3108,22 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>149</v>
+      </c>
+      <c r="C50" t="s">
+        <v>150</v>
+      </c>
+      <c r="D50" t="s">
         <v>151</v>
-      </c>
-      <c r="C50" t="s">
-        <v>152</v>
-      </c>
-      <c r="D50" t="s">
-        <v>153</v>
       </c>
       <c r="E50">
         <v>120</v>
       </c>
-      <c r="F50" s="4">
-        <v>291</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>29</v>
+      <c r="F50" s="2">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3169,22 +3131,22 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>152</v>
+      </c>
+      <c r="C51" t="s">
+        <v>153</v>
+      </c>
+      <c r="D51" t="s">
         <v>154</v>
       </c>
-      <c r="C51" t="s">
-        <v>155</v>
-      </c>
-      <c r="D51" t="s">
-        <v>156</v>
-      </c>
       <c r="E51">
         <v>10</v>
       </c>
-      <c r="F51" s="4">
-        <v>10</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>29</v>
+      <c r="F51" s="2">
+        <v>0</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3192,22 +3154,22 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>155</v>
+      </c>
+      <c r="C52" t="s">
+        <v>156</v>
+      </c>
+      <c r="D52" t="s">
         <v>157</v>
-      </c>
-      <c r="C52" t="s">
-        <v>158</v>
-      </c>
-      <c r="D52" t="s">
-        <v>159</v>
       </c>
       <c r="E52">
         <v>60</v>
       </c>
-      <c r="F52" s="4">
-        <v>82</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>29</v>
+      <c r="F52" s="2">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3215,22 +3177,22 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>158</v>
+      </c>
+      <c r="C53" t="s">
+        <v>159</v>
+      </c>
+      <c r="D53" t="s">
         <v>160</v>
-      </c>
-      <c r="C53" t="s">
-        <v>161</v>
-      </c>
-      <c r="D53" t="s">
-        <v>162</v>
       </c>
       <c r="E53">
         <v>20</v>
       </c>
-      <c r="F53" s="4">
-        <v>27</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>29</v>
+      <c r="F53" s="2">
+        <v>0</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3238,22 +3200,22 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>161</v>
+      </c>
+      <c r="C54" t="s">
+        <v>162</v>
+      </c>
+      <c r="D54" t="s">
         <v>163</v>
-      </c>
-      <c r="C54" t="s">
-        <v>164</v>
-      </c>
-      <c r="D54" t="s">
-        <v>165</v>
       </c>
       <c r="E54">
         <v>720</v>
       </c>
-      <c r="F54" s="4">
-        <v>2462</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>29</v>
+      <c r="F54" s="2">
+        <v>0</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3261,22 +3223,22 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>164</v>
+      </c>
+      <c r="C55" t="s">
+        <v>165</v>
+      </c>
+      <c r="D55" t="s">
         <v>166</v>
-      </c>
-      <c r="C55" t="s">
-        <v>167</v>
-      </c>
-      <c r="D55" t="s">
-        <v>168</v>
       </c>
       <c r="E55">
         <v>120</v>
       </c>
-      <c r="F55" s="4">
-        <v>208</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>29</v>
+      <c r="F55" s="2">
+        <v>0</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -3284,22 +3246,22 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>167</v>
+      </c>
+      <c r="C56" t="s">
+        <v>168</v>
+      </c>
+      <c r="D56" t="s">
         <v>169</v>
-      </c>
-      <c r="C56" t="s">
-        <v>170</v>
-      </c>
-      <c r="D56" t="s">
-        <v>171</v>
       </c>
       <c r="E56">
         <v>120</v>
       </c>
-      <c r="F56" s="6">
-        <v>0</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>38</v>
+      <c r="F56" s="2">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3307,19 +3269,19 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
+        <v>170</v>
+      </c>
+      <c r="C57" t="s">
+        <v>171</v>
+      </c>
+      <c r="D57" t="s">
         <v>172</v>
-      </c>
-      <c r="C57" t="s">
-        <v>173</v>
-      </c>
-      <c r="D57" t="s">
-        <v>174</v>
       </c>
       <c r="E57">
         <v>720</v>
       </c>
       <c r="F57" s="2">
-        <v>4873</v>
+        <v>0</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3330,22 +3292,22 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>173</v>
+      </c>
+      <c r="C58" t="s">
+        <v>174</v>
+      </c>
+      <c r="D58" t="s">
         <v>175</v>
-      </c>
-      <c r="C58" t="s">
-        <v>176</v>
-      </c>
-      <c r="D58" t="s">
-        <v>177</v>
       </c>
       <c r="E58">
         <v>240</v>
       </c>
-      <c r="F58" s="4">
-        <v>201</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>29</v>
+      <c r="F58" s="2">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3353,22 +3315,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
+        <v>176</v>
+      </c>
+      <c r="C59" t="s">
+        <v>177</v>
+      </c>
+      <c r="D59" t="s">
         <v>178</v>
-      </c>
-      <c r="C59" t="s">
-        <v>179</v>
-      </c>
-      <c r="D59" t="s">
-        <v>180</v>
       </c>
       <c r="E59">
         <v>120</v>
       </c>
-      <c r="F59" s="6">
-        <v>0</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>38</v>
+      <c r="F59" s="2">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3376,22 +3338,22 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C60" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D60" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E60">
         <v>240</v>
       </c>
-      <c r="F60" s="6">
-        <v>0</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>38</v>
+      <c r="F60" s="2">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3399,22 +3361,22 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
+        <v>181</v>
+      </c>
+      <c r="C61" t="s">
+        <v>182</v>
+      </c>
+      <c r="D61" t="s">
         <v>183</v>
-      </c>
-      <c r="C61" t="s">
-        <v>184</v>
-      </c>
-      <c r="D61" t="s">
-        <v>185</v>
       </c>
       <c r="E61">
         <v>240</v>
       </c>
-      <c r="F61" s="4">
-        <v>300</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>29</v>
+      <c r="F61" s="2">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3422,22 +3384,22 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C62" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D62" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E62">
         <v>240</v>
       </c>
-      <c r="F62" s="4">
-        <v>198</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>29</v>
+      <c r="F62" s="2">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3445,19 +3407,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>186</v>
+      </c>
+      <c r="C63" t="s">
+        <v>187</v>
+      </c>
+      <c r="D63" t="s">
         <v>188</v>
-      </c>
-      <c r="C63" t="s">
-        <v>189</v>
-      </c>
-      <c r="D63" t="s">
-        <v>190</v>
       </c>
       <c r="E63">
         <v>240</v>
       </c>
       <c r="F63" s="2">
-        <v>7884</v>
+        <v>0</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3468,19 +3430,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C64" t="s">
+        <v>190</v>
+      </c>
+      <c r="D64" t="s">
         <v>191</v>
-      </c>
-      <c r="C64" t="s">
-        <v>192</v>
-      </c>
-      <c r="D64" t="s">
-        <v>193</v>
       </c>
       <c r="E64">
         <v>60</v>
       </c>
       <c r="F64" s="2">
-        <v>513</v>
+        <v>0</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>10</v>
@@ -3491,22 +3453,22 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>192</v>
+      </c>
+      <c r="C65" t="s">
+        <v>193</v>
+      </c>
+      <c r="D65" t="s">
         <v>194</v>
-      </c>
-      <c r="C65" t="s">
-        <v>195</v>
-      </c>
-      <c r="D65" t="s">
-        <v>196</v>
       </c>
       <c r="E65">
         <v>60</v>
       </c>
-      <c r="F65" s="4">
-        <v>65</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>29</v>
+      <c r="F65" s="2">
+        <v>0</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3514,22 +3476,22 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>195</v>
+      </c>
+      <c r="C66" t="s">
+        <v>196</v>
+      </c>
+      <c r="D66" t="s">
         <v>197</v>
-      </c>
-      <c r="C66" t="s">
-        <v>198</v>
-      </c>
-      <c r="D66" t="s">
-        <v>199</v>
       </c>
       <c r="E66">
         <v>120</v>
       </c>
-      <c r="F66" s="4">
-        <v>69</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>29</v>
+      <c r="F66" s="2">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3537,22 +3499,22 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
+        <v>198</v>
+      </c>
+      <c r="C67" t="s">
+        <v>199</v>
+      </c>
+      <c r="D67" t="s">
         <v>200</v>
-      </c>
-      <c r="C67" t="s">
-        <v>201</v>
-      </c>
-      <c r="D67" t="s">
-        <v>202</v>
       </c>
       <c r="E67">
         <v>240</v>
       </c>
-      <c r="F67" s="6">
-        <v>0</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>38</v>
+      <c r="F67" s="2">
+        <v>0</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3560,22 +3522,22 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>201</v>
+      </c>
+      <c r="C68" t="s">
+        <v>202</v>
+      </c>
+      <c r="D68" t="s">
         <v>203</v>
-      </c>
-      <c r="C68" t="s">
-        <v>204</v>
-      </c>
-      <c r="D68" t="s">
-        <v>205</v>
       </c>
       <c r="E68">
         <v>240</v>
       </c>
-      <c r="F68" s="4">
-        <v>55</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>29</v>
+      <c r="F68" s="2">
+        <v>0</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3583,19 +3545,19 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>204</v>
+      </c>
+      <c r="C69" t="s">
+        <v>205</v>
+      </c>
+      <c r="D69" t="s">
         <v>206</v>
-      </c>
-      <c r="C69" t="s">
-        <v>207</v>
-      </c>
-      <c r="D69" t="s">
-        <v>208</v>
       </c>
       <c r="E69">
         <v>240</v>
       </c>
       <c r="F69" s="2">
-        <v>4170</v>
+        <v>0</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -3606,22 +3568,22 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>207</v>
+      </c>
+      <c r="C70" t="s">
+        <v>208</v>
+      </c>
+      <c r="D70" t="s">
         <v>209</v>
-      </c>
-      <c r="C70" t="s">
-        <v>210</v>
-      </c>
-      <c r="D70" t="s">
-        <v>211</v>
       </c>
       <c r="E70">
         <v>240</v>
       </c>
-      <c r="F70" s="4">
-        <v>130</v>
-      </c>
-      <c r="G70" s="5" t="s">
-        <v>29</v>
+      <c r="F70" s="2">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3629,22 +3591,22 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>210</v>
+      </c>
+      <c r="C71" t="s">
+        <v>211</v>
+      </c>
+      <c r="D71" t="s">
         <v>212</v>
-      </c>
-      <c r="C71" t="s">
-        <v>213</v>
-      </c>
-      <c r="D71" t="s">
-        <v>214</v>
       </c>
       <c r="E71">
         <v>240</v>
       </c>
-      <c r="F71" s="6">
-        <v>0</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>38</v>
+      <c r="F71" s="2">
+        <v>0</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3652,22 +3614,22 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>213</v>
+      </c>
+      <c r="C72" t="s">
+        <v>214</v>
+      </c>
+      <c r="D72" t="s">
         <v>215</v>
-      </c>
-      <c r="C72" t="s">
-        <v>216</v>
-      </c>
-      <c r="D72" t="s">
-        <v>217</v>
       </c>
       <c r="E72">
         <v>480</v>
       </c>
-      <c r="F72" s="4">
-        <v>412</v>
-      </c>
-      <c r="G72" s="5" t="s">
-        <v>29</v>
+      <c r="F72" s="2">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3675,22 +3637,22 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>216</v>
+      </c>
+      <c r="C73" t="s">
+        <v>217</v>
+      </c>
+      <c r="D73" t="s">
         <v>218</v>
-      </c>
-      <c r="C73" t="s">
-        <v>219</v>
-      </c>
-      <c r="D73" t="s">
-        <v>220</v>
       </c>
       <c r="E73">
         <v>240</v>
       </c>
-      <c r="F73" s="4">
-        <v>500</v>
-      </c>
-      <c r="G73" s="5" t="s">
-        <v>29</v>
+      <c r="F73" s="2">
+        <v>0</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3698,19 +3660,19 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>219</v>
+      </c>
+      <c r="C74" t="s">
+        <v>220</v>
+      </c>
+      <c r="D74" t="s">
         <v>221</v>
-      </c>
-      <c r="C74" t="s">
-        <v>222</v>
-      </c>
-      <c r="D74" t="s">
-        <v>223</v>
       </c>
       <c r="E74">
         <v>240</v>
       </c>
       <c r="F74" s="2">
-        <v>1529</v>
+        <v>0</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3721,19 +3683,19 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>222</v>
+      </c>
+      <c r="C75" t="s">
+        <v>223</v>
+      </c>
+      <c r="D75" t="s">
         <v>224</v>
-      </c>
-      <c r="C75" t="s">
-        <v>225</v>
-      </c>
-      <c r="D75" t="s">
-        <v>226</v>
       </c>
       <c r="E75">
         <v>240</v>
       </c>
       <c r="F75" s="2">
-        <v>4001</v>
+        <v>0</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -3744,22 +3706,22 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
+        <v>225</v>
+      </c>
+      <c r="C76" t="s">
+        <v>226</v>
+      </c>
+      <c r="D76" t="s">
         <v>227</v>
-      </c>
-      <c r="C76" t="s">
-        <v>228</v>
-      </c>
-      <c r="D76" t="s">
-        <v>229</v>
       </c>
       <c r="E76">
         <v>240</v>
       </c>
-      <c r="F76" s="6">
-        <v>0</v>
-      </c>
-      <c r="G76" s="7" t="s">
-        <v>38</v>
+      <c r="F76" s="2">
+        <v>0</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -3767,22 +3729,22 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C77" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D77" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E77">
         <v>600</v>
       </c>
-      <c r="F77" s="4">
-        <v>539</v>
-      </c>
-      <c r="G77" s="5" t="s">
-        <v>29</v>
+      <c r="F77" s="2">
+        <v>0</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -3790,22 +3752,22 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
+        <v>230</v>
+      </c>
+      <c r="C78" t="s">
+        <v>231</v>
+      </c>
+      <c r="D78" t="s">
         <v>232</v>
-      </c>
-      <c r="C78" t="s">
-        <v>233</v>
-      </c>
-      <c r="D78" t="s">
-        <v>234</v>
       </c>
       <c r="E78">
         <v>120</v>
       </c>
-      <c r="F78" s="4">
-        <v>114</v>
-      </c>
-      <c r="G78" s="5" t="s">
-        <v>29</v>
+      <c r="F78" s="2">
+        <v>0</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -3813,22 +3775,22 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
+        <v>233</v>
+      </c>
+      <c r="C79" t="s">
+        <v>234</v>
+      </c>
+      <c r="D79" t="s">
         <v>235</v>
-      </c>
-      <c r="C79" t="s">
-        <v>236</v>
-      </c>
-      <c r="D79" t="s">
-        <v>237</v>
       </c>
       <c r="E79">
         <v>120</v>
       </c>
-      <c r="F79" s="4">
-        <v>4</v>
-      </c>
-      <c r="G79" s="5" t="s">
-        <v>29</v>
+      <c r="F79" s="2">
+        <v>0</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3836,22 +3798,22 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>236</v>
+      </c>
+      <c r="C80" t="s">
+        <v>237</v>
+      </c>
+      <c r="D80" t="s">
         <v>238</v>
-      </c>
-      <c r="C80" t="s">
-        <v>239</v>
-      </c>
-      <c r="D80" t="s">
-        <v>240</v>
       </c>
       <c r="E80">
         <v>60</v>
       </c>
-      <c r="F80" s="4">
-        <v>12</v>
-      </c>
-      <c r="G80" s="5" t="s">
-        <v>29</v>
+      <c r="F80" s="2">
+        <v>0</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3859,19 +3821,19 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
+        <v>239</v>
+      </c>
+      <c r="C81" t="s">
+        <v>240</v>
+      </c>
+      <c r="D81" t="s">
         <v>241</v>
-      </c>
-      <c r="C81" t="s">
-        <v>242</v>
-      </c>
-      <c r="D81" t="s">
-        <v>243</v>
       </c>
       <c r="E81">
         <v>20</v>
       </c>
       <c r="F81" s="2">
-        <v>469</v>
+        <v>0</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>10</v>
@@ -3882,19 +3844,19 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
+        <v>242</v>
+      </c>
+      <c r="C82" t="s">
+        <v>243</v>
+      </c>
+      <c r="D82" t="s">
         <v>244</v>
-      </c>
-      <c r="C82" t="s">
-        <v>245</v>
-      </c>
-      <c r="D82" t="s">
-        <v>246</v>
       </c>
       <c r="E82">
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>2766</v>
+        <v>0</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -3905,22 +3867,22 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
+        <v>245</v>
+      </c>
+      <c r="C83" t="s">
+        <v>246</v>
+      </c>
+      <c r="D83" t="s">
         <v>247</v>
-      </c>
-      <c r="C83" t="s">
-        <v>248</v>
-      </c>
-      <c r="D83" t="s">
-        <v>249</v>
       </c>
       <c r="E83">
         <v>40</v>
       </c>
-      <c r="F83" s="6">
-        <v>0</v>
-      </c>
-      <c r="G83" s="7" t="s">
-        <v>38</v>
+      <c r="F83" s="2">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -3928,22 +3890,22 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
+        <v>248</v>
+      </c>
+      <c r="C84" t="s">
+        <v>249</v>
+      </c>
+      <c r="D84" t="s">
         <v>250</v>
-      </c>
-      <c r="C84" t="s">
-        <v>251</v>
-      </c>
-      <c r="D84" t="s">
-        <v>252</v>
       </c>
       <c r="E84">
         <v>40</v>
       </c>
-      <c r="F84" s="4">
-        <v>80</v>
-      </c>
-      <c r="G84" s="5" t="s">
-        <v>29</v>
+      <c r="F84" s="2">
+        <v>0</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -3951,22 +3913,22 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
+        <v>251</v>
+      </c>
+      <c r="C85" t="s">
+        <v>252</v>
+      </c>
+      <c r="D85" t="s">
         <v>253</v>
-      </c>
-      <c r="C85" t="s">
-        <v>254</v>
-      </c>
-      <c r="D85" t="s">
-        <v>255</v>
       </c>
       <c r="E85">
         <v>40</v>
       </c>
-      <c r="F85" s="6">
-        <v>0</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>38</v>
+      <c r="F85" s="2">
+        <v>0</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -3974,22 +3936,22 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
+        <v>254</v>
+      </c>
+      <c r="C86" t="s">
+        <v>255</v>
+      </c>
+      <c r="D86" t="s">
         <v>256</v>
-      </c>
-      <c r="C86" t="s">
-        <v>257</v>
-      </c>
-      <c r="D86" t="s">
-        <v>258</v>
       </c>
       <c r="E86">
         <v>40</v>
       </c>
-      <c r="F86" s="6">
-        <v>0</v>
-      </c>
-      <c r="G86" s="7" t="s">
-        <v>38</v>
+      <c r="F86" s="2">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -3997,22 +3959,22 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
+        <v>257</v>
+      </c>
+      <c r="C87" t="s">
+        <v>258</v>
+      </c>
+      <c r="D87" t="s">
         <v>259</v>
-      </c>
-      <c r="C87" t="s">
-        <v>260</v>
-      </c>
-      <c r="D87" t="s">
-        <v>261</v>
       </c>
       <c r="E87">
         <v>40</v>
       </c>
-      <c r="F87" s="6">
-        <v>0</v>
-      </c>
-      <c r="G87" s="7" t="s">
-        <v>38</v>
+      <c r="F87" s="2">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4020,22 +3982,22 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
+        <v>260</v>
+      </c>
+      <c r="C88" t="s">
+        <v>261</v>
+      </c>
+      <c r="D88" t="s">
         <v>262</v>
-      </c>
-      <c r="C88" t="s">
-        <v>263</v>
-      </c>
-      <c r="D88" t="s">
-        <v>264</v>
       </c>
       <c r="E88">
         <v>20</v>
       </c>
-      <c r="F88" s="6">
-        <v>0</v>
-      </c>
-      <c r="G88" s="7" t="s">
-        <v>38</v>
+      <c r="F88" s="2">
+        <v>0</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4043,19 +4005,19 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
+        <v>263</v>
+      </c>
+      <c r="C89" t="s">
+        <v>264</v>
+      </c>
+      <c r="D89" t="s">
         <v>265</v>
-      </c>
-      <c r="C89" t="s">
-        <v>266</v>
-      </c>
-      <c r="D89" t="s">
-        <v>267</v>
       </c>
       <c r="E89">
         <v>20</v>
       </c>
       <c r="F89" s="2">
-        <v>1473</v>
+        <v>0</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>10</v>
@@ -4066,19 +4028,19 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
+        <v>266</v>
+      </c>
+      <c r="C90" t="s">
+        <v>267</v>
+      </c>
+      <c r="D90" t="s">
         <v>268</v>
-      </c>
-      <c r="C90" t="s">
-        <v>269</v>
-      </c>
-      <c r="D90" t="s">
-        <v>270</v>
       </c>
       <c r="E90">
         <v>100</v>
       </c>
       <c r="F90" s="2">
-        <v>108017</v>
+        <v>0</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -4089,19 +4051,19 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
+        <v>269</v>
+      </c>
+      <c r="C91" t="s">
+        <v>270</v>
+      </c>
+      <c r="D91" t="s">
         <v>271</v>
       </c>
-      <c r="C91" t="s">
-        <v>272</v>
-      </c>
-      <c r="D91" t="s">
-        <v>273</v>
-      </c>
       <c r="E91">
         <v>10</v>
       </c>
       <c r="F91" s="2">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -4112,19 +4074,19 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
+        <v>272</v>
+      </c>
+      <c r="C92" t="s">
+        <v>273</v>
+      </c>
+      <c r="D92" t="s">
         <v>274</v>
       </c>
-      <c r="C92" t="s">
-        <v>275</v>
-      </c>
-      <c r="D92" t="s">
-        <v>276</v>
-      </c>
       <c r="E92">
         <v>10</v>
       </c>
       <c r="F92" s="2">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -4135,19 +4097,19 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
+        <v>275</v>
+      </c>
+      <c r="C93" t="s">
+        <v>276</v>
+      </c>
+      <c r="D93" t="s">
         <v>277</v>
-      </c>
-      <c r="C93" t="s">
-        <v>278</v>
-      </c>
-      <c r="D93" t="s">
-        <v>279</v>
       </c>
       <c r="E93">
         <v>2</v>
       </c>
       <c r="F93" s="2">
-        <v>283</v>
+        <v>0</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -4158,19 +4120,19 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C94" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D94" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E94">
         <v>6</v>
       </c>
       <c r="F94" s="2">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4181,22 +4143,22 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
+        <v>280</v>
+      </c>
+      <c r="C95" t="s">
+        <v>281</v>
+      </c>
+      <c r="D95" t="s">
         <v>282</v>
-      </c>
-      <c r="C95" t="s">
-        <v>283</v>
-      </c>
-      <c r="D95" t="s">
-        <v>284</v>
       </c>
       <c r="E95">
         <v>120</v>
       </c>
-      <c r="F95" s="6">
-        <v>0</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>38</v>
+      <c r="F95" s="2">
+        <v>0</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4204,22 +4166,22 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C96" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D96" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E96">
         <v>120</v>
       </c>
-      <c r="F96" s="6">
-        <v>0</v>
-      </c>
-      <c r="G96" s="7" t="s">
-        <v>38</v>
+      <c r="F96" s="2">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -4227,22 +4189,22 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
+        <v>285</v>
+      </c>
+      <c r="C97" t="s">
+        <v>286</v>
+      </c>
+      <c r="D97" t="s">
         <v>287</v>
       </c>
-      <c r="C97" t="s">
-        <v>288</v>
-      </c>
-      <c r="D97" t="s">
-        <v>289</v>
-      </c>
       <c r="E97">
         <v>10</v>
       </c>
-      <c r="F97" s="4">
-        <v>7</v>
-      </c>
-      <c r="G97" s="5" t="s">
-        <v>29</v>
+      <c r="F97" s="2">
+        <v>0</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4250,22 +4212,22 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
+        <v>288</v>
+      </c>
+      <c r="C98" t="s">
+        <v>289</v>
+      </c>
+      <c r="D98" t="s">
         <v>290</v>
-      </c>
-      <c r="C98" t="s">
-        <v>291</v>
-      </c>
-      <c r="D98" t="s">
-        <v>292</v>
       </c>
       <c r="E98">
         <v>5</v>
       </c>
-      <c r="F98" s="6">
-        <v>0</v>
-      </c>
-      <c r="G98" s="7" t="s">
-        <v>38</v>
+      <c r="F98" s="2">
+        <v>0</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4273,22 +4235,22 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
+        <v>291</v>
+      </c>
+      <c r="C99" t="s">
+        <v>292</v>
+      </c>
+      <c r="D99" t="s">
         <v>293</v>
-      </c>
-      <c r="C99" t="s">
-        <v>294</v>
-      </c>
-      <c r="D99" t="s">
-        <v>295</v>
       </c>
       <c r="E99">
         <v>5</v>
       </c>
-      <c r="F99" s="6">
-        <v>0</v>
-      </c>
-      <c r="G99" s="7" t="s">
-        <v>38</v>
+      <c r="F99" s="2">
+        <v>0</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -4296,19 +4258,19 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
+        <v>294</v>
+      </c>
+      <c r="C100" t="s">
+        <v>295</v>
+      </c>
+      <c r="D100" t="s">
         <v>296</v>
-      </c>
-      <c r="C100" t="s">
-        <v>297</v>
-      </c>
-      <c r="D100" t="s">
-        <v>298</v>
       </c>
       <c r="E100">
         <v>6</v>
       </c>
       <c r="F100" s="2">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -4319,19 +4281,19 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
+        <v>297</v>
+      </c>
+      <c r="C101" t="s">
+        <v>298</v>
+      </c>
+      <c r="D101" t="s">
         <v>299</v>
-      </c>
-      <c r="C101" t="s">
-        <v>300</v>
-      </c>
-      <c r="D101" t="s">
-        <v>301</v>
       </c>
       <c r="E101">
         <v>6</v>
       </c>
       <c r="F101" s="2">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -4342,19 +4304,19 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
+        <v>300</v>
+      </c>
+      <c r="C102" t="s">
+        <v>301</v>
+      </c>
+      <c r="D102" t="s">
         <v>302</v>
-      </c>
-      <c r="C102" t="s">
-        <v>303</v>
-      </c>
-      <c r="D102" t="s">
-        <v>304</v>
       </c>
       <c r="E102">
         <v>6</v>
       </c>
       <c r="F102" s="2">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>10</v>
@@ -4365,19 +4327,19 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
+        <v>303</v>
+      </c>
+      <c r="C103" t="s">
+        <v>304</v>
+      </c>
+      <c r="D103" t="s">
         <v>305</v>
-      </c>
-      <c r="C103" t="s">
-        <v>306</v>
-      </c>
-      <c r="D103" t="s">
-        <v>307</v>
       </c>
       <c r="E103">
         <v>6</v>
       </c>
       <c r="F103" s="2">
-        <v>391</v>
+        <v>0</v>
       </c>
       <c r="G103" s="3" t="s">
         <v>10</v>
@@ -4388,22 +4350,22 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
+        <v>306</v>
+      </c>
+      <c r="C104" t="s">
+        <v>307</v>
+      </c>
+      <c r="D104" t="s">
         <v>308</v>
-      </c>
-      <c r="C104" t="s">
-        <v>309</v>
-      </c>
-      <c r="D104" t="s">
-        <v>310</v>
       </c>
       <c r="E104">
         <v>200</v>
       </c>
-      <c r="F104" s="4">
-        <v>4</v>
-      </c>
-      <c r="G104" s="5" t="s">
-        <v>29</v>
+      <c r="F104" s="2">
+        <v>0</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -4411,19 +4373,19 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
+        <v>309</v>
+      </c>
+      <c r="C105" t="s">
+        <v>310</v>
+      </c>
+      <c r="D105" t="s">
         <v>311</v>
-      </c>
-      <c r="C105" t="s">
-        <v>312</v>
-      </c>
-      <c r="D105" t="s">
-        <v>313</v>
       </c>
       <c r="E105">
         <v>56</v>
       </c>
       <c r="F105" s="2">
-        <v>354</v>
+        <v>0</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>10</v>
@@ -4434,22 +4396,22 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
+        <v>312</v>
+      </c>
+      <c r="C106" t="s">
+        <v>313</v>
+      </c>
+      <c r="D106" t="s">
         <v>314</v>
-      </c>
-      <c r="C106" t="s">
-        <v>315</v>
-      </c>
-      <c r="D106" t="s">
-        <v>316</v>
       </c>
       <c r="E106">
         <v>120</v>
       </c>
-      <c r="F106" s="4">
-        <v>15</v>
-      </c>
-      <c r="G106" s="5" t="s">
-        <v>29</v>
+      <c r="F106" s="2">
+        <v>0</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4457,22 +4419,22 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
+        <v>315</v>
+      </c>
+      <c r="C107" t="s">
+        <v>316</v>
+      </c>
+      <c r="D107" t="s">
         <v>317</v>
-      </c>
-      <c r="C107" t="s">
-        <v>318</v>
-      </c>
-      <c r="D107" t="s">
-        <v>319</v>
       </c>
       <c r="E107">
         <v>120</v>
       </c>
-      <c r="F107" s="4">
-        <v>1</v>
-      </c>
-      <c r="G107" s="5" t="s">
-        <v>29</v>
+      <c r="F107" s="2">
+        <v>0</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -4480,22 +4442,22 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
+        <v>318</v>
+      </c>
+      <c r="C108" t="s">
+        <v>319</v>
+      </c>
+      <c r="D108" t="s">
         <v>320</v>
-      </c>
-      <c r="C108" t="s">
-        <v>321</v>
-      </c>
-      <c r="D108" t="s">
-        <v>322</v>
       </c>
       <c r="E108">
         <v>18</v>
       </c>
-      <c r="F108" s="4">
-        <v>79</v>
-      </c>
-      <c r="G108" s="5" t="s">
-        <v>29</v>
+      <c r="F108" s="2">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -4503,22 +4465,22 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C109" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D109" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E109">
         <v>6</v>
       </c>
-      <c r="F109" s="6">
-        <v>0</v>
-      </c>
-      <c r="G109" s="7" t="s">
-        <v>38</v>
+      <c r="F109" s="2">
+        <v>0</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -4526,19 +4488,19 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
+        <v>323</v>
+      </c>
+      <c r="C110" t="s">
+        <v>324</v>
+      </c>
+      <c r="D110" t="s">
         <v>325</v>
-      </c>
-      <c r="C110" t="s">
-        <v>326</v>
-      </c>
-      <c r="D110" t="s">
-        <v>327</v>
       </c>
       <c r="E110">
         <v>54</v>
       </c>
       <c r="F110" s="2">
-        <v>1093</v>
+        <v>0</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>10</v>
@@ -4549,22 +4511,22 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C111" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D111" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E111">
         <v>10</v>
       </c>
-      <c r="F111" s="6">
-        <v>0</v>
-      </c>
-      <c r="G111" s="7" t="s">
-        <v>38</v>
+      <c r="F111" s="2">
+        <v>0</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -4572,22 +4534,22 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C112" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D112" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E112">
         <v>12</v>
       </c>
-      <c r="F112" s="6">
-        <v>0</v>
-      </c>
-      <c r="G112" s="7" t="s">
-        <v>38</v>
+      <c r="F112" s="2">
+        <v>0</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -4595,22 +4557,22 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C113" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D113" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E113">
         <v>12</v>
       </c>
-      <c r="F113" s="6">
-        <v>0</v>
-      </c>
-      <c r="G113" s="7" t="s">
-        <v>38</v>
+      <c r="F113" s="2">
+        <v>0</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -4618,19 +4580,19 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C114" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D114" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E114">
         <v>5</v>
       </c>
       <c r="F114" s="2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -4641,22 +4603,22 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C115" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D115" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E115">
         <v>800</v>
       </c>
-      <c r="F115" s="4">
-        <v>312</v>
-      </c>
-      <c r="G115" s="5" t="s">
-        <v>29</v>
+      <c r="F115" s="2">
+        <v>0</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -4664,22 +4626,22 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C116" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D116" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E116">
         <v>5</v>
       </c>
-      <c r="F116" s="6">
-        <v>0</v>
-      </c>
-      <c r="G116" s="7" t="s">
-        <v>38</v>
+      <c r="F116" s="2">
+        <v>0</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -4687,22 +4649,22 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C117" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D117" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E117">
         <v>5</v>
       </c>
-      <c r="F117" s="4">
-        <v>2</v>
-      </c>
-      <c r="G117" s="5" t="s">
-        <v>29</v>
+      <c r="F117" s="2">
+        <v>0</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -4710,19 +4672,19 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C118" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D118" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E118">
         <v>10</v>
       </c>
       <c r="F118" s="2">
-        <v>314</v>
+        <v>0</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>10</v>
@@ -4733,22 +4695,22 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C119" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D119" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E119">
         <v>10</v>
       </c>
-      <c r="F119" s="4">
-        <v>6</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>29</v>
+      <c r="F119" s="2">
+        <v>0</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -4756,22 +4718,22 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C120" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D120" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E120">
         <v>10</v>
       </c>
-      <c r="F120" s="4">
-        <v>36</v>
-      </c>
-      <c r="G120" s="5" t="s">
-        <v>29</v>
+      <c r="F120" s="2">
+        <v>0</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -4779,22 +4741,22 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C121" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D121" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E121">
         <v>6</v>
       </c>
-      <c r="F121" s="6">
-        <v>0</v>
-      </c>
-      <c r="G121" s="7" t="s">
-        <v>38</v>
+      <c r="F121" s="2">
+        <v>0</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -4802,22 +4764,22 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C122" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D122" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E122">
         <v>6</v>
       </c>
-      <c r="F122" s="6">
-        <v>0</v>
-      </c>
-      <c r="G122" s="7" t="s">
-        <v>38</v>
+      <c r="F122" s="2">
+        <v>0</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -4825,22 +4787,22 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C123" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D123" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E123">
         <v>40</v>
       </c>
-      <c r="F123" s="4">
-        <v>127</v>
-      </c>
-      <c r="G123" s="5" t="s">
-        <v>29</v>
+      <c r="F123" s="2">
+        <v>0</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -4848,19 +4810,19 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C124" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D124" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E124">
         <v>4</v>
       </c>
       <c r="F124" s="2">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>10</v>
@@ -4871,22 +4833,22 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
+        <v>354</v>
+      </c>
+      <c r="C125" t="s">
+        <v>355</v>
+      </c>
+      <c r="D125" t="s">
         <v>356</v>
-      </c>
-      <c r="C125" t="s">
-        <v>357</v>
-      </c>
-      <c r="D125" t="s">
-        <v>358</v>
       </c>
       <c r="E125">
         <v>1</v>
       </c>
-      <c r="F125" s="6">
-        <v>0</v>
-      </c>
-      <c r="G125" s="7" t="s">
-        <v>38</v>
+      <c r="F125" s="2">
+        <v>0</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -4894,22 +4856,22 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C126" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D126" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E126">
         <v>4</v>
       </c>
-      <c r="F126" s="4">
-        <v>17</v>
-      </c>
-      <c r="G126" s="5" t="s">
-        <v>29</v>
+      <c r="F126" s="2">
+        <v>0</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -4917,19 +4879,19 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C127" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D127" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E127">
         <v>4</v>
       </c>
       <c r="F127" s="2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>10</v>
@@ -4940,22 +4902,22 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C128" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D128" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E128">
         <v>4</v>
       </c>
-      <c r="F128" s="4">
-        <v>18</v>
-      </c>
-      <c r="G128" s="5" t="s">
-        <v>29</v>
+      <c r="F128" s="2">
+        <v>0</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -4963,22 +4925,22 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C129" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D129" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E129">
         <v>1</v>
       </c>
-      <c r="F129" s="4">
-        <v>4</v>
-      </c>
-      <c r="G129" s="5" t="s">
-        <v>29</v>
+      <c r="F129" s="2">
+        <v>0</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -4986,22 +4948,22 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C130" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D130" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E130">
         <v>60</v>
       </c>
-      <c r="F130" s="4">
-        <v>3</v>
-      </c>
-      <c r="G130" s="5" t="s">
-        <v>29</v>
+      <c r="F130" s="2">
+        <v>0</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5009,19 +4971,19 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C131" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D131" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E131">
         <v>60</v>
       </c>
       <c r="F131" s="2">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>10</v>
@@ -5032,22 +4994,22 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C132" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D132" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E132">
         <v>60</v>
       </c>
-      <c r="F132" s="4">
-        <v>58</v>
-      </c>
-      <c r="G132" s="5" t="s">
-        <v>29</v>
+      <c r="F132" s="2">
+        <v>0</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5055,22 +5017,22 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C133" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D133" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E133">
         <v>60</v>
       </c>
-      <c r="F133" s="4">
-        <v>138</v>
-      </c>
-      <c r="G133" s="5" t="s">
-        <v>29</v>
+      <c r="F133" s="2">
+        <v>0</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5078,19 +5040,19 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C134" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D134" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E134">
         <v>60</v>
       </c>
       <c r="F134" s="2">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>10</v>
@@ -5101,19 +5063,19 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C135" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D135" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E135">
         <v>60</v>
       </c>
       <c r="F135" s="2">
-        <v>521</v>
+        <v>0</v>
       </c>
       <c r="G135" s="3" t="s">
         <v>10</v>
@@ -5124,19 +5086,19 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C136" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D136" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E136">
         <v>60</v>
       </c>
       <c r="F136" s="2">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>10</v>
@@ -5147,19 +5109,19 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C137" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D137" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E137">
         <v>30</v>
       </c>
       <c r="F137" s="2">
-        <v>1601</v>
+        <v>0</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>10</v>
@@ -5170,19 +5132,19 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C138" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D138" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E138">
         <v>40</v>
       </c>
       <c r="F138" s="2">
-        <v>1130</v>
+        <v>0</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>10</v>
@@ -5193,19 +5155,19 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C139" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D139" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E139">
         <v>63</v>
       </c>
       <c r="F139" s="2">
-        <v>566</v>
+        <v>0</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>10</v>
@@ -5216,19 +5178,19 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C140" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D140" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E140">
         <v>10</v>
       </c>
       <c r="F140" s="2">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>10</v>
@@ -5239,22 +5201,22 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C141" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D141" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E141">
         <v>40</v>
       </c>
-      <c r="F141" s="4">
-        <v>108</v>
-      </c>
-      <c r="G141" s="5" t="s">
-        <v>29</v>
+      <c r="F141" s="2">
+        <v>0</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -5262,22 +5224,22 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C142" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D142" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E142">
         <v>60</v>
       </c>
-      <c r="F142" s="4">
-        <v>122</v>
-      </c>
-      <c r="G142" s="5" t="s">
-        <v>29</v>
+      <c r="F142" s="2">
+        <v>0</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -5285,22 +5247,22 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C143" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D143" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E143">
         <v>6</v>
       </c>
-      <c r="F143" s="4">
-        <v>15</v>
-      </c>
-      <c r="G143" s="5" t="s">
-        <v>29</v>
+      <c r="F143" s="2">
+        <v>0</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -5308,22 +5270,22 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C144" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D144" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E144">
         <v>18</v>
       </c>
-      <c r="F144" s="6">
-        <v>0</v>
-      </c>
-      <c r="G144" s="7" t="s">
-        <v>38</v>
+      <c r="F144" s="2">
+        <v>0</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -5331,22 +5293,22 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C145" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D145" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E145">
         <v>8</v>
       </c>
-      <c r="F145" s="4">
-        <v>10</v>
-      </c>
-      <c r="G145" s="5" t="s">
-        <v>29</v>
+      <c r="F145" s="2">
+        <v>0</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -5354,22 +5316,22 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C146" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D146" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E146">
         <v>30</v>
       </c>
-      <c r="F146" s="4">
-        <v>34</v>
-      </c>
-      <c r="G146" s="5" t="s">
-        <v>29</v>
+      <c r="F146" s="2">
+        <v>0</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -5377,22 +5339,22 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C147" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D147" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E147">
         <v>2</v>
       </c>
-      <c r="F147" s="6">
-        <v>0</v>
-      </c>
-      <c r="G147" s="7" t="s">
-        <v>38</v>
+      <c r="F147" s="2">
+        <v>0</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -5400,19 +5362,19 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C148" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D148" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E148">
         <v>5</v>
       </c>
       <c r="F148" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G148" s="3" t="s">
         <v>10</v>
@@ -5423,19 +5385,19 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C149" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D149" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E149">
         <v>5</v>
       </c>
       <c r="F149" s="2">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="G149" s="3" t="s">
         <v>10</v>
@@ -5446,19 +5408,19 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C150" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D150" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E150">
         <v>5</v>
       </c>
       <c r="F150" s="2">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>10</v>
@@ -5469,19 +5431,19 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C151" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D151" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E151">
         <v>5</v>
       </c>
       <c r="F151" s="2">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>10</v>
@@ -5492,22 +5454,22 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C152" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D152" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E152">
         <v>20</v>
       </c>
-      <c r="F152" s="4">
-        <v>8</v>
-      </c>
-      <c r="G152" s="5" t="s">
-        <v>29</v>
+      <c r="F152" s="2">
+        <v>0</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -5515,22 +5477,22 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C153" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D153" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E153">
         <v>240</v>
       </c>
-      <c r="F153" s="4">
-        <v>640</v>
-      </c>
-      <c r="G153" s="5" t="s">
-        <v>29</v>
+      <c r="F153" s="2">
+        <v>0</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -5538,22 +5500,22 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
+        <v>413</v>
+      </c>
+      <c r="C154" t="s">
+        <v>414</v>
+      </c>
+      <c r="D154" t="s">
         <v>415</v>
-      </c>
-      <c r="C154" t="s">
-        <v>416</v>
-      </c>
-      <c r="D154" t="s">
-        <v>417</v>
       </c>
       <c r="E154">
         <v>120</v>
       </c>
-      <c r="F154" s="4">
-        <v>121</v>
-      </c>
-      <c r="G154" s="5" t="s">
-        <v>29</v>
+      <c r="F154" s="2">
+        <v>0</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -5561,19 +5523,19 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C155" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D155" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E155">
         <v>60</v>
       </c>
       <c r="F155" s="2">
-        <v>855</v>
+        <v>0</v>
       </c>
       <c r="G155" s="3" t="s">
         <v>10</v>
@@ -5584,22 +5546,22 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C156" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D156" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E156">
         <v>120</v>
       </c>
-      <c r="F156" s="6">
-        <v>0</v>
-      </c>
-      <c r="G156" s="7" t="s">
-        <v>38</v>
+      <c r="F156" s="2">
+        <v>0</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -5607,22 +5569,22 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
+        <v>420</v>
+      </c>
+      <c r="C157" t="s">
+        <v>421</v>
+      </c>
+      <c r="D157" t="s">
         <v>422</v>
-      </c>
-      <c r="C157" t="s">
-        <v>423</v>
-      </c>
-      <c r="D157" t="s">
-        <v>424</v>
       </c>
       <c r="E157">
         <v>72</v>
       </c>
-      <c r="F157" s="4">
-        <v>66</v>
-      </c>
-      <c r="G157" s="5" t="s">
-        <v>29</v>
+      <c r="F157" s="2">
+        <v>0</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -5630,22 +5592,22 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C158" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D158" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E158">
         <v>60</v>
       </c>
-      <c r="F158" s="4">
-        <v>30</v>
-      </c>
-      <c r="G158" s="5" t="s">
-        <v>29</v>
+      <c r="F158" s="2">
+        <v>0</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5653,22 +5615,22 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
+        <v>425</v>
+      </c>
+      <c r="C159" t="s">
+        <v>426</v>
+      </c>
+      <c r="D159" t="s">
         <v>427</v>
-      </c>
-      <c r="C159" t="s">
-        <v>428</v>
-      </c>
-      <c r="D159" t="s">
-        <v>429</v>
       </c>
       <c r="E159">
         <v>120</v>
       </c>
-      <c r="F159" s="4">
-        <v>83</v>
-      </c>
-      <c r="G159" s="5" t="s">
-        <v>29</v>
+      <c r="F159" s="2">
+        <v>0</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -5676,22 +5638,22 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
+        <v>428</v>
+      </c>
+      <c r="C160" t="s">
+        <v>429</v>
+      </c>
+      <c r="D160" t="s">
         <v>430</v>
-      </c>
-      <c r="C160" t="s">
-        <v>431</v>
-      </c>
-      <c r="D160" t="s">
-        <v>432</v>
       </c>
       <c r="E160">
         <v>72</v>
       </c>
-      <c r="F160" s="4">
-        <v>10</v>
-      </c>
-      <c r="G160" s="5" t="s">
-        <v>29</v>
+      <c r="F160" s="2">
+        <v>0</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5699,22 +5661,22 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C161" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D161" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E161">
         <v>20</v>
       </c>
-      <c r="F161" s="4">
-        <v>51</v>
-      </c>
-      <c r="G161" s="5" t="s">
-        <v>29</v>
+      <c r="F161" s="2">
+        <v>0</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5722,22 +5684,22 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C162" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D162" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E162">
         <v>100</v>
       </c>
-      <c r="F162" s="4">
-        <v>74</v>
-      </c>
-      <c r="G162" s="5" t="s">
-        <v>29</v>
+      <c r="F162" s="2">
+        <v>0</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -5745,22 +5707,22 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C163" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D163" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E163">
         <v>5</v>
       </c>
-      <c r="F163" s="4">
-        <v>11</v>
-      </c>
-      <c r="G163" s="5" t="s">
-        <v>29</v>
+      <c r="F163" s="2">
+        <v>0</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -5768,22 +5730,22 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C164" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D164" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E164">
         <v>10</v>
       </c>
-      <c r="F164" s="4">
-        <v>4</v>
-      </c>
-      <c r="G164" s="5" t="s">
-        <v>29</v>
+      <c r="F164" s="2">
+        <v>0</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -5791,22 +5753,22 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C165" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D165" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E165">
         <v>20</v>
       </c>
-      <c r="F165" s="4">
-        <v>35</v>
-      </c>
-      <c r="G165" s="5" t="s">
-        <v>29</v>
+      <c r="F165" s="2">
+        <v>0</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -5814,22 +5776,22 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
+        <v>441</v>
+      </c>
+      <c r="C166" t="s">
+        <v>442</v>
+      </c>
+      <c r="D166" t="s">
         <v>443</v>
-      </c>
-      <c r="C166" t="s">
-        <v>444</v>
-      </c>
-      <c r="D166" t="s">
-        <v>445</v>
       </c>
       <c r="E166">
         <v>20</v>
       </c>
-      <c r="F166" s="4">
-        <v>62</v>
-      </c>
-      <c r="G166" s="5" t="s">
-        <v>29</v>
+      <c r="F166" s="2">
+        <v>0</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -5837,22 +5799,22 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
+        <v>444</v>
+      </c>
+      <c r="C167" t="s">
+        <v>445</v>
+      </c>
+      <c r="D167" t="s">
         <v>446</v>
-      </c>
-      <c r="C167" t="s">
-        <v>447</v>
-      </c>
-      <c r="D167" t="s">
-        <v>448</v>
       </c>
       <c r="E167">
         <v>24</v>
       </c>
-      <c r="F167" s="4">
-        <v>28</v>
-      </c>
-      <c r="G167" s="5" t="s">
-        <v>29</v>
+      <c r="F167" s="2">
+        <v>0</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -5860,22 +5822,22 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C168" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D168" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E168">
         <v>240</v>
       </c>
-      <c r="F168" s="4">
-        <v>920</v>
-      </c>
-      <c r="G168" s="5" t="s">
-        <v>29</v>
+      <c r="F168" s="2">
+        <v>0</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -5883,22 +5845,22 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C169" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D169" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E169">
         <v>240</v>
       </c>
-      <c r="F169" s="4">
-        <v>102</v>
-      </c>
-      <c r="G169" s="5" t="s">
-        <v>29</v>
+      <c r="F169" s="2">
+        <v>0</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -5906,22 +5868,22 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C170" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D170" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E170">
         <v>480</v>
       </c>
-      <c r="F170" s="4">
-        <v>211</v>
-      </c>
-      <c r="G170" s="5" t="s">
-        <v>29</v>
+      <c r="F170" s="2">
+        <v>0</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -5929,19 +5891,19 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C171" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D171" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E171">
         <v>120</v>
       </c>
       <c r="F171" s="2">
-        <v>753</v>
+        <v>0</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>10</v>
@@ -5952,22 +5914,22 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C172" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D172" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E172">
         <v>240</v>
       </c>
-      <c r="F172" s="4">
-        <v>31</v>
-      </c>
-      <c r="G172" s="5" t="s">
-        <v>29</v>
+      <c r="F172" s="2">
+        <v>0</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -5975,22 +5937,22 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C173" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D173" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E173">
         <v>240</v>
       </c>
-      <c r="F173" s="4">
-        <v>93</v>
-      </c>
-      <c r="G173" s="5" t="s">
-        <v>29</v>
+      <c r="F173" s="2">
+        <v>0</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -5998,22 +5960,22 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C174" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D174" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E174">
         <v>480</v>
       </c>
-      <c r="F174" s="4">
-        <v>378</v>
-      </c>
-      <c r="G174" s="5" t="s">
-        <v>29</v>
+      <c r="F174" s="2">
+        <v>0</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6021,22 +5983,22 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C175" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D175" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E175">
         <v>120</v>
       </c>
-      <c r="F175" s="4">
-        <v>94</v>
-      </c>
-      <c r="G175" s="5" t="s">
-        <v>29</v>
+      <c r="F175" s="2">
+        <v>0</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6044,22 +6006,22 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
+        <v>463</v>
+      </c>
+      <c r="C176" t="s">
+        <v>464</v>
+      </c>
+      <c r="D176" t="s">
         <v>465</v>
-      </c>
-      <c r="C176" t="s">
-        <v>466</v>
-      </c>
-      <c r="D176" t="s">
-        <v>467</v>
       </c>
       <c r="E176">
         <v>120</v>
       </c>
-      <c r="F176" s="4">
-        <v>103</v>
-      </c>
-      <c r="G176" s="5" t="s">
-        <v>29</v>
+      <c r="F176" s="2">
+        <v>0</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6067,22 +6029,22 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
+        <v>466</v>
+      </c>
+      <c r="C177" t="s">
+        <v>467</v>
+      </c>
+      <c r="D177" t="s">
         <v>468</v>
-      </c>
-      <c r="C177" t="s">
-        <v>469</v>
-      </c>
-      <c r="D177" t="s">
-        <v>470</v>
       </c>
       <c r="E177">
         <v>120</v>
       </c>
-      <c r="F177" s="4">
-        <v>93</v>
-      </c>
-      <c r="G177" s="5" t="s">
-        <v>29</v>
+      <c r="F177" s="2">
+        <v>0</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6090,19 +6052,19 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C178" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D178" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E178">
         <v>12</v>
       </c>
       <c r="F178" s="2">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>10</v>
@@ -6113,19 +6075,19 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C179" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D179" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E179">
         <v>12</v>
       </c>
       <c r="F179" s="2">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="G179" s="3" t="s">
         <v>10</v>
@@ -6136,22 +6098,22 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C180" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D180" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E180">
         <v>30</v>
       </c>
-      <c r="F180" s="6">
-        <v>0</v>
-      </c>
-      <c r="G180" s="7" t="s">
-        <v>38</v>
+      <c r="F180" s="2">
+        <v>0</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6159,22 +6121,22 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C181" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D181" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E181">
         <v>12</v>
       </c>
-      <c r="F181" s="4">
-        <v>4</v>
-      </c>
-      <c r="G181" s="5" t="s">
-        <v>29</v>
+      <c r="F181" s="2">
+        <v>0</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6182,22 +6144,22 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C182" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D182" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E182">
         <v>6</v>
       </c>
-      <c r="F182" s="4">
-        <v>6</v>
-      </c>
-      <c r="G182" s="5" t="s">
-        <v>29</v>
+      <c r="F182" s="2">
+        <v>0</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6205,19 +6167,19 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C183" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D183" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E183">
         <v>1</v>
       </c>
       <c r="F183" s="2">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>10</v>
@@ -6228,19 +6190,19 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C184" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D184" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E184">
         <v>20</v>
       </c>
       <c r="F184" s="2">
-        <v>3763</v>
+        <v>0</v>
       </c>
       <c r="G184" s="3" t="s">
         <v>10</v>
@@ -6251,19 +6213,19 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C185" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D185" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E185">
         <v>20</v>
       </c>
       <c r="F185" s="2">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>10</v>
@@ -6274,22 +6236,22 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C186" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D186" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E186">
         <v>20</v>
       </c>
-      <c r="F186" s="4">
-        <v>40</v>
-      </c>
-      <c r="G186" s="5" t="s">
-        <v>29</v>
+      <c r="F186" s="2">
+        <v>0</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -6297,22 +6259,22 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C187" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D187" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E187">
         <v>56</v>
       </c>
-      <c r="F187" s="4">
-        <v>20</v>
-      </c>
-      <c r="G187" s="5" t="s">
-        <v>29</v>
+      <c r="F187" s="2">
+        <v>0</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -6320,22 +6282,22 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C188" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D188" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E188">
         <v>50</v>
       </c>
-      <c r="F188" s="4">
-        <v>17</v>
-      </c>
-      <c r="G188" s="5" t="s">
-        <v>29</v>
+      <c r="F188" s="2">
+        <v>0</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -6343,19 +6305,19 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C189" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D189" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E189">
         <v>50</v>
       </c>
       <c r="F189" s="2">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>10</v>
@@ -6366,19 +6328,19 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C190" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D190" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E190">
         <v>50</v>
       </c>
       <c r="F190" s="2">
-        <v>1181</v>
+        <v>0</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>10</v>
@@ -6389,19 +6351,19 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
+        <v>495</v>
+      </c>
+      <c r="C191" t="s">
+        <v>496</v>
+      </c>
+      <c r="D191" t="s">
         <v>497</v>
-      </c>
-      <c r="C191" t="s">
-        <v>498</v>
-      </c>
-      <c r="D191" t="s">
-        <v>499</v>
       </c>
       <c r="E191">
         <v>50</v>
       </c>
       <c r="F191" s="2">
-        <v>1873</v>
+        <v>0</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>10</v>
@@ -6412,19 +6374,19 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
+        <v>498</v>
+      </c>
+      <c r="C192" t="s">
+        <v>499</v>
+      </c>
+      <c r="D192" t="s">
         <v>500</v>
-      </c>
-      <c r="C192" t="s">
-        <v>501</v>
-      </c>
-      <c r="D192" t="s">
-        <v>502</v>
       </c>
       <c r="E192">
         <v>50</v>
       </c>
       <c r="F192" s="2">
-        <v>1210</v>
+        <v>0</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>10</v>
@@ -6435,19 +6397,19 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
+        <v>501</v>
+      </c>
+      <c r="C193" t="s">
+        <v>502</v>
+      </c>
+      <c r="D193" t="s">
         <v>503</v>
-      </c>
-      <c r="C193" t="s">
-        <v>504</v>
-      </c>
-      <c r="D193" t="s">
-        <v>505</v>
       </c>
       <c r="E193">
         <v>50</v>
       </c>
       <c r="F193" s="2">
-        <v>19771</v>
+        <v>0</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>10</v>
@@ -6458,19 +6420,19 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
+        <v>504</v>
+      </c>
+      <c r="C194" t="s">
+        <v>505</v>
+      </c>
+      <c r="D194" t="s">
         <v>506</v>
-      </c>
-      <c r="C194" t="s">
-        <v>507</v>
-      </c>
-      <c r="D194" t="s">
-        <v>508</v>
       </c>
       <c r="E194">
         <v>100</v>
       </c>
       <c r="F194" s="2">
-        <v>1181</v>
+        <v>0</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>10</v>
@@ -6481,19 +6443,19 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
+        <v>507</v>
+      </c>
+      <c r="C195" t="s">
+        <v>508</v>
+      </c>
+      <c r="D195" t="s">
         <v>509</v>
-      </c>
-      <c r="C195" t="s">
-        <v>510</v>
-      </c>
-      <c r="D195" t="s">
-        <v>511</v>
       </c>
       <c r="E195">
         <v>60</v>
       </c>
       <c r="F195" s="2">
-        <v>454</v>
+        <v>0</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>10</v>
@@ -6504,19 +6466,19 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C196" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D196" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E196">
         <v>100</v>
       </c>
       <c r="F196" s="2">
-        <v>880</v>
+        <v>0</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>10</v>
@@ -6527,19 +6489,19 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
+        <v>512</v>
+      </c>
+      <c r="C197" t="s">
+        <v>513</v>
+      </c>
+      <c r="D197" t="s">
         <v>514</v>
-      </c>
-      <c r="C197" t="s">
-        <v>515</v>
-      </c>
-      <c r="D197" t="s">
-        <v>516</v>
       </c>
       <c r="E197">
         <v>80</v>
       </c>
       <c r="F197" s="2">
-        <v>1247</v>
+        <v>0</v>
       </c>
       <c r="G197" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2652,7 +2652,7 @@
         <v>120</v>
       </c>
       <c r="F28" s="2">
-        <v>9252</v>
+        <v>9192</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -3273,7 +3273,7 @@
         <v>120</v>
       </c>
       <c r="F55" s="4">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>29</v>
@@ -3480,7 +3480,7 @@
         <v>60</v>
       </c>
       <c r="F64" s="2">
-        <v>513</v>
+        <v>489</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>6410</v>
+        <v>5900</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2123,7 +2123,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>20489</v>
+        <v>20189</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2146,7 +2146,7 @@
         <v>200</v>
       </c>
       <c r="F6" s="2">
-        <v>36483</v>
+        <v>36463</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -4147,7 +4147,7 @@
         <v>2</v>
       </c>
       <c r="F93" s="2">
-        <v>283</v>
+        <v>203</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>5900</v>
+        <v>5600</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>5600</v>
+        <v>5780</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2123,7 +2123,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>20189</v>
+        <v>20389</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2514,7 +2514,7 @@
         <v>120</v>
       </c>
       <c r="F22" s="2">
-        <v>2053</v>
+        <v>2103</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -2652,7 +2652,7 @@
         <v>120</v>
       </c>
       <c r="F28" s="2">
-        <v>9192</v>
+        <v>9244</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -2721,7 +2721,7 @@
         <v>120</v>
       </c>
       <c r="F31" s="2">
-        <v>3120</v>
+        <v>3420</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -3710,7 +3710,7 @@
         <v>240</v>
       </c>
       <c r="F74" s="2">
-        <v>1529</v>
+        <v>1624</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3825,7 +3825,7 @@
         <v>120</v>
       </c>
       <c r="F79" s="4">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>29</v>
@@ -4031,11 +4031,11 @@
       <c r="E88">
         <v>20</v>
       </c>
-      <c r="F88" s="6">
-        <v>0</v>
-      </c>
-      <c r="G88" s="7" t="s">
-        <v>38</v>
+      <c r="F88" s="4">
+        <v>10</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4261,11 +4261,11 @@
       <c r="E98">
         <v>5</v>
       </c>
-      <c r="F98" s="6">
-        <v>0</v>
-      </c>
-      <c r="G98" s="7" t="s">
-        <v>38</v>
+      <c r="F98" s="4">
+        <v>20</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4537,11 +4537,11 @@
       <c r="E110">
         <v>54</v>
       </c>
-      <c r="F110" s="2">
-        <v>1093</v>
-      </c>
-      <c r="G110" s="3" t="s">
-        <v>10</v>
+      <c r="F110" s="4">
+        <v>93</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -6401,7 +6401,7 @@
         <v>50</v>
       </c>
       <c r="F191" s="2">
-        <v>1873</v>
+        <v>2173</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>10</v>
@@ -6424,7 +6424,7 @@
         <v>50</v>
       </c>
       <c r="F192" s="2">
-        <v>1210</v>
+        <v>1510</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2123,7 +2123,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>20389</v>
+        <v>20189</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2514,7 +2514,7 @@
         <v>120</v>
       </c>
       <c r="F22" s="2">
-        <v>2103</v>
+        <v>1803</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -2652,7 +2652,7 @@
         <v>120</v>
       </c>
       <c r="F28" s="2">
-        <v>9244</v>
+        <v>8444</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -2721,7 +2721,7 @@
         <v>120</v>
       </c>
       <c r="F31" s="2">
-        <v>3420</v>
+        <v>2820</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -3710,7 +3710,7 @@
         <v>240</v>
       </c>
       <c r="F74" s="2">
-        <v>1624</v>
+        <v>1356</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3825,7 +3825,7 @@
         <v>120</v>
       </c>
       <c r="F79" s="4">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>29</v>
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>2596</v>
+        <v>1896</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -4261,11 +4261,11 @@
       <c r="E98">
         <v>5</v>
       </c>
-      <c r="F98" s="4">
-        <v>20</v>
-      </c>
-      <c r="G98" s="5" t="s">
-        <v>29</v>
+      <c r="F98" s="6">
+        <v>0</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -6401,7 +6401,7 @@
         <v>50</v>
       </c>
       <c r="F191" s="2">
-        <v>2173</v>
+        <v>1373</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>10</v>
@@ -6424,7 +6424,7 @@
         <v>50</v>
       </c>
       <c r="F192" s="2">
-        <v>1510</v>
+        <v>710</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>5600</v>
+        <v>5780</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2514,7 +2514,7 @@
         <v>120</v>
       </c>
       <c r="F22" s="2">
-        <v>2053</v>
+        <v>1803</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -2652,7 +2652,7 @@
         <v>120</v>
       </c>
       <c r="F28" s="2">
-        <v>9192</v>
+        <v>8444</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -2721,7 +2721,7 @@
         <v>120</v>
       </c>
       <c r="F31" s="2">
-        <v>3120</v>
+        <v>2820</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -3710,7 +3710,7 @@
         <v>240</v>
       </c>
       <c r="F74" s="2">
-        <v>1529</v>
+        <v>1356</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3825,7 +3825,7 @@
         <v>120</v>
       </c>
       <c r="F79" s="4">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>29</v>
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>2596</v>
+        <v>1896</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -4031,11 +4031,11 @@
       <c r="E88">
         <v>20</v>
       </c>
-      <c r="F88" s="6">
-        <v>0</v>
-      </c>
-      <c r="G88" s="7" t="s">
-        <v>38</v>
+      <c r="F88" s="4">
+        <v>10</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4537,11 +4537,11 @@
       <c r="E110">
         <v>54</v>
       </c>
-      <c r="F110" s="2">
-        <v>1093</v>
-      </c>
-      <c r="G110" s="3" t="s">
-        <v>10</v>
+      <c r="F110" s="4">
+        <v>93</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -6401,7 +6401,7 @@
         <v>50</v>
       </c>
       <c r="F191" s="2">
-        <v>1873</v>
+        <v>1373</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>10</v>
@@ -6424,7 +6424,7 @@
         <v>50</v>
       </c>
       <c r="F192" s="2">
-        <v>1210</v>
+        <v>710</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2169,7 +2169,7 @@
         <v>120</v>
       </c>
       <c r="F7" s="2">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>5580</v>
+        <v>5565</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>26906</v>
+        <v>26866</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -4078,7 +4078,7 @@
         <v>100</v>
       </c>
       <c r="F90" s="2">
-        <v>108017</v>
+        <v>107957</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>1896</v>
+        <v>1856</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -4078,7 +4078,7 @@
         <v>100</v>
       </c>
       <c r="F90" s="2">
-        <v>107957</v>
+        <v>107557</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>5565</v>
+        <v>5415</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>26866</v>
+        <v>25666</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>1856</v>
+        <v>1938</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -4147,7 +4147,7 @@
         <v>2</v>
       </c>
       <c r="F93" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2536,11 +2536,11 @@
       <c r="E23">
         <v>60</v>
       </c>
-      <c r="F23" s="4">
-        <v>3</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>29</v>
+      <c r="F23" s="6">
+        <v>0</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="515">
   <si>
     <t>#</t>
   </si>
@@ -43,7 +43,7 @@
     <t>LIGAS N° 18 - 80 MM X 2 MM X 1 LBS - NATURAL - ALLEANZA</t>
   </si>
   <si>
-    <t>✓ OK</t>
+    <t>✗ AGOTADO</t>
   </si>
   <si>
     <t>85007</t>
@@ -100,9 +100,6 @@
     <t>CUCHILLA ARTE AK-4</t>
   </si>
   <si>
-    <t>⚠ BAJO</t>
-  </si>
-  <si>
     <t>85770</t>
   </si>
   <si>
@@ -125,9 +122,6 @@
   </si>
   <si>
     <t>CUCHILLLA DE ARTE AK-5/5B</t>
-  </si>
-  <si>
-    <t>✗ AGOTADO</t>
   </si>
   <si>
     <t>85166</t>
@@ -1568,7 +1562,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1587,21 +1581,11 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF065F46"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFD97706"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b/>
       <color rgb="FFDC2626"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1611,16 +1595,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF13DAEC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -1641,7 +1615,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1650,18 +1624,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2054,7 +2016,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>5780</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2077,7 +2039,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>27106</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2100,7 +2062,7 @@
         <v>80</v>
       </c>
       <c r="F4" s="2">
-        <v>7881</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -2123,7 +2085,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>20189</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2146,7 +2108,7 @@
         <v>200</v>
       </c>
       <c r="F6" s="2">
-        <v>36463</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -2169,7 +2131,7 @@
         <v>120</v>
       </c>
       <c r="F7" s="2">
-        <v>1027</v>
+        <v>0</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -2191,11 +2153,11 @@
       <c r="E8">
         <v>120</v>
       </c>
-      <c r="F8" s="4">
-        <v>268</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>29</v>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2203,22 +2165,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
       </c>
       <c r="E9">
         <v>240</v>
       </c>
-      <c r="F9" s="4">
-        <v>253</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>29</v>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2226,22 +2188,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
         <v>33</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>35</v>
       </c>
       <c r="E10">
         <v>200</v>
       </c>
-      <c r="F10" s="4">
-        <v>59</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>29</v>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2249,22 +2211,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
         <v>36</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>37</v>
       </c>
       <c r="E11">
         <v>240</v>
       </c>
-      <c r="F11" s="6">
-        <v>0</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>38</v>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2272,22 +2234,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
         <v>39</v>
-      </c>
-      <c r="C12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" t="s">
-        <v>41</v>
       </c>
       <c r="E12">
         <v>60</v>
       </c>
-      <c r="F12" s="4">
-        <v>132</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>29</v>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2295,22 +2257,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
         <v>42</v>
-      </c>
-      <c r="C13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" t="s">
-        <v>44</v>
       </c>
       <c r="E13">
         <v>120</v>
       </c>
-      <c r="F13" s="4">
-        <v>191</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>29</v>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2318,22 +2280,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
         <v>45</v>
-      </c>
-      <c r="C14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" t="s">
-        <v>47</v>
       </c>
       <c r="E14">
         <v>120</v>
       </c>
-      <c r="F14" s="4">
-        <v>189</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>29</v>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2341,22 +2303,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
         <v>48</v>
-      </c>
-      <c r="C15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" t="s">
-        <v>50</v>
       </c>
       <c r="E15">
         <v>120</v>
       </c>
-      <c r="F15" s="4">
-        <v>84</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>29</v>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2364,19 +2326,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
         <v>51</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" t="s">
-        <v>53</v>
       </c>
       <c r="E16">
         <v>120</v>
       </c>
       <c r="F16" s="2">
-        <v>692</v>
+        <v>0</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -2387,22 +2349,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
         <v>54</v>
-      </c>
-      <c r="C17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" t="s">
-        <v>56</v>
       </c>
       <c r="E17">
         <v>120</v>
       </c>
-      <c r="F17" s="4">
-        <v>257</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>29</v>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2410,19 +2372,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" t="s">
         <v>57</v>
-      </c>
-      <c r="C18" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" t="s">
-        <v>59</v>
       </c>
       <c r="E18">
         <v>120</v>
       </c>
       <c r="F18" s="2">
-        <v>983</v>
+        <v>0</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -2433,22 +2395,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
         <v>60</v>
-      </c>
-      <c r="C19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" t="s">
-        <v>62</v>
       </c>
       <c r="E19">
         <v>120</v>
       </c>
-      <c r="F19" s="4">
-        <v>195</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>29</v>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2456,22 +2418,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" t="s">
         <v>63</v>
-      </c>
-      <c r="C20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" t="s">
-        <v>65</v>
       </c>
       <c r="E20">
         <v>120</v>
       </c>
-      <c r="F20" s="4">
-        <v>75</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>29</v>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2479,22 +2441,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" t="s">
         <v>66</v>
-      </c>
-      <c r="C21" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" t="s">
-        <v>68</v>
       </c>
       <c r="E21">
         <v>120</v>
       </c>
-      <c r="F21" s="4">
-        <v>439</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>29</v>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2502,19 +2464,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
         <v>69</v>
-      </c>
-      <c r="C22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" t="s">
-        <v>71</v>
       </c>
       <c r="E22">
         <v>120</v>
       </c>
       <c r="F22" s="2">
-        <v>1803</v>
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -2525,22 +2487,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" t="s">
         <v>72</v>
-      </c>
-      <c r="C23" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" t="s">
-        <v>74</v>
       </c>
       <c r="E23">
         <v>60</v>
       </c>
-      <c r="F23" s="4">
-        <v>3</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>29</v>
+      <c r="F23" s="2">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2548,22 +2510,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" t="s">
         <v>75</v>
-      </c>
-      <c r="C24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" t="s">
-        <v>77</v>
       </c>
       <c r="E24">
         <v>120</v>
       </c>
-      <c r="F24" s="4">
-        <v>113</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>29</v>
+      <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2571,22 +2533,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" t="s">
         <v>78</v>
-      </c>
-      <c r="C25" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" t="s">
-        <v>80</v>
       </c>
       <c r="E25">
         <v>120</v>
       </c>
-      <c r="F25" s="4">
-        <v>348</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>29</v>
+      <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2594,22 +2556,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" t="s">
         <v>81</v>
-      </c>
-      <c r="C26" t="s">
-        <v>82</v>
-      </c>
-      <c r="D26" t="s">
-        <v>83</v>
       </c>
       <c r="E26">
         <v>120</v>
       </c>
-      <c r="F26" s="4">
-        <v>123</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>29</v>
+      <c r="F26" s="2">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2617,22 +2579,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" t="s">
         <v>84</v>
-      </c>
-      <c r="C27" t="s">
-        <v>85</v>
-      </c>
-      <c r="D27" t="s">
-        <v>86</v>
       </c>
       <c r="E27">
         <v>120</v>
       </c>
-      <c r="F27" s="4">
-        <v>160</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>29</v>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2640,19 +2602,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28" t="s">
         <v>87</v>
-      </c>
-      <c r="C28" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" t="s">
-        <v>89</v>
       </c>
       <c r="E28">
         <v>120</v>
       </c>
       <c r="F28" s="2">
-        <v>8444</v>
+        <v>0</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -2663,22 +2625,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" t="s">
         <v>90</v>
-      </c>
-      <c r="C29" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" t="s">
-        <v>92</v>
       </c>
       <c r="E29">
         <v>72</v>
       </c>
-      <c r="F29" s="4">
-        <v>94</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>29</v>
+      <c r="F29" s="2">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2686,22 +2648,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" t="s">
         <v>93</v>
-      </c>
-      <c r="C30" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" t="s">
-        <v>95</v>
       </c>
       <c r="E30">
         <v>120</v>
       </c>
-      <c r="F30" s="4">
-        <v>56</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>29</v>
+      <c r="F30" s="2">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2709,19 +2671,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" t="s">
+        <v>95</v>
+      </c>
+      <c r="D31" t="s">
         <v>96</v>
-      </c>
-      <c r="C31" t="s">
-        <v>97</v>
-      </c>
-      <c r="D31" t="s">
-        <v>98</v>
       </c>
       <c r="E31">
         <v>120</v>
       </c>
       <c r="F31" s="2">
-        <v>2820</v>
+        <v>0</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -2732,19 +2694,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" t="s">
         <v>99</v>
-      </c>
-      <c r="C32" t="s">
-        <v>100</v>
-      </c>
-      <c r="D32" t="s">
-        <v>101</v>
       </c>
       <c r="E32">
         <v>120</v>
       </c>
       <c r="F32" s="2">
-        <v>1445</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -2755,22 +2717,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" t="s">
         <v>102</v>
-      </c>
-      <c r="C33" t="s">
-        <v>103</v>
-      </c>
-      <c r="D33" t="s">
-        <v>104</v>
       </c>
       <c r="E33">
         <v>144</v>
       </c>
-      <c r="F33" s="6">
-        <v>0</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>38</v>
+      <c r="F33" s="2">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2778,19 +2740,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34" t="s">
         <v>105</v>
-      </c>
-      <c r="C34" t="s">
-        <v>106</v>
-      </c>
-      <c r="D34" t="s">
-        <v>107</v>
       </c>
       <c r="E34">
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>907</v>
+        <v>0</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -2801,22 +2763,22 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>106</v>
+      </c>
+      <c r="C35" t="s">
+        <v>107</v>
+      </c>
+      <c r="D35" t="s">
         <v>108</v>
-      </c>
-      <c r="C35" t="s">
-        <v>109</v>
-      </c>
-      <c r="D35" t="s">
-        <v>110</v>
       </c>
       <c r="E35">
         <v>128</v>
       </c>
-      <c r="F35" s="6">
-        <v>0</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>38</v>
+      <c r="F35" s="2">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2824,22 +2786,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" t="s">
+        <v>110</v>
+      </c>
+      <c r="D36" t="s">
         <v>111</v>
-      </c>
-      <c r="C36" t="s">
-        <v>112</v>
-      </c>
-      <c r="D36" t="s">
-        <v>113</v>
       </c>
       <c r="E36">
         <v>120</v>
       </c>
-      <c r="F36" s="4">
-        <v>118</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>29</v>
+      <c r="F36" s="2">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2847,22 +2809,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" t="s">
+        <v>113</v>
+      </c>
+      <c r="D37" t="s">
         <v>114</v>
-      </c>
-      <c r="C37" t="s">
-        <v>115</v>
-      </c>
-      <c r="D37" t="s">
-        <v>116</v>
       </c>
       <c r="E37">
         <v>240</v>
       </c>
-      <c r="F37" s="4">
-        <v>944</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>29</v>
+      <c r="F37" s="2">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2870,22 +2832,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>115</v>
+      </c>
+      <c r="C38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D38" t="s">
         <v>117</v>
-      </c>
-      <c r="C38" t="s">
-        <v>118</v>
-      </c>
-      <c r="D38" t="s">
-        <v>119</v>
       </c>
       <c r="E38">
         <v>120</v>
       </c>
-      <c r="F38" s="4">
-        <v>123</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>29</v>
+      <c r="F38" s="2">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2893,22 +2855,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>118</v>
+      </c>
+      <c r="C39" t="s">
+        <v>119</v>
+      </c>
+      <c r="D39" t="s">
         <v>120</v>
-      </c>
-      <c r="C39" t="s">
-        <v>121</v>
-      </c>
-      <c r="D39" t="s">
-        <v>122</v>
       </c>
       <c r="E39">
         <v>240</v>
       </c>
-      <c r="F39" s="4">
-        <v>254</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>29</v>
+      <c r="F39" s="2">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2916,22 +2878,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>121</v>
+      </c>
+      <c r="C40" t="s">
+        <v>122</v>
+      </c>
+      <c r="D40" t="s">
         <v>123</v>
-      </c>
-      <c r="C40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D40" t="s">
-        <v>125</v>
       </c>
       <c r="E40">
         <v>240</v>
       </c>
-      <c r="F40" s="4">
-        <v>245</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>29</v>
+      <c r="F40" s="2">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2939,22 +2901,22 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
+        <v>124</v>
+      </c>
+      <c r="C41" t="s">
+        <v>125</v>
+      </c>
+      <c r="D41" t="s">
         <v>126</v>
-      </c>
-      <c r="C41" t="s">
-        <v>127</v>
-      </c>
-      <c r="D41" t="s">
-        <v>128</v>
       </c>
       <c r="E41">
         <v>240</v>
       </c>
-      <c r="F41" s="4">
-        <v>107</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>29</v>
+      <c r="F41" s="2">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2962,22 +2924,22 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D42" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E42">
         <v>240</v>
       </c>
-      <c r="F42" s="4">
-        <v>273</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>29</v>
+      <c r="F42" s="2">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2985,19 +2947,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>129</v>
+      </c>
+      <c r="C43" t="s">
+        <v>130</v>
+      </c>
+      <c r="D43" t="s">
         <v>131</v>
-      </c>
-      <c r="C43" t="s">
-        <v>132</v>
-      </c>
-      <c r="D43" t="s">
-        <v>133</v>
       </c>
       <c r="E43">
         <v>240</v>
       </c>
       <c r="F43" s="2">
-        <v>2865</v>
+        <v>0</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>10</v>
@@ -3008,22 +2970,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>132</v>
+      </c>
+      <c r="C44" t="s">
+        <v>133</v>
+      </c>
+      <c r="D44" t="s">
         <v>134</v>
-      </c>
-      <c r="C44" t="s">
-        <v>135</v>
-      </c>
-      <c r="D44" t="s">
-        <v>136</v>
       </c>
       <c r="E44">
         <v>480</v>
       </c>
-      <c r="F44" s="4">
-        <v>1090</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>29</v>
+      <c r="F44" s="2">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3031,22 +2993,22 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" t="s">
+        <v>136</v>
+      </c>
+      <c r="D45" t="s">
         <v>137</v>
-      </c>
-      <c r="C45" t="s">
-        <v>138</v>
-      </c>
-      <c r="D45" t="s">
-        <v>139</v>
       </c>
       <c r="E45">
         <v>240</v>
       </c>
-      <c r="F45" s="4">
-        <v>163</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>29</v>
+      <c r="F45" s="2">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3054,22 +3016,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>138</v>
+      </c>
+      <c r="C46" t="s">
+        <v>139</v>
+      </c>
+      <c r="D46" t="s">
         <v>140</v>
-      </c>
-      <c r="C46" t="s">
-        <v>141</v>
-      </c>
-      <c r="D46" t="s">
-        <v>142</v>
       </c>
       <c r="E46">
         <v>800</v>
       </c>
-      <c r="F46" s="4">
-        <v>1475</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>29</v>
+      <c r="F46" s="2">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3077,22 +3039,22 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>141</v>
+      </c>
+      <c r="C47" t="s">
+        <v>142</v>
+      </c>
+      <c r="D47" t="s">
         <v>143</v>
-      </c>
-      <c r="C47" t="s">
-        <v>144</v>
-      </c>
-      <c r="D47" t="s">
-        <v>145</v>
       </c>
       <c r="E47">
         <v>240</v>
       </c>
-      <c r="F47" s="4">
-        <v>164</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>29</v>
+      <c r="F47" s="2">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3100,22 +3062,22 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D48" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E48">
         <v>120</v>
       </c>
-      <c r="F48" s="6">
-        <v>0</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>38</v>
+      <c r="F48" s="2">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3123,22 +3085,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>146</v>
+      </c>
+      <c r="C49" t="s">
+        <v>147</v>
+      </c>
+      <c r="D49" t="s">
         <v>148</v>
-      </c>
-      <c r="C49" t="s">
-        <v>149</v>
-      </c>
-      <c r="D49" t="s">
-        <v>150</v>
       </c>
       <c r="E49">
         <v>120</v>
       </c>
-      <c r="F49" s="4">
-        <v>261</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>29</v>
+      <c r="F49" s="2">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3146,22 +3108,22 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>149</v>
+      </c>
+      <c r="C50" t="s">
+        <v>150</v>
+      </c>
+      <c r="D50" t="s">
         <v>151</v>
-      </c>
-      <c r="C50" t="s">
-        <v>152</v>
-      </c>
-      <c r="D50" t="s">
-        <v>153</v>
       </c>
       <c r="E50">
         <v>120</v>
       </c>
-      <c r="F50" s="4">
-        <v>291</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>29</v>
+      <c r="F50" s="2">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3169,22 +3131,22 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>152</v>
+      </c>
+      <c r="C51" t="s">
+        <v>153</v>
+      </c>
+      <c r="D51" t="s">
         <v>154</v>
       </c>
-      <c r="C51" t="s">
-        <v>155</v>
-      </c>
-      <c r="D51" t="s">
-        <v>156</v>
-      </c>
       <c r="E51">
         <v>10</v>
       </c>
-      <c r="F51" s="4">
-        <v>10</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>29</v>
+      <c r="F51" s="2">
+        <v>0</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3192,22 +3154,22 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>155</v>
+      </c>
+      <c r="C52" t="s">
+        <v>156</v>
+      </c>
+      <c r="D52" t="s">
         <v>157</v>
-      </c>
-      <c r="C52" t="s">
-        <v>158</v>
-      </c>
-      <c r="D52" t="s">
-        <v>159</v>
       </c>
       <c r="E52">
         <v>60</v>
       </c>
-      <c r="F52" s="4">
-        <v>82</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>29</v>
+      <c r="F52" s="2">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3215,22 +3177,22 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>158</v>
+      </c>
+      <c r="C53" t="s">
+        <v>159</v>
+      </c>
+      <c r="D53" t="s">
         <v>160</v>
-      </c>
-      <c r="C53" t="s">
-        <v>161</v>
-      </c>
-      <c r="D53" t="s">
-        <v>162</v>
       </c>
       <c r="E53">
         <v>20</v>
       </c>
-      <c r="F53" s="4">
-        <v>27</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>29</v>
+      <c r="F53" s="2">
+        <v>0</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3238,22 +3200,22 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>161</v>
+      </c>
+      <c r="C54" t="s">
+        <v>162</v>
+      </c>
+      <c r="D54" t="s">
         <v>163</v>
-      </c>
-      <c r="C54" t="s">
-        <v>164</v>
-      </c>
-      <c r="D54" t="s">
-        <v>165</v>
       </c>
       <c r="E54">
         <v>720</v>
       </c>
-      <c r="F54" s="4">
-        <v>2342</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>29</v>
+      <c r="F54" s="2">
+        <v>0</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3261,22 +3223,22 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>164</v>
+      </c>
+      <c r="C55" t="s">
+        <v>165</v>
+      </c>
+      <c r="D55" t="s">
         <v>166</v>
-      </c>
-      <c r="C55" t="s">
-        <v>167</v>
-      </c>
-      <c r="D55" t="s">
-        <v>168</v>
       </c>
       <c r="E55">
         <v>120</v>
       </c>
-      <c r="F55" s="4">
-        <v>178</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>29</v>
+      <c r="F55" s="2">
+        <v>0</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -3284,22 +3246,22 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>167</v>
+      </c>
+      <c r="C56" t="s">
+        <v>168</v>
+      </c>
+      <c r="D56" t="s">
         <v>169</v>
-      </c>
-      <c r="C56" t="s">
-        <v>170</v>
-      </c>
-      <c r="D56" t="s">
-        <v>171</v>
       </c>
       <c r="E56">
         <v>120</v>
       </c>
-      <c r="F56" s="6">
-        <v>0</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>38</v>
+      <c r="F56" s="2">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3307,19 +3269,19 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
+        <v>170</v>
+      </c>
+      <c r="C57" t="s">
+        <v>171</v>
+      </c>
+      <c r="D57" t="s">
         <v>172</v>
-      </c>
-      <c r="C57" t="s">
-        <v>173</v>
-      </c>
-      <c r="D57" t="s">
-        <v>174</v>
       </c>
       <c r="E57">
         <v>720</v>
       </c>
       <c r="F57" s="2">
-        <v>4633</v>
+        <v>0</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3330,22 +3292,22 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>173</v>
+      </c>
+      <c r="C58" t="s">
+        <v>174</v>
+      </c>
+      <c r="D58" t="s">
         <v>175</v>
-      </c>
-      <c r="C58" t="s">
-        <v>176</v>
-      </c>
-      <c r="D58" t="s">
-        <v>177</v>
       </c>
       <c r="E58">
         <v>240</v>
       </c>
-      <c r="F58" s="4">
-        <v>201</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>29</v>
+      <c r="F58" s="2">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3353,22 +3315,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
+        <v>176</v>
+      </c>
+      <c r="C59" t="s">
+        <v>177</v>
+      </c>
+      <c r="D59" t="s">
         <v>178</v>
-      </c>
-      <c r="C59" t="s">
-        <v>179</v>
-      </c>
-      <c r="D59" t="s">
-        <v>180</v>
       </c>
       <c r="E59">
         <v>120</v>
       </c>
-      <c r="F59" s="6">
-        <v>0</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>38</v>
+      <c r="F59" s="2">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3376,22 +3338,22 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C60" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D60" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E60">
         <v>240</v>
       </c>
-      <c r="F60" s="6">
-        <v>0</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>38</v>
+      <c r="F60" s="2">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3399,22 +3361,22 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
+        <v>181</v>
+      </c>
+      <c r="C61" t="s">
+        <v>182</v>
+      </c>
+      <c r="D61" t="s">
         <v>183</v>
-      </c>
-      <c r="C61" t="s">
-        <v>184</v>
-      </c>
-      <c r="D61" t="s">
-        <v>185</v>
       </c>
       <c r="E61">
         <v>240</v>
       </c>
-      <c r="F61" s="4">
-        <v>300</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>29</v>
+      <c r="F61" s="2">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3422,22 +3384,22 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C62" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D62" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E62">
         <v>240</v>
       </c>
-      <c r="F62" s="4">
-        <v>198</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>29</v>
+      <c r="F62" s="2">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3445,19 +3407,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>186</v>
+      </c>
+      <c r="C63" t="s">
+        <v>187</v>
+      </c>
+      <c r="D63" t="s">
         <v>188</v>
-      </c>
-      <c r="C63" t="s">
-        <v>189</v>
-      </c>
-      <c r="D63" t="s">
-        <v>190</v>
       </c>
       <c r="E63">
         <v>240</v>
       </c>
       <c r="F63" s="2">
-        <v>7644</v>
+        <v>0</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3468,19 +3430,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C64" t="s">
+        <v>190</v>
+      </c>
+      <c r="D64" t="s">
         <v>191</v>
-      </c>
-      <c r="C64" t="s">
-        <v>192</v>
-      </c>
-      <c r="D64" t="s">
-        <v>193</v>
       </c>
       <c r="E64">
         <v>60</v>
       </c>
       <c r="F64" s="2">
-        <v>489</v>
+        <v>0</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>10</v>
@@ -3491,22 +3453,22 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>192</v>
+      </c>
+      <c r="C65" t="s">
+        <v>193</v>
+      </c>
+      <c r="D65" t="s">
         <v>194</v>
-      </c>
-      <c r="C65" t="s">
-        <v>195</v>
-      </c>
-      <c r="D65" t="s">
-        <v>196</v>
       </c>
       <c r="E65">
         <v>60</v>
       </c>
-      <c r="F65" s="4">
-        <v>65</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>29</v>
+      <c r="F65" s="2">
+        <v>0</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3514,22 +3476,22 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>195</v>
+      </c>
+      <c r="C66" t="s">
+        <v>196</v>
+      </c>
+      <c r="D66" t="s">
         <v>197</v>
-      </c>
-      <c r="C66" t="s">
-        <v>198</v>
-      </c>
-      <c r="D66" t="s">
-        <v>199</v>
       </c>
       <c r="E66">
         <v>120</v>
       </c>
-      <c r="F66" s="4">
-        <v>69</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>29</v>
+      <c r="F66" s="2">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3537,22 +3499,22 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
+        <v>198</v>
+      </c>
+      <c r="C67" t="s">
+        <v>199</v>
+      </c>
+      <c r="D67" t="s">
         <v>200</v>
-      </c>
-      <c r="C67" t="s">
-        <v>201</v>
-      </c>
-      <c r="D67" t="s">
-        <v>202</v>
       </c>
       <c r="E67">
         <v>240</v>
       </c>
-      <c r="F67" s="6">
-        <v>0</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>38</v>
+      <c r="F67" s="2">
+        <v>0</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3560,22 +3522,22 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>201</v>
+      </c>
+      <c r="C68" t="s">
+        <v>202</v>
+      </c>
+      <c r="D68" t="s">
         <v>203</v>
-      </c>
-      <c r="C68" t="s">
-        <v>204</v>
-      </c>
-      <c r="D68" t="s">
-        <v>205</v>
       </c>
       <c r="E68">
         <v>240</v>
       </c>
-      <c r="F68" s="4">
-        <v>55</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>29</v>
+      <c r="F68" s="2">
+        <v>0</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3583,19 +3545,19 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>204</v>
+      </c>
+      <c r="C69" t="s">
+        <v>205</v>
+      </c>
+      <c r="D69" t="s">
         <v>206</v>
-      </c>
-      <c r="C69" t="s">
-        <v>207</v>
-      </c>
-      <c r="D69" t="s">
-        <v>208</v>
       </c>
       <c r="E69">
         <v>240</v>
       </c>
       <c r="F69" s="2">
-        <v>4170</v>
+        <v>0</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -3606,22 +3568,22 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>207</v>
+      </c>
+      <c r="C70" t="s">
+        <v>208</v>
+      </c>
+      <c r="D70" t="s">
         <v>209</v>
-      </c>
-      <c r="C70" t="s">
-        <v>210</v>
-      </c>
-      <c r="D70" t="s">
-        <v>211</v>
       </c>
       <c r="E70">
         <v>240</v>
       </c>
-      <c r="F70" s="4">
-        <v>130</v>
-      </c>
-      <c r="G70" s="5" t="s">
-        <v>29</v>
+      <c r="F70" s="2">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3629,22 +3591,22 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>210</v>
+      </c>
+      <c r="C71" t="s">
+        <v>211</v>
+      </c>
+      <c r="D71" t="s">
         <v>212</v>
-      </c>
-      <c r="C71" t="s">
-        <v>213</v>
-      </c>
-      <c r="D71" t="s">
-        <v>214</v>
       </c>
       <c r="E71">
         <v>240</v>
       </c>
-      <c r="F71" s="6">
-        <v>0</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>38</v>
+      <c r="F71" s="2">
+        <v>0</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3652,22 +3614,22 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>213</v>
+      </c>
+      <c r="C72" t="s">
+        <v>214</v>
+      </c>
+      <c r="D72" t="s">
         <v>215</v>
-      </c>
-      <c r="C72" t="s">
-        <v>216</v>
-      </c>
-      <c r="D72" t="s">
-        <v>217</v>
       </c>
       <c r="E72">
         <v>480</v>
       </c>
-      <c r="F72" s="4">
-        <v>412</v>
-      </c>
-      <c r="G72" s="5" t="s">
-        <v>29</v>
+      <c r="F72" s="2">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3675,22 +3637,22 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>216</v>
+      </c>
+      <c r="C73" t="s">
+        <v>217</v>
+      </c>
+      <c r="D73" t="s">
         <v>218</v>
-      </c>
-      <c r="C73" t="s">
-        <v>219</v>
-      </c>
-      <c r="D73" t="s">
-        <v>220</v>
       </c>
       <c r="E73">
         <v>240</v>
       </c>
-      <c r="F73" s="4">
-        <v>500</v>
-      </c>
-      <c r="G73" s="5" t="s">
-        <v>29</v>
+      <c r="F73" s="2">
+        <v>0</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3698,19 +3660,19 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>219</v>
+      </c>
+      <c r="C74" t="s">
+        <v>220</v>
+      </c>
+      <c r="D74" t="s">
         <v>221</v>
-      </c>
-      <c r="C74" t="s">
-        <v>222</v>
-      </c>
-      <c r="D74" t="s">
-        <v>223</v>
       </c>
       <c r="E74">
         <v>240</v>
       </c>
       <c r="F74" s="2">
-        <v>1356</v>
+        <v>0</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3721,19 +3683,19 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>222</v>
+      </c>
+      <c r="C75" t="s">
+        <v>223</v>
+      </c>
+      <c r="D75" t="s">
         <v>224</v>
-      </c>
-      <c r="C75" t="s">
-        <v>225</v>
-      </c>
-      <c r="D75" t="s">
-        <v>226</v>
       </c>
       <c r="E75">
         <v>240</v>
       </c>
       <c r="F75" s="2">
-        <v>4001</v>
+        <v>0</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -3744,22 +3706,22 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
+        <v>225</v>
+      </c>
+      <c r="C76" t="s">
+        <v>226</v>
+      </c>
+      <c r="D76" t="s">
         <v>227</v>
-      </c>
-      <c r="C76" t="s">
-        <v>228</v>
-      </c>
-      <c r="D76" t="s">
-        <v>229</v>
       </c>
       <c r="E76">
         <v>240</v>
       </c>
-      <c r="F76" s="6">
-        <v>0</v>
-      </c>
-      <c r="G76" s="7" t="s">
-        <v>38</v>
+      <c r="F76" s="2">
+        <v>0</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -3767,22 +3729,22 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C77" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D77" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E77">
         <v>600</v>
       </c>
-      <c r="F77" s="4">
-        <v>529</v>
-      </c>
-      <c r="G77" s="5" t="s">
-        <v>29</v>
+      <c r="F77" s="2">
+        <v>0</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -3790,22 +3752,22 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
+        <v>230</v>
+      </c>
+      <c r="C78" t="s">
+        <v>231</v>
+      </c>
+      <c r="D78" t="s">
         <v>232</v>
-      </c>
-      <c r="C78" t="s">
-        <v>233</v>
-      </c>
-      <c r="D78" t="s">
-        <v>234</v>
       </c>
       <c r="E78">
         <v>120</v>
       </c>
-      <c r="F78" s="4">
-        <v>114</v>
-      </c>
-      <c r="G78" s="5" t="s">
-        <v>29</v>
+      <c r="F78" s="2">
+        <v>0</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -3813,22 +3775,22 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
+        <v>233</v>
+      </c>
+      <c r="C79" t="s">
+        <v>234</v>
+      </c>
+      <c r="D79" t="s">
         <v>235</v>
-      </c>
-      <c r="C79" t="s">
-        <v>236</v>
-      </c>
-      <c r="D79" t="s">
-        <v>237</v>
       </c>
       <c r="E79">
         <v>120</v>
       </c>
-      <c r="F79" s="4">
-        <v>4</v>
-      </c>
-      <c r="G79" s="5" t="s">
-        <v>29</v>
+      <c r="F79" s="2">
+        <v>0</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3836,22 +3798,22 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>236</v>
+      </c>
+      <c r="C80" t="s">
+        <v>237</v>
+      </c>
+      <c r="D80" t="s">
         <v>238</v>
-      </c>
-      <c r="C80" t="s">
-        <v>239</v>
-      </c>
-      <c r="D80" t="s">
-        <v>240</v>
       </c>
       <c r="E80">
         <v>60</v>
       </c>
-      <c r="F80" s="4">
-        <v>12</v>
-      </c>
-      <c r="G80" s="5" t="s">
-        <v>29</v>
+      <c r="F80" s="2">
+        <v>0</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3859,19 +3821,19 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
+        <v>239</v>
+      </c>
+      <c r="C81" t="s">
+        <v>240</v>
+      </c>
+      <c r="D81" t="s">
         <v>241</v>
-      </c>
-      <c r="C81" t="s">
-        <v>242</v>
-      </c>
-      <c r="D81" t="s">
-        <v>243</v>
       </c>
       <c r="E81">
         <v>20</v>
       </c>
       <c r="F81" s="2">
-        <v>469</v>
+        <v>0</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>10</v>
@@ -3882,19 +3844,19 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
+        <v>242</v>
+      </c>
+      <c r="C82" t="s">
+        <v>243</v>
+      </c>
+      <c r="D82" t="s">
         <v>244</v>
-      </c>
-      <c r="C82" t="s">
-        <v>245</v>
-      </c>
-      <c r="D82" t="s">
-        <v>246</v>
       </c>
       <c r="E82">
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>1896</v>
+        <v>0</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -3905,22 +3867,22 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
+        <v>245</v>
+      </c>
+      <c r="C83" t="s">
+        <v>246</v>
+      </c>
+      <c r="D83" t="s">
         <v>247</v>
-      </c>
-      <c r="C83" t="s">
-        <v>248</v>
-      </c>
-      <c r="D83" t="s">
-        <v>249</v>
       </c>
       <c r="E83">
         <v>40</v>
       </c>
-      <c r="F83" s="6">
-        <v>0</v>
-      </c>
-      <c r="G83" s="7" t="s">
-        <v>38</v>
+      <c r="F83" s="2">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -3928,22 +3890,22 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
+        <v>248</v>
+      </c>
+      <c r="C84" t="s">
+        <v>249</v>
+      </c>
+      <c r="D84" t="s">
         <v>250</v>
-      </c>
-      <c r="C84" t="s">
-        <v>251</v>
-      </c>
-      <c r="D84" t="s">
-        <v>252</v>
       </c>
       <c r="E84">
         <v>40</v>
       </c>
-      <c r="F84" s="4">
-        <v>80</v>
-      </c>
-      <c r="G84" s="5" t="s">
-        <v>29</v>
+      <c r="F84" s="2">
+        <v>0</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -3951,22 +3913,22 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
+        <v>251</v>
+      </c>
+      <c r="C85" t="s">
+        <v>252</v>
+      </c>
+      <c r="D85" t="s">
         <v>253</v>
-      </c>
-      <c r="C85" t="s">
-        <v>254</v>
-      </c>
-      <c r="D85" t="s">
-        <v>255</v>
       </c>
       <c r="E85">
         <v>40</v>
       </c>
-      <c r="F85" s="6">
-        <v>0</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>38</v>
+      <c r="F85" s="2">
+        <v>0</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -3974,22 +3936,22 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
+        <v>254</v>
+      </c>
+      <c r="C86" t="s">
+        <v>255</v>
+      </c>
+      <c r="D86" t="s">
         <v>256</v>
-      </c>
-      <c r="C86" t="s">
-        <v>257</v>
-      </c>
-      <c r="D86" t="s">
-        <v>258</v>
       </c>
       <c r="E86">
         <v>40</v>
       </c>
-      <c r="F86" s="6">
-        <v>0</v>
-      </c>
-      <c r="G86" s="7" t="s">
-        <v>38</v>
+      <c r="F86" s="2">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -3997,22 +3959,22 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
+        <v>257</v>
+      </c>
+      <c r="C87" t="s">
+        <v>258</v>
+      </c>
+      <c r="D87" t="s">
         <v>259</v>
-      </c>
-      <c r="C87" t="s">
-        <v>260</v>
-      </c>
-      <c r="D87" t="s">
-        <v>261</v>
       </c>
       <c r="E87">
         <v>40</v>
       </c>
-      <c r="F87" s="6">
-        <v>0</v>
-      </c>
-      <c r="G87" s="7" t="s">
-        <v>38</v>
+      <c r="F87" s="2">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4020,22 +3982,22 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
+        <v>260</v>
+      </c>
+      <c r="C88" t="s">
+        <v>261</v>
+      </c>
+      <c r="D88" t="s">
         <v>262</v>
-      </c>
-      <c r="C88" t="s">
-        <v>263</v>
-      </c>
-      <c r="D88" t="s">
-        <v>264</v>
       </c>
       <c r="E88">
         <v>20</v>
       </c>
-      <c r="F88" s="4">
-        <v>10</v>
-      </c>
-      <c r="G88" s="5" t="s">
-        <v>29</v>
+      <c r="F88" s="2">
+        <v>0</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4043,19 +4005,19 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
+        <v>263</v>
+      </c>
+      <c r="C89" t="s">
+        <v>264</v>
+      </c>
+      <c r="D89" t="s">
         <v>265</v>
-      </c>
-      <c r="C89" t="s">
-        <v>266</v>
-      </c>
-      <c r="D89" t="s">
-        <v>267</v>
       </c>
       <c r="E89">
         <v>20</v>
       </c>
       <c r="F89" s="2">
-        <v>1473</v>
+        <v>0</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>10</v>
@@ -4066,19 +4028,19 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
+        <v>266</v>
+      </c>
+      <c r="C90" t="s">
+        <v>267</v>
+      </c>
+      <c r="D90" t="s">
         <v>268</v>
-      </c>
-      <c r="C90" t="s">
-        <v>269</v>
-      </c>
-      <c r="D90" t="s">
-        <v>270</v>
       </c>
       <c r="E90">
         <v>100</v>
       </c>
       <c r="F90" s="2">
-        <v>108017</v>
+        <v>0</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -4089,19 +4051,19 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
+        <v>269</v>
+      </c>
+      <c r="C91" t="s">
+        <v>270</v>
+      </c>
+      <c r="D91" t="s">
         <v>271</v>
       </c>
-      <c r="C91" t="s">
-        <v>272</v>
-      </c>
-      <c r="D91" t="s">
-        <v>273</v>
-      </c>
       <c r="E91">
         <v>10</v>
       </c>
       <c r="F91" s="2">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -4112,19 +4074,19 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
+        <v>272</v>
+      </c>
+      <c r="C92" t="s">
+        <v>273</v>
+      </c>
+      <c r="D92" t="s">
         <v>274</v>
       </c>
-      <c r="C92" t="s">
-        <v>275</v>
-      </c>
-      <c r="D92" t="s">
-        <v>276</v>
-      </c>
       <c r="E92">
         <v>10</v>
       </c>
       <c r="F92" s="2">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -4135,19 +4097,19 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
+        <v>275</v>
+      </c>
+      <c r="C93" t="s">
+        <v>276</v>
+      </c>
+      <c r="D93" t="s">
         <v>277</v>
-      </c>
-      <c r="C93" t="s">
-        <v>278</v>
-      </c>
-      <c r="D93" t="s">
-        <v>279</v>
       </c>
       <c r="E93">
         <v>2</v>
       </c>
       <c r="F93" s="2">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -4158,19 +4120,19 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C94" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D94" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E94">
         <v>6</v>
       </c>
       <c r="F94" s="2">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4181,22 +4143,22 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
+        <v>280</v>
+      </c>
+      <c r="C95" t="s">
+        <v>281</v>
+      </c>
+      <c r="D95" t="s">
         <v>282</v>
-      </c>
-      <c r="C95" t="s">
-        <v>283</v>
-      </c>
-      <c r="D95" t="s">
-        <v>284</v>
       </c>
       <c r="E95">
         <v>120</v>
       </c>
-      <c r="F95" s="6">
-        <v>0</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>38</v>
+      <c r="F95" s="2">
+        <v>0</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4204,22 +4166,22 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C96" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D96" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E96">
         <v>120</v>
       </c>
-      <c r="F96" s="6">
-        <v>0</v>
-      </c>
-      <c r="G96" s="7" t="s">
-        <v>38</v>
+      <c r="F96" s="2">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -4227,22 +4189,22 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
+        <v>285</v>
+      </c>
+      <c r="C97" t="s">
+        <v>286</v>
+      </c>
+      <c r="D97" t="s">
         <v>287</v>
       </c>
-      <c r="C97" t="s">
-        <v>288</v>
-      </c>
-      <c r="D97" t="s">
-        <v>289</v>
-      </c>
       <c r="E97">
         <v>10</v>
       </c>
-      <c r="F97" s="4">
-        <v>7</v>
-      </c>
-      <c r="G97" s="5" t="s">
-        <v>29</v>
+      <c r="F97" s="2">
+        <v>0</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4250,22 +4212,22 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
+        <v>288</v>
+      </c>
+      <c r="C98" t="s">
+        <v>289</v>
+      </c>
+      <c r="D98" t="s">
         <v>290</v>
-      </c>
-      <c r="C98" t="s">
-        <v>291</v>
-      </c>
-      <c r="D98" t="s">
-        <v>292</v>
       </c>
       <c r="E98">
         <v>5</v>
       </c>
-      <c r="F98" s="6">
-        <v>0</v>
-      </c>
-      <c r="G98" s="7" t="s">
-        <v>38</v>
+      <c r="F98" s="2">
+        <v>0</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4273,22 +4235,22 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
+        <v>291</v>
+      </c>
+      <c r="C99" t="s">
+        <v>292</v>
+      </c>
+      <c r="D99" t="s">
         <v>293</v>
-      </c>
-      <c r="C99" t="s">
-        <v>294</v>
-      </c>
-      <c r="D99" t="s">
-        <v>295</v>
       </c>
       <c r="E99">
         <v>5</v>
       </c>
-      <c r="F99" s="6">
-        <v>0</v>
-      </c>
-      <c r="G99" s="7" t="s">
-        <v>38</v>
+      <c r="F99" s="2">
+        <v>0</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -4296,19 +4258,19 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
+        <v>294</v>
+      </c>
+      <c r="C100" t="s">
+        <v>295</v>
+      </c>
+      <c r="D100" t="s">
         <v>296</v>
-      </c>
-      <c r="C100" t="s">
-        <v>297</v>
-      </c>
-      <c r="D100" t="s">
-        <v>298</v>
       </c>
       <c r="E100">
         <v>6</v>
       </c>
       <c r="F100" s="2">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -4319,19 +4281,19 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
+        <v>297</v>
+      </c>
+      <c r="C101" t="s">
+        <v>298</v>
+      </c>
+      <c r="D101" t="s">
         <v>299</v>
-      </c>
-      <c r="C101" t="s">
-        <v>300</v>
-      </c>
-      <c r="D101" t="s">
-        <v>301</v>
       </c>
       <c r="E101">
         <v>6</v>
       </c>
       <c r="F101" s="2">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -4342,19 +4304,19 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
+        <v>300</v>
+      </c>
+      <c r="C102" t="s">
+        <v>301</v>
+      </c>
+      <c r="D102" t="s">
         <v>302</v>
-      </c>
-      <c r="C102" t="s">
-        <v>303</v>
-      </c>
-      <c r="D102" t="s">
-        <v>304</v>
       </c>
       <c r="E102">
         <v>6</v>
       </c>
       <c r="F102" s="2">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>10</v>
@@ -4365,19 +4327,19 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
+        <v>303</v>
+      </c>
+      <c r="C103" t="s">
+        <v>304</v>
+      </c>
+      <c r="D103" t="s">
         <v>305</v>
-      </c>
-      <c r="C103" t="s">
-        <v>306</v>
-      </c>
-      <c r="D103" t="s">
-        <v>307</v>
       </c>
       <c r="E103">
         <v>6</v>
       </c>
       <c r="F103" s="2">
-        <v>391</v>
+        <v>0</v>
       </c>
       <c r="G103" s="3" t="s">
         <v>10</v>
@@ -4388,22 +4350,22 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
+        <v>306</v>
+      </c>
+      <c r="C104" t="s">
+        <v>307</v>
+      </c>
+      <c r="D104" t="s">
         <v>308</v>
-      </c>
-      <c r="C104" t="s">
-        <v>309</v>
-      </c>
-      <c r="D104" t="s">
-        <v>310</v>
       </c>
       <c r="E104">
         <v>200</v>
       </c>
-      <c r="F104" s="4">
-        <v>4</v>
-      </c>
-      <c r="G104" s="5" t="s">
-        <v>29</v>
+      <c r="F104" s="2">
+        <v>0</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -4411,19 +4373,19 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
+        <v>309</v>
+      </c>
+      <c r="C105" t="s">
+        <v>310</v>
+      </c>
+      <c r="D105" t="s">
         <v>311</v>
-      </c>
-      <c r="C105" t="s">
-        <v>312</v>
-      </c>
-      <c r="D105" t="s">
-        <v>313</v>
       </c>
       <c r="E105">
         <v>56</v>
       </c>
       <c r="F105" s="2">
-        <v>354</v>
+        <v>0</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>10</v>
@@ -4434,22 +4396,22 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
+        <v>312</v>
+      </c>
+      <c r="C106" t="s">
+        <v>313</v>
+      </c>
+      <c r="D106" t="s">
         <v>314</v>
-      </c>
-      <c r="C106" t="s">
-        <v>315</v>
-      </c>
-      <c r="D106" t="s">
-        <v>316</v>
       </c>
       <c r="E106">
         <v>120</v>
       </c>
-      <c r="F106" s="4">
-        <v>15</v>
-      </c>
-      <c r="G106" s="5" t="s">
-        <v>29</v>
+      <c r="F106" s="2">
+        <v>0</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4457,22 +4419,22 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
+        <v>315</v>
+      </c>
+      <c r="C107" t="s">
+        <v>316</v>
+      </c>
+      <c r="D107" t="s">
         <v>317</v>
-      </c>
-      <c r="C107" t="s">
-        <v>318</v>
-      </c>
-      <c r="D107" t="s">
-        <v>319</v>
       </c>
       <c r="E107">
         <v>120</v>
       </c>
-      <c r="F107" s="4">
-        <v>1</v>
-      </c>
-      <c r="G107" s="5" t="s">
-        <v>29</v>
+      <c r="F107" s="2">
+        <v>0</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -4480,22 +4442,22 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
+        <v>318</v>
+      </c>
+      <c r="C108" t="s">
+        <v>319</v>
+      </c>
+      <c r="D108" t="s">
         <v>320</v>
-      </c>
-      <c r="C108" t="s">
-        <v>321</v>
-      </c>
-      <c r="D108" t="s">
-        <v>322</v>
       </c>
       <c r="E108">
         <v>18</v>
       </c>
-      <c r="F108" s="4">
-        <v>79</v>
-      </c>
-      <c r="G108" s="5" t="s">
-        <v>29</v>
+      <c r="F108" s="2">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -4503,22 +4465,22 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C109" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D109" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E109">
         <v>6</v>
       </c>
-      <c r="F109" s="6">
-        <v>0</v>
-      </c>
-      <c r="G109" s="7" t="s">
-        <v>38</v>
+      <c r="F109" s="2">
+        <v>0</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -4526,22 +4488,22 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
+        <v>323</v>
+      </c>
+      <c r="C110" t="s">
+        <v>324</v>
+      </c>
+      <c r="D110" t="s">
         <v>325</v>
-      </c>
-      <c r="C110" t="s">
-        <v>326</v>
-      </c>
-      <c r="D110" t="s">
-        <v>327</v>
       </c>
       <c r="E110">
         <v>54</v>
       </c>
-      <c r="F110" s="4">
-        <v>93</v>
-      </c>
-      <c r="G110" s="5" t="s">
-        <v>29</v>
+      <c r="F110" s="2">
+        <v>0</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -4549,22 +4511,22 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C111" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D111" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E111">
         <v>10</v>
       </c>
-      <c r="F111" s="6">
-        <v>0</v>
-      </c>
-      <c r="G111" s="7" t="s">
-        <v>38</v>
+      <c r="F111" s="2">
+        <v>0</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -4572,22 +4534,22 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C112" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D112" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E112">
         <v>12</v>
       </c>
-      <c r="F112" s="6">
-        <v>0</v>
-      </c>
-      <c r="G112" s="7" t="s">
-        <v>38</v>
+      <c r="F112" s="2">
+        <v>0</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -4595,22 +4557,22 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C113" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D113" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E113">
         <v>12</v>
       </c>
-      <c r="F113" s="6">
-        <v>0</v>
-      </c>
-      <c r="G113" s="7" t="s">
-        <v>38</v>
+      <c r="F113" s="2">
+        <v>0</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -4618,19 +4580,19 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C114" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D114" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E114">
         <v>5</v>
       </c>
       <c r="F114" s="2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -4641,22 +4603,22 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C115" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D115" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E115">
         <v>800</v>
       </c>
-      <c r="F115" s="4">
-        <v>312</v>
-      </c>
-      <c r="G115" s="5" t="s">
-        <v>29</v>
+      <c r="F115" s="2">
+        <v>0</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -4664,22 +4626,22 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C116" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D116" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E116">
         <v>5</v>
       </c>
-      <c r="F116" s="6">
-        <v>0</v>
-      </c>
-      <c r="G116" s="7" t="s">
-        <v>38</v>
+      <c r="F116" s="2">
+        <v>0</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -4687,22 +4649,22 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C117" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D117" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E117">
         <v>5</v>
       </c>
-      <c r="F117" s="4">
-        <v>2</v>
-      </c>
-      <c r="G117" s="5" t="s">
-        <v>29</v>
+      <c r="F117" s="2">
+        <v>0</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -4710,19 +4672,19 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C118" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D118" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E118">
         <v>10</v>
       </c>
       <c r="F118" s="2">
-        <v>314</v>
+        <v>0</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>10</v>
@@ -4733,22 +4695,22 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C119" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D119" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E119">
         <v>10</v>
       </c>
-      <c r="F119" s="4">
-        <v>6</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>29</v>
+      <c r="F119" s="2">
+        <v>0</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -4756,22 +4718,22 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C120" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D120" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E120">
         <v>10</v>
       </c>
-      <c r="F120" s="4">
-        <v>36</v>
-      </c>
-      <c r="G120" s="5" t="s">
-        <v>29</v>
+      <c r="F120" s="2">
+        <v>0</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -4779,22 +4741,22 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C121" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D121" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E121">
         <v>6</v>
       </c>
-      <c r="F121" s="6">
-        <v>0</v>
-      </c>
-      <c r="G121" s="7" t="s">
-        <v>38</v>
+      <c r="F121" s="2">
+        <v>0</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -4802,22 +4764,22 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C122" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D122" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E122">
         <v>6</v>
       </c>
-      <c r="F122" s="6">
-        <v>0</v>
-      </c>
-      <c r="G122" s="7" t="s">
-        <v>38</v>
+      <c r="F122" s="2">
+        <v>0</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -4825,22 +4787,22 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C123" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D123" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E123">
         <v>40</v>
       </c>
-      <c r="F123" s="4">
-        <v>127</v>
-      </c>
-      <c r="G123" s="5" t="s">
-        <v>29</v>
+      <c r="F123" s="2">
+        <v>0</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -4848,19 +4810,19 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C124" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D124" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E124">
         <v>4</v>
       </c>
       <c r="F124" s="2">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>10</v>
@@ -4871,22 +4833,22 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
+        <v>354</v>
+      </c>
+      <c r="C125" t="s">
+        <v>355</v>
+      </c>
+      <c r="D125" t="s">
         <v>356</v>
-      </c>
-      <c r="C125" t="s">
-        <v>357</v>
-      </c>
-      <c r="D125" t="s">
-        <v>358</v>
       </c>
       <c r="E125">
         <v>1</v>
       </c>
-      <c r="F125" s="6">
-        <v>0</v>
-      </c>
-      <c r="G125" s="7" t="s">
-        <v>38</v>
+      <c r="F125" s="2">
+        <v>0</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -4894,22 +4856,22 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C126" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D126" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E126">
         <v>4</v>
       </c>
-      <c r="F126" s="4">
-        <v>17</v>
-      </c>
-      <c r="G126" s="5" t="s">
-        <v>29</v>
+      <c r="F126" s="2">
+        <v>0</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -4917,19 +4879,19 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C127" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D127" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E127">
         <v>4</v>
       </c>
       <c r="F127" s="2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>10</v>
@@ -4940,22 +4902,22 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C128" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D128" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E128">
         <v>4</v>
       </c>
-      <c r="F128" s="4">
-        <v>18</v>
-      </c>
-      <c r="G128" s="5" t="s">
-        <v>29</v>
+      <c r="F128" s="2">
+        <v>0</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -4963,22 +4925,22 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C129" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D129" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E129">
         <v>1</v>
       </c>
-      <c r="F129" s="4">
-        <v>4</v>
-      </c>
-      <c r="G129" s="5" t="s">
-        <v>29</v>
+      <c r="F129" s="2">
+        <v>0</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -4986,22 +4948,22 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C130" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D130" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E130">
         <v>60</v>
       </c>
-      <c r="F130" s="4">
-        <v>3</v>
-      </c>
-      <c r="G130" s="5" t="s">
-        <v>29</v>
+      <c r="F130" s="2">
+        <v>0</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5009,19 +4971,19 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C131" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D131" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E131">
         <v>60</v>
       </c>
       <c r="F131" s="2">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>10</v>
@@ -5032,22 +4994,22 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C132" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D132" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E132">
         <v>60</v>
       </c>
-      <c r="F132" s="4">
-        <v>58</v>
-      </c>
-      <c r="G132" s="5" t="s">
-        <v>29</v>
+      <c r="F132" s="2">
+        <v>0</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5055,22 +5017,22 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C133" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D133" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E133">
         <v>60</v>
       </c>
-      <c r="F133" s="4">
-        <v>138</v>
-      </c>
-      <c r="G133" s="5" t="s">
-        <v>29</v>
+      <c r="F133" s="2">
+        <v>0</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5078,19 +5040,19 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C134" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D134" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E134">
         <v>60</v>
       </c>
       <c r="F134" s="2">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>10</v>
@@ -5101,19 +5063,19 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C135" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D135" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E135">
         <v>60</v>
       </c>
       <c r="F135" s="2">
-        <v>521</v>
+        <v>0</v>
       </c>
       <c r="G135" s="3" t="s">
         <v>10</v>
@@ -5124,19 +5086,19 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C136" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D136" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E136">
         <v>60</v>
       </c>
       <c r="F136" s="2">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>10</v>
@@ -5147,19 +5109,19 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C137" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D137" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E137">
         <v>30</v>
       </c>
       <c r="F137" s="2">
-        <v>1601</v>
+        <v>0</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>10</v>
@@ -5170,19 +5132,19 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C138" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D138" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E138">
         <v>40</v>
       </c>
       <c r="F138" s="2">
-        <v>1130</v>
+        <v>0</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>10</v>
@@ -5193,19 +5155,19 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C139" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D139" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E139">
         <v>63</v>
       </c>
       <c r="F139" s="2">
-        <v>566</v>
+        <v>0</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>10</v>
@@ -5216,19 +5178,19 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C140" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D140" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E140">
         <v>10</v>
       </c>
       <c r="F140" s="2">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>10</v>
@@ -5239,22 +5201,22 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C141" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D141" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E141">
         <v>40</v>
       </c>
-      <c r="F141" s="4">
-        <v>108</v>
-      </c>
-      <c r="G141" s="5" t="s">
-        <v>29</v>
+      <c r="F141" s="2">
+        <v>0</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -5262,22 +5224,22 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C142" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D142" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E142">
         <v>60</v>
       </c>
-      <c r="F142" s="4">
-        <v>122</v>
-      </c>
-      <c r="G142" s="5" t="s">
-        <v>29</v>
+      <c r="F142" s="2">
+        <v>0</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -5285,22 +5247,22 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C143" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D143" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E143">
         <v>6</v>
       </c>
-      <c r="F143" s="4">
-        <v>15</v>
-      </c>
-      <c r="G143" s="5" t="s">
-        <v>29</v>
+      <c r="F143" s="2">
+        <v>0</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -5308,22 +5270,22 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C144" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D144" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E144">
         <v>18</v>
       </c>
-      <c r="F144" s="6">
-        <v>0</v>
-      </c>
-      <c r="G144" s="7" t="s">
-        <v>38</v>
+      <c r="F144" s="2">
+        <v>0</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -5331,22 +5293,22 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C145" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D145" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E145">
         <v>8</v>
       </c>
-      <c r="F145" s="4">
-        <v>10</v>
-      </c>
-      <c r="G145" s="5" t="s">
-        <v>29</v>
+      <c r="F145" s="2">
+        <v>0</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -5354,22 +5316,22 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C146" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D146" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E146">
         <v>30</v>
       </c>
-      <c r="F146" s="4">
-        <v>34</v>
-      </c>
-      <c r="G146" s="5" t="s">
-        <v>29</v>
+      <c r="F146" s="2">
+        <v>0</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -5377,22 +5339,22 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C147" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D147" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E147">
         <v>2</v>
       </c>
-      <c r="F147" s="6">
-        <v>0</v>
-      </c>
-      <c r="G147" s="7" t="s">
-        <v>38</v>
+      <c r="F147" s="2">
+        <v>0</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -5400,19 +5362,19 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C148" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D148" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E148">
         <v>5</v>
       </c>
       <c r="F148" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G148" s="3" t="s">
         <v>10</v>
@@ -5423,19 +5385,19 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C149" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D149" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E149">
         <v>5</v>
       </c>
       <c r="F149" s="2">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="G149" s="3" t="s">
         <v>10</v>
@@ -5446,19 +5408,19 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C150" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D150" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E150">
         <v>5</v>
       </c>
       <c r="F150" s="2">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>10</v>
@@ -5469,19 +5431,19 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C151" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D151" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E151">
         <v>5</v>
       </c>
       <c r="F151" s="2">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>10</v>
@@ -5492,22 +5454,22 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C152" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D152" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E152">
         <v>20</v>
       </c>
-      <c r="F152" s="4">
-        <v>8</v>
-      </c>
-      <c r="G152" s="5" t="s">
-        <v>29</v>
+      <c r="F152" s="2">
+        <v>0</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -5515,22 +5477,22 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C153" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D153" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E153">
         <v>240</v>
       </c>
-      <c r="F153" s="4">
-        <v>640</v>
-      </c>
-      <c r="G153" s="5" t="s">
-        <v>29</v>
+      <c r="F153" s="2">
+        <v>0</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -5538,22 +5500,22 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
+        <v>413</v>
+      </c>
+      <c r="C154" t="s">
+        <v>414</v>
+      </c>
+      <c r="D154" t="s">
         <v>415</v>
-      </c>
-      <c r="C154" t="s">
-        <v>416</v>
-      </c>
-      <c r="D154" t="s">
-        <v>417</v>
       </c>
       <c r="E154">
         <v>120</v>
       </c>
-      <c r="F154" s="4">
-        <v>121</v>
-      </c>
-      <c r="G154" s="5" t="s">
-        <v>29</v>
+      <c r="F154" s="2">
+        <v>0</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -5561,19 +5523,19 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C155" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D155" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E155">
         <v>60</v>
       </c>
       <c r="F155" s="2">
-        <v>855</v>
+        <v>0</v>
       </c>
       <c r="G155" s="3" t="s">
         <v>10</v>
@@ -5584,22 +5546,22 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C156" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D156" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E156">
         <v>120</v>
       </c>
-      <c r="F156" s="6">
-        <v>0</v>
-      </c>
-      <c r="G156" s="7" t="s">
-        <v>38</v>
+      <c r="F156" s="2">
+        <v>0</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -5607,22 +5569,22 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
+        <v>420</v>
+      </c>
+      <c r="C157" t="s">
+        <v>421</v>
+      </c>
+      <c r="D157" t="s">
         <v>422</v>
-      </c>
-      <c r="C157" t="s">
-        <v>423</v>
-      </c>
-      <c r="D157" t="s">
-        <v>424</v>
       </c>
       <c r="E157">
         <v>72</v>
       </c>
-      <c r="F157" s="4">
-        <v>66</v>
-      </c>
-      <c r="G157" s="5" t="s">
-        <v>29</v>
+      <c r="F157" s="2">
+        <v>0</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -5630,22 +5592,22 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C158" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D158" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E158">
         <v>60</v>
       </c>
-      <c r="F158" s="4">
-        <v>30</v>
-      </c>
-      <c r="G158" s="5" t="s">
-        <v>29</v>
+      <c r="F158" s="2">
+        <v>0</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5653,22 +5615,22 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
+        <v>425</v>
+      </c>
+      <c r="C159" t="s">
+        <v>426</v>
+      </c>
+      <c r="D159" t="s">
         <v>427</v>
-      </c>
-      <c r="C159" t="s">
-        <v>428</v>
-      </c>
-      <c r="D159" t="s">
-        <v>429</v>
       </c>
       <c r="E159">
         <v>120</v>
       </c>
-      <c r="F159" s="4">
-        <v>83</v>
-      </c>
-      <c r="G159" s="5" t="s">
-        <v>29</v>
+      <c r="F159" s="2">
+        <v>0</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -5676,22 +5638,22 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
+        <v>428</v>
+      </c>
+      <c r="C160" t="s">
+        <v>429</v>
+      </c>
+      <c r="D160" t="s">
         <v>430</v>
-      </c>
-      <c r="C160" t="s">
-        <v>431</v>
-      </c>
-      <c r="D160" t="s">
-        <v>432</v>
       </c>
       <c r="E160">
         <v>72</v>
       </c>
-      <c r="F160" s="4">
-        <v>10</v>
-      </c>
-      <c r="G160" s="5" t="s">
-        <v>29</v>
+      <c r="F160" s="2">
+        <v>0</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5699,22 +5661,22 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C161" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D161" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E161">
         <v>20</v>
       </c>
-      <c r="F161" s="4">
-        <v>51</v>
-      </c>
-      <c r="G161" s="5" t="s">
-        <v>29</v>
+      <c r="F161" s="2">
+        <v>0</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5722,22 +5684,22 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C162" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D162" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E162">
         <v>100</v>
       </c>
-      <c r="F162" s="4">
-        <v>74</v>
-      </c>
-      <c r="G162" s="5" t="s">
-        <v>29</v>
+      <c r="F162" s="2">
+        <v>0</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -5745,22 +5707,22 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C163" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D163" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E163">
         <v>5</v>
       </c>
-      <c r="F163" s="4">
-        <v>11</v>
-      </c>
-      <c r="G163" s="5" t="s">
-        <v>29</v>
+      <c r="F163" s="2">
+        <v>0</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -5768,22 +5730,22 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C164" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D164" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E164">
         <v>10</v>
       </c>
-      <c r="F164" s="4">
-        <v>4</v>
-      </c>
-      <c r="G164" s="5" t="s">
-        <v>29</v>
+      <c r="F164" s="2">
+        <v>0</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -5791,22 +5753,22 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C165" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D165" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E165">
         <v>20</v>
       </c>
-      <c r="F165" s="4">
-        <v>35</v>
-      </c>
-      <c r="G165" s="5" t="s">
-        <v>29</v>
+      <c r="F165" s="2">
+        <v>0</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -5814,22 +5776,22 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
+        <v>441</v>
+      </c>
+      <c r="C166" t="s">
+        <v>442</v>
+      </c>
+      <c r="D166" t="s">
         <v>443</v>
-      </c>
-      <c r="C166" t="s">
-        <v>444</v>
-      </c>
-      <c r="D166" t="s">
-        <v>445</v>
       </c>
       <c r="E166">
         <v>20</v>
       </c>
-      <c r="F166" s="4">
-        <v>62</v>
-      </c>
-      <c r="G166" s="5" t="s">
-        <v>29</v>
+      <c r="F166" s="2">
+        <v>0</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -5837,22 +5799,22 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
+        <v>444</v>
+      </c>
+      <c r="C167" t="s">
+        <v>445</v>
+      </c>
+      <c r="D167" t="s">
         <v>446</v>
-      </c>
-      <c r="C167" t="s">
-        <v>447</v>
-      </c>
-      <c r="D167" t="s">
-        <v>448</v>
       </c>
       <c r="E167">
         <v>24</v>
       </c>
-      <c r="F167" s="4">
-        <v>28</v>
-      </c>
-      <c r="G167" s="5" t="s">
-        <v>29</v>
+      <c r="F167" s="2">
+        <v>0</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -5860,22 +5822,22 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C168" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D168" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E168">
         <v>240</v>
       </c>
-      <c r="F168" s="4">
-        <v>920</v>
-      </c>
-      <c r="G168" s="5" t="s">
-        <v>29</v>
+      <c r="F168" s="2">
+        <v>0</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -5883,22 +5845,22 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C169" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D169" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E169">
         <v>240</v>
       </c>
-      <c r="F169" s="4">
-        <v>102</v>
-      </c>
-      <c r="G169" s="5" t="s">
-        <v>29</v>
+      <c r="F169" s="2">
+        <v>0</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -5906,22 +5868,22 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C170" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D170" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E170">
         <v>480</v>
       </c>
-      <c r="F170" s="4">
-        <v>211</v>
-      </c>
-      <c r="G170" s="5" t="s">
-        <v>29</v>
+      <c r="F170" s="2">
+        <v>0</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -5929,19 +5891,19 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C171" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D171" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E171">
         <v>120</v>
       </c>
       <c r="F171" s="2">
-        <v>753</v>
+        <v>0</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>10</v>
@@ -5952,22 +5914,22 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C172" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D172" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E172">
         <v>240</v>
       </c>
-      <c r="F172" s="4">
-        <v>31</v>
-      </c>
-      <c r="G172" s="5" t="s">
-        <v>29</v>
+      <c r="F172" s="2">
+        <v>0</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -5975,22 +5937,22 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C173" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D173" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E173">
         <v>240</v>
       </c>
-      <c r="F173" s="4">
-        <v>93</v>
-      </c>
-      <c r="G173" s="5" t="s">
-        <v>29</v>
+      <c r="F173" s="2">
+        <v>0</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -5998,22 +5960,22 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C174" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D174" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E174">
         <v>480</v>
       </c>
-      <c r="F174" s="4">
-        <v>378</v>
-      </c>
-      <c r="G174" s="5" t="s">
-        <v>29</v>
+      <c r="F174" s="2">
+        <v>0</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6021,22 +5983,22 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C175" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D175" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E175">
         <v>120</v>
       </c>
-      <c r="F175" s="4">
-        <v>94</v>
-      </c>
-      <c r="G175" s="5" t="s">
-        <v>29</v>
+      <c r="F175" s="2">
+        <v>0</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6044,22 +6006,22 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
+        <v>463</v>
+      </c>
+      <c r="C176" t="s">
+        <v>464</v>
+      </c>
+      <c r="D176" t="s">
         <v>465</v>
-      </c>
-      <c r="C176" t="s">
-        <v>466</v>
-      </c>
-      <c r="D176" t="s">
-        <v>467</v>
       </c>
       <c r="E176">
         <v>120</v>
       </c>
-      <c r="F176" s="4">
-        <v>103</v>
-      </c>
-      <c r="G176" s="5" t="s">
-        <v>29</v>
+      <c r="F176" s="2">
+        <v>0</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6067,22 +6029,22 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
+        <v>466</v>
+      </c>
+      <c r="C177" t="s">
+        <v>467</v>
+      </c>
+      <c r="D177" t="s">
         <v>468</v>
-      </c>
-      <c r="C177" t="s">
-        <v>469</v>
-      </c>
-      <c r="D177" t="s">
-        <v>470</v>
       </c>
       <c r="E177">
         <v>120</v>
       </c>
-      <c r="F177" s="4">
-        <v>93</v>
-      </c>
-      <c r="G177" s="5" t="s">
-        <v>29</v>
+      <c r="F177" s="2">
+        <v>0</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6090,19 +6052,19 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C178" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D178" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E178">
         <v>12</v>
       </c>
       <c r="F178" s="2">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>10</v>
@@ -6113,19 +6075,19 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C179" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D179" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E179">
         <v>12</v>
       </c>
       <c r="F179" s="2">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="G179" s="3" t="s">
         <v>10</v>
@@ -6136,22 +6098,22 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C180" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D180" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E180">
         <v>30</v>
       </c>
-      <c r="F180" s="6">
-        <v>0</v>
-      </c>
-      <c r="G180" s="7" t="s">
-        <v>38</v>
+      <c r="F180" s="2">
+        <v>0</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6159,22 +6121,22 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C181" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D181" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E181">
         <v>12</v>
       </c>
-      <c r="F181" s="4">
-        <v>4</v>
-      </c>
-      <c r="G181" s="5" t="s">
-        <v>29</v>
+      <c r="F181" s="2">
+        <v>0</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6182,22 +6144,22 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C182" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D182" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E182">
         <v>6</v>
       </c>
-      <c r="F182" s="4">
-        <v>6</v>
-      </c>
-      <c r="G182" s="5" t="s">
-        <v>29</v>
+      <c r="F182" s="2">
+        <v>0</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6205,19 +6167,19 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C183" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D183" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E183">
         <v>1</v>
       </c>
       <c r="F183" s="2">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>10</v>
@@ -6228,19 +6190,19 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C184" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D184" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E184">
         <v>20</v>
       </c>
       <c r="F184" s="2">
-        <v>3763</v>
+        <v>0</v>
       </c>
       <c r="G184" s="3" t="s">
         <v>10</v>
@@ -6251,19 +6213,19 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C185" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D185" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E185">
         <v>20</v>
       </c>
       <c r="F185" s="2">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>10</v>
@@ -6274,22 +6236,22 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C186" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D186" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E186">
         <v>20</v>
       </c>
-      <c r="F186" s="4">
-        <v>40</v>
-      </c>
-      <c r="G186" s="5" t="s">
-        <v>29</v>
+      <c r="F186" s="2">
+        <v>0</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -6297,22 +6259,22 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C187" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D187" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E187">
         <v>56</v>
       </c>
-      <c r="F187" s="4">
-        <v>20</v>
-      </c>
-      <c r="G187" s="5" t="s">
-        <v>29</v>
+      <c r="F187" s="2">
+        <v>0</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -6320,22 +6282,22 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C188" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D188" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E188">
         <v>50</v>
       </c>
-      <c r="F188" s="4">
-        <v>17</v>
-      </c>
-      <c r="G188" s="5" t="s">
-        <v>29</v>
+      <c r="F188" s="2">
+        <v>0</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -6343,19 +6305,19 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C189" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D189" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E189">
         <v>50</v>
       </c>
       <c r="F189" s="2">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>10</v>
@@ -6366,19 +6328,19 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C190" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D190" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E190">
         <v>50</v>
       </c>
       <c r="F190" s="2">
-        <v>1181</v>
+        <v>0</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>10</v>
@@ -6389,19 +6351,19 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
+        <v>495</v>
+      </c>
+      <c r="C191" t="s">
+        <v>496</v>
+      </c>
+      <c r="D191" t="s">
         <v>497</v>
-      </c>
-      <c r="C191" t="s">
-        <v>498</v>
-      </c>
-      <c r="D191" t="s">
-        <v>499</v>
       </c>
       <c r="E191">
         <v>50</v>
       </c>
       <c r="F191" s="2">
-        <v>1373</v>
+        <v>0</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>10</v>
@@ -6412,19 +6374,19 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
+        <v>498</v>
+      </c>
+      <c r="C192" t="s">
+        <v>499</v>
+      </c>
+      <c r="D192" t="s">
         <v>500</v>
-      </c>
-      <c r="C192" t="s">
-        <v>501</v>
-      </c>
-      <c r="D192" t="s">
-        <v>502</v>
       </c>
       <c r="E192">
         <v>50</v>
       </c>
       <c r="F192" s="2">
-        <v>710</v>
+        <v>0</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>10</v>
@@ -6435,19 +6397,19 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
+        <v>501</v>
+      </c>
+      <c r="C193" t="s">
+        <v>502</v>
+      </c>
+      <c r="D193" t="s">
         <v>503</v>
-      </c>
-      <c r="C193" t="s">
-        <v>504</v>
-      </c>
-      <c r="D193" t="s">
-        <v>505</v>
       </c>
       <c r="E193">
         <v>50</v>
       </c>
       <c r="F193" s="2">
-        <v>19771</v>
+        <v>0</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>10</v>
@@ -6458,19 +6420,19 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
+        <v>504</v>
+      </c>
+      <c r="C194" t="s">
+        <v>505</v>
+      </c>
+      <c r="D194" t="s">
         <v>506</v>
-      </c>
-      <c r="C194" t="s">
-        <v>507</v>
-      </c>
-      <c r="D194" t="s">
-        <v>508</v>
       </c>
       <c r="E194">
         <v>100</v>
       </c>
       <c r="F194" s="2">
-        <v>1181</v>
+        <v>0</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>10</v>
@@ -6481,19 +6443,19 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
+        <v>507</v>
+      </c>
+      <c r="C195" t="s">
+        <v>508</v>
+      </c>
+      <c r="D195" t="s">
         <v>509</v>
-      </c>
-      <c r="C195" t="s">
-        <v>510</v>
-      </c>
-      <c r="D195" t="s">
-        <v>511</v>
       </c>
       <c r="E195">
         <v>60</v>
       </c>
       <c r="F195" s="2">
-        <v>454</v>
+        <v>0</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>10</v>
@@ -6504,19 +6466,19 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C196" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D196" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E196">
         <v>100</v>
       </c>
       <c r="F196" s="2">
-        <v>880</v>
+        <v>0</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>10</v>
@@ -6527,19 +6489,19 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
+        <v>512</v>
+      </c>
+      <c r="C197" t="s">
+        <v>513</v>
+      </c>
+      <c r="D197" t="s">
         <v>514</v>
-      </c>
-      <c r="C197" t="s">
-        <v>515</v>
-      </c>
-      <c r="D197" t="s">
-        <v>516</v>
       </c>
       <c r="E197">
         <v>80</v>
       </c>
       <c r="F197" s="2">
-        <v>1247</v>
+        <v>0</v>
       </c>
       <c r="G197" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2445,7 +2445,7 @@
         <v>120</v>
       </c>
       <c r="F19" s="4">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>29</v>
@@ -2514,7 +2514,7 @@
         <v>120</v>
       </c>
       <c r="F22" s="2">
-        <v>1803</v>
+        <v>1791</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -2583,7 +2583,7 @@
         <v>120</v>
       </c>
       <c r="F25" s="4">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>29</v>
@@ -3020,7 +3020,7 @@
         <v>480</v>
       </c>
       <c r="F44" s="4">
-        <v>1090</v>
+        <v>1072</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>29</v>
@@ -3250,7 +3250,7 @@
         <v>720</v>
       </c>
       <c r="F54" s="4">
-        <v>2342</v>
+        <v>2282</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>29</v>
@@ -3319,7 +3319,7 @@
         <v>720</v>
       </c>
       <c r="F57" s="2">
-        <v>4633</v>
+        <v>4573</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3457,7 +3457,7 @@
         <v>240</v>
       </c>
       <c r="F63" s="2">
-        <v>7644</v>
+        <v>7584</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3595,7 +3595,7 @@
         <v>240</v>
       </c>
       <c r="F69" s="2">
-        <v>4170</v>
+        <v>4110</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="517">
   <si>
     <t>#</t>
   </si>
@@ -43,85 +43,91 @@
     <t>LIGAS N° 18 - 80 MM X 2 MM X 1 LBS - NATURAL - ALLEANZA</t>
   </si>
   <si>
+    <t>✓ OK</t>
+  </si>
+  <si>
+    <t>85007</t>
+  </si>
+  <si>
+    <t>7754807850063</t>
+  </si>
+  <si>
+    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - NATURAL - ALLEANZA</t>
+  </si>
+  <si>
+    <t>85768</t>
+  </si>
+  <si>
+    <t>7754807857680</t>
+  </si>
+  <si>
+    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - VERDE - ALLEANZA</t>
+  </si>
+  <si>
+    <t>85008</t>
+  </si>
+  <si>
+    <t>7754807850087</t>
+  </si>
+  <si>
+    <t>LIGAS N° 78 - 140 MM X 10 MM X 1 LBS - NATURAL - ALLEANZA</t>
+  </si>
+  <si>
+    <t>85801</t>
+  </si>
+  <si>
+    <t>7754807857024</t>
+  </si>
+  <si>
+    <t>ALFILER ALLEANZA 35 MM CAJA X 50 GR</t>
+  </si>
+  <si>
+    <t>85163</t>
+  </si>
+  <si>
+    <t>091511400595</t>
+  </si>
+  <si>
+    <t>CUCHILLA ARTE AK-1/5B</t>
+  </si>
+  <si>
+    <t>85164</t>
+  </si>
+  <si>
+    <t>091511400670</t>
+  </si>
+  <si>
+    <t>CUCHILLA ARTE AK-4</t>
+  </si>
+  <si>
+    <t>⚠ BAJO</t>
+  </si>
+  <si>
+    <t>85770</t>
+  </si>
+  <si>
+    <t>091511220292</t>
+  </si>
+  <si>
+    <t>CUCHILLA ARTE AK-5 + KB-5/30B</t>
+  </si>
+  <si>
+    <t>85868</t>
+  </si>
+  <si>
+    <t>4901165202925</t>
+  </si>
+  <si>
+    <t>CUCHILLLA ARTE AK-5 PINK</t>
+  </si>
+  <si>
+    <t>85871</t>
+  </si>
+  <si>
+    <t>CUCHILLLA DE ARTE AK-5/5B</t>
+  </si>
+  <si>
     <t>✗ AGOTADO</t>
-  </si>
-  <si>
-    <t>85007</t>
-  </si>
-  <si>
-    <t>7754807850063</t>
-  </si>
-  <si>
-    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - NATURAL - ALLEANZA</t>
-  </si>
-  <si>
-    <t>85768</t>
-  </si>
-  <si>
-    <t>7754807857680</t>
-  </si>
-  <si>
-    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - VERDE - ALLEANZA</t>
-  </si>
-  <si>
-    <t>85008</t>
-  </si>
-  <si>
-    <t>7754807850087</t>
-  </si>
-  <si>
-    <t>LIGAS N° 78 - 140 MM X 10 MM X 1 LBS - NATURAL - ALLEANZA</t>
-  </si>
-  <si>
-    <t>85801</t>
-  </si>
-  <si>
-    <t>7754807857024</t>
-  </si>
-  <si>
-    <t>ALFILER ALLEANZA 35 MM CAJA X 50 GR</t>
-  </si>
-  <si>
-    <t>85163</t>
-  </si>
-  <si>
-    <t>091511400595</t>
-  </si>
-  <si>
-    <t>CUCHILLA ARTE AK-1/5B</t>
-  </si>
-  <si>
-    <t>85164</t>
-  </si>
-  <si>
-    <t>091511400670</t>
-  </si>
-  <si>
-    <t>CUCHILLA ARTE AK-4</t>
-  </si>
-  <si>
-    <t>85770</t>
-  </si>
-  <si>
-    <t>091511220292</t>
-  </si>
-  <si>
-    <t>CUCHILLA ARTE AK-5 + KB-5/30B</t>
-  </si>
-  <si>
-    <t>85868</t>
-  </si>
-  <si>
-    <t>4901165202925</t>
-  </si>
-  <si>
-    <t>CUCHILLLA ARTE AK-5 PINK</t>
-  </si>
-  <si>
-    <t>85871</t>
-  </si>
-  <si>
-    <t>CUCHILLLA DE ARTE AK-5/5B</t>
   </si>
   <si>
     <t>85166</t>
@@ -1562,7 +1568,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1581,11 +1587,21 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF065F46"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFD97706"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFDC2626"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1595,6 +1611,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF13DAEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -1615,7 +1641,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1624,6 +1650,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2016,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>5415</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2039,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>0</v>
+        <v>25558</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2062,7 +2100,7 @@
         <v>80</v>
       </c>
       <c r="F4" s="2">
-        <v>0</v>
+        <v>7881</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -2085,7 +2123,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>0</v>
+        <v>19989</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2108,7 +2146,7 @@
         <v>200</v>
       </c>
       <c r="F6" s="2">
-        <v>0</v>
+        <v>36463</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -2131,7 +2169,7 @@
         <v>120</v>
       </c>
       <c r="F7" s="2">
-        <v>0</v>
+        <v>1027</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -2153,11 +2191,11 @@
       <c r="E8">
         <v>120</v>
       </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
+      <c r="F8" s="4">
+        <v>268</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2165,22 +2203,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9">
         <v>240</v>
       </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
+      <c r="F9" s="4">
+        <v>253</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2188,22 +2226,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E10">
         <v>200</v>
       </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>10</v>
+      <c r="F10" s="4">
+        <v>59</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2211,22 +2249,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>240</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="6">
         <v>0</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>10</v>
+      <c r="G11" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2234,22 +2272,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E12">
         <v>60</v>
       </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
+      <c r="F12" s="4">
+        <v>132</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2257,22 +2295,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E13">
         <v>120</v>
       </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
+      <c r="F13" s="4">
+        <v>191</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2280,22 +2318,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E14">
         <v>120</v>
       </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="F14" s="4">
+        <v>189</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2303,22 +2341,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E15">
         <v>120</v>
       </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>10</v>
+      <c r="F15" s="4">
+        <v>84</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2326,19 +2364,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E16">
         <v>120</v>
       </c>
       <c r="F16" s="2">
-        <v>0</v>
+        <v>692</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -2349,22 +2387,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E17">
         <v>120</v>
       </c>
-      <c r="F17" s="2">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>10</v>
+      <c r="F17" s="4">
+        <v>257</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2372,19 +2410,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E18">
         <v>120</v>
       </c>
       <c r="F18" s="2">
-        <v>0</v>
+        <v>983</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -2395,22 +2433,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E19">
         <v>120</v>
       </c>
-      <c r="F19" s="2">
-        <v>0</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>10</v>
+      <c r="F19" s="4">
+        <v>177</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2418,22 +2456,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E20">
         <v>120</v>
       </c>
-      <c r="F20" s="2">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>10</v>
+      <c r="F20" s="4">
+        <v>75</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2441,22 +2479,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E21">
         <v>120</v>
       </c>
-      <c r="F21" s="2">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>10</v>
+      <c r="F21" s="4">
+        <v>421</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2464,19 +2502,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E22">
         <v>120</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>1791</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -2487,22 +2525,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E23">
         <v>60</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="6">
         <v>0</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>10</v>
+      <c r="G23" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2510,22 +2548,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E24">
         <v>120</v>
       </c>
-      <c r="F24" s="2">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>10</v>
+      <c r="F24" s="4">
+        <v>113</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2533,22 +2571,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E25">
         <v>120</v>
       </c>
-      <c r="F25" s="2">
-        <v>0</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>10</v>
+      <c r="F25" s="4">
+        <v>342</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2556,22 +2594,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E26">
         <v>120</v>
       </c>
-      <c r="F26" s="2">
-        <v>0</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>10</v>
+      <c r="F26" s="4">
+        <v>123</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2579,22 +2617,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E27">
         <v>120</v>
       </c>
-      <c r="F27" s="2">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>10</v>
+      <c r="F27" s="4">
+        <v>160</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2602,19 +2640,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E28">
         <v>120</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>8444</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -2625,22 +2663,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E29">
         <v>72</v>
       </c>
-      <c r="F29" s="2">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>10</v>
+      <c r="F29" s="4">
+        <v>94</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2648,22 +2686,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D30" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E30">
         <v>120</v>
       </c>
-      <c r="F30" s="2">
-        <v>0</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>10</v>
+      <c r="F30" s="4">
+        <v>56</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2671,19 +2709,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D31" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E31">
         <v>120</v>
       </c>
       <c r="F31" s="2">
-        <v>0</v>
+        <v>2820</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -2694,19 +2732,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E32">
         <v>120</v>
       </c>
       <c r="F32" s="2">
-        <v>0</v>
+        <v>1445</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -2717,22 +2755,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E33">
         <v>144</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="6">
         <v>0</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>10</v>
+      <c r="G33" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2740,19 +2778,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E34">
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -2763,22 +2801,22 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C35" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D35" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E35">
         <v>128</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="6">
         <v>0</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>10</v>
+      <c r="G35" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2786,22 +2824,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D36" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E36">
         <v>120</v>
       </c>
-      <c r="F36" s="2">
-        <v>0</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>10</v>
+      <c r="F36" s="4">
+        <v>118</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2809,22 +2847,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C37" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D37" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E37">
         <v>240</v>
       </c>
-      <c r="F37" s="2">
-        <v>0</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>10</v>
+      <c r="F37" s="4">
+        <v>944</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2832,22 +2870,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C38" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D38" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E38">
         <v>120</v>
       </c>
-      <c r="F38" s="2">
-        <v>0</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>10</v>
+      <c r="F38" s="4">
+        <v>123</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2855,22 +2893,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C39" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D39" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E39">
         <v>240</v>
       </c>
-      <c r="F39" s="2">
-        <v>0</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>10</v>
+      <c r="F39" s="4">
+        <v>254</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2878,22 +2916,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C40" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D40" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E40">
         <v>240</v>
       </c>
-      <c r="F40" s="2">
-        <v>0</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>10</v>
+      <c r="F40" s="4">
+        <v>245</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2901,22 +2939,22 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C41" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D41" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E41">
         <v>240</v>
       </c>
-      <c r="F41" s="2">
-        <v>0</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>10</v>
+      <c r="F41" s="4">
+        <v>107</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2924,22 +2962,22 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C42" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D42" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E42">
         <v>240</v>
       </c>
-      <c r="F42" s="2">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>10</v>
+      <c r="F42" s="4">
+        <v>273</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2947,19 +2985,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C43" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D43" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E43">
         <v>240</v>
       </c>
       <c r="F43" s="2">
-        <v>0</v>
+        <v>2865</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>10</v>
@@ -2970,22 +3008,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C44" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D44" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E44">
         <v>480</v>
       </c>
-      <c r="F44" s="2">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>10</v>
+      <c r="F44" s="4">
+        <v>1072</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -2993,22 +3031,22 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C45" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D45" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E45">
         <v>240</v>
       </c>
-      <c r="F45" s="2">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>10</v>
+      <c r="F45" s="4">
+        <v>163</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3016,22 +3054,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C46" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D46" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E46">
         <v>800</v>
       </c>
-      <c r="F46" s="2">
-        <v>0</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>10</v>
+      <c r="F46" s="4">
+        <v>1475</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3039,22 +3077,22 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C47" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D47" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E47">
         <v>240</v>
       </c>
-      <c r="F47" s="2">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>10</v>
+      <c r="F47" s="4">
+        <v>164</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3062,22 +3100,22 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C48" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D48" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E48">
         <v>120</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="6">
         <v>0</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>10</v>
+      <c r="G48" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3085,22 +3123,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C49" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D49" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E49">
         <v>120</v>
       </c>
-      <c r="F49" s="2">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>10</v>
+      <c r="F49" s="4">
+        <v>261</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3108,22 +3146,22 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C50" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D50" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E50">
         <v>120</v>
       </c>
-      <c r="F50" s="2">
-        <v>0</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>10</v>
+      <c r="F50" s="4">
+        <v>291</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3131,22 +3169,22 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C51" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D51" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E51">
         <v>10</v>
       </c>
-      <c r="F51" s="2">
-        <v>0</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>10</v>
+      <c r="F51" s="4">
+        <v>10</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3154,22 +3192,22 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C52" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D52" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E52">
         <v>60</v>
       </c>
-      <c r="F52" s="2">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>10</v>
+      <c r="F52" s="4">
+        <v>82</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3177,22 +3215,22 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C53" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D53" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E53">
         <v>20</v>
       </c>
-      <c r="F53" s="2">
-        <v>0</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>10</v>
+      <c r="F53" s="4">
+        <v>27</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3200,22 +3238,22 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C54" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D54" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E54">
         <v>720</v>
       </c>
-      <c r="F54" s="2">
-        <v>0</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>10</v>
+      <c r="F54" s="4">
+        <v>2282</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3223,22 +3261,22 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C55" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D55" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E55">
         <v>120</v>
       </c>
-      <c r="F55" s="2">
-        <v>0</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>10</v>
+      <c r="F55" s="4">
+        <v>178</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -3246,22 +3284,22 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C56" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D56" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E56">
         <v>120</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="6">
         <v>0</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>10</v>
+      <c r="G56" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3269,19 +3307,19 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C57" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D57" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E57">
         <v>720</v>
       </c>
       <c r="F57" s="2">
-        <v>0</v>
+        <v>4573</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3292,22 +3330,22 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C58" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D58" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E58">
         <v>240</v>
       </c>
-      <c r="F58" s="2">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>10</v>
+      <c r="F58" s="4">
+        <v>201</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3315,22 +3353,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C59" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D59" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E59">
         <v>120</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="6">
         <v>0</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>10</v>
+      <c r="G59" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3338,22 +3376,22 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C60" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D60" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E60">
         <v>240</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="6">
         <v>0</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>10</v>
+      <c r="G60" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3361,22 +3399,22 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C61" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D61" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E61">
         <v>240</v>
       </c>
-      <c r="F61" s="2">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>10</v>
+      <c r="F61" s="4">
+        <v>300</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3384,22 +3422,22 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C62" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D62" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E62">
         <v>240</v>
       </c>
-      <c r="F62" s="2">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>10</v>
+      <c r="F62" s="4">
+        <v>198</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3407,19 +3445,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C63" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D63" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E63">
         <v>240</v>
       </c>
       <c r="F63" s="2">
-        <v>0</v>
+        <v>7584</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3430,19 +3468,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C64" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D64" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E64">
         <v>60</v>
       </c>
       <c r="F64" s="2">
-        <v>0</v>
+        <v>489</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>10</v>
@@ -3453,22 +3491,22 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C65" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D65" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E65">
         <v>60</v>
       </c>
-      <c r="F65" s="2">
-        <v>0</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>10</v>
+      <c r="F65" s="4">
+        <v>65</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3476,22 +3514,22 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C66" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D66" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E66">
         <v>120</v>
       </c>
-      <c r="F66" s="2">
-        <v>0</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>10</v>
+      <c r="F66" s="4">
+        <v>69</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3499,22 +3537,22 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C67" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D67" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E67">
         <v>240</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="6">
         <v>0</v>
       </c>
-      <c r="G67" s="3" t="s">
-        <v>10</v>
+      <c r="G67" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3522,22 +3560,22 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C68" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D68" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E68">
         <v>240</v>
       </c>
-      <c r="F68" s="2">
-        <v>0</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>10</v>
+      <c r="F68" s="4">
+        <v>55</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3545,19 +3583,19 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C69" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D69" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E69">
         <v>240</v>
       </c>
       <c r="F69" s="2">
-        <v>0</v>
+        <v>4110</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -3568,22 +3606,22 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C70" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D70" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E70">
         <v>240</v>
       </c>
-      <c r="F70" s="2">
-        <v>0</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>10</v>
+      <c r="F70" s="4">
+        <v>130</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3591,22 +3629,22 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C71" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D71" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E71">
         <v>240</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="6">
         <v>0</v>
       </c>
-      <c r="G71" s="3" t="s">
-        <v>10</v>
+      <c r="G71" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3614,22 +3652,22 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C72" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D72" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E72">
         <v>480</v>
       </c>
-      <c r="F72" s="2">
-        <v>0</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>10</v>
+      <c r="F72" s="4">
+        <v>412</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3637,22 +3675,22 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C73" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D73" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E73">
         <v>240</v>
       </c>
-      <c r="F73" s="2">
-        <v>0</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>10</v>
+      <c r="F73" s="4">
+        <v>500</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3660,19 +3698,19 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C74" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D74" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E74">
         <v>240</v>
       </c>
       <c r="F74" s="2">
-        <v>0</v>
+        <v>1356</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -3683,19 +3721,19 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C75" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D75" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E75">
         <v>240</v>
       </c>
       <c r="F75" s="2">
-        <v>0</v>
+        <v>4001</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -3706,22 +3744,22 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C76" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D76" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E76">
         <v>240</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="6">
         <v>0</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>10</v>
+      <c r="G76" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -3729,22 +3767,22 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C77" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D77" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E77">
         <v>600</v>
       </c>
-      <c r="F77" s="2">
-        <v>0</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>10</v>
+      <c r="F77" s="4">
+        <v>529</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -3752,22 +3790,22 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C78" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D78" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E78">
         <v>120</v>
       </c>
-      <c r="F78" s="2">
-        <v>0</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>10</v>
+      <c r="F78" s="4">
+        <v>114</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -3775,22 +3813,22 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C79" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D79" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E79">
         <v>120</v>
       </c>
-      <c r="F79" s="2">
-        <v>0</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>10</v>
+      <c r="F79" s="4">
+        <v>4</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3798,22 +3836,22 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C80" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D80" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E80">
         <v>60</v>
       </c>
-      <c r="F80" s="2">
-        <v>0</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>10</v>
+      <c r="F80" s="4">
+        <v>12</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3821,19 +3859,19 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C81" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D81" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E81">
         <v>20</v>
       </c>
       <c r="F81" s="2">
-        <v>0</v>
+        <v>469</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>10</v>
@@ -3844,19 +3882,19 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C82" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D82" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E82">
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>0</v>
+        <v>1938</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -3867,22 +3905,22 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C83" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D83" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E83">
         <v>40</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83" s="6">
         <v>0</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>10</v>
+      <c r="G83" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -3890,22 +3928,22 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C84" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D84" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E84">
         <v>40</v>
       </c>
-      <c r="F84" s="2">
-        <v>0</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>10</v>
+      <c r="F84" s="4">
+        <v>80</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -3913,22 +3951,22 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C85" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D85" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E85">
         <v>40</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="6">
         <v>0</v>
       </c>
-      <c r="G85" s="3" t="s">
-        <v>10</v>
+      <c r="G85" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -3936,22 +3974,22 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C86" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D86" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E86">
         <v>40</v>
       </c>
-      <c r="F86" s="2">
+      <c r="F86" s="6">
         <v>0</v>
       </c>
-      <c r="G86" s="3" t="s">
-        <v>10</v>
+      <c r="G86" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -3959,22 +3997,22 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C87" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D87" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E87">
         <v>40</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="6">
         <v>0</v>
       </c>
-      <c r="G87" s="3" t="s">
-        <v>10</v>
+      <c r="G87" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -3982,22 +4020,22 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E88">
         <v>20</v>
       </c>
-      <c r="F88" s="2">
-        <v>0</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>10</v>
+      <c r="F88" s="4">
+        <v>10</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4005,19 +4043,19 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C89" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D89" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E89">
         <v>20</v>
       </c>
       <c r="F89" s="2">
-        <v>0</v>
+        <v>1473</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>10</v>
@@ -4028,19 +4066,19 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C90" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D90" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E90">
         <v>100</v>
       </c>
       <c r="F90" s="2">
-        <v>0</v>
+        <v>107521</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -4051,19 +4089,19 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C91" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D91" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E91">
         <v>10</v>
       </c>
       <c r="F91" s="2">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -4074,19 +4112,19 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C92" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D92" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E92">
         <v>10</v>
       </c>
       <c r="F92" s="2">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -4097,19 +4135,19 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C93" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D93" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E93">
         <v>2</v>
       </c>
       <c r="F93" s="2">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -4120,19 +4158,19 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C94" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D94" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E94">
         <v>6</v>
       </c>
       <c r="F94" s="2">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4143,22 +4181,22 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C95" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D95" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E95">
         <v>120</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="6">
         <v>0</v>
       </c>
-      <c r="G95" s="3" t="s">
-        <v>10</v>
+      <c r="G95" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4166,22 +4204,22 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C96" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D96" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E96">
         <v>120</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="6">
         <v>0</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>10</v>
+      <c r="G96" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -4189,22 +4227,22 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C97" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D97" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E97">
         <v>10</v>
       </c>
-      <c r="F97" s="2">
-        <v>0</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>10</v>
+      <c r="F97" s="4">
+        <v>7</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4212,22 +4250,22 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C98" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D98" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E98">
         <v>5</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F98" s="6">
         <v>0</v>
       </c>
-      <c r="G98" s="3" t="s">
-        <v>10</v>
+      <c r="G98" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4235,22 +4273,22 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C99" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D99" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E99">
         <v>5</v>
       </c>
-      <c r="F99" s="2">
+      <c r="F99" s="6">
         <v>0</v>
       </c>
-      <c r="G99" s="3" t="s">
-        <v>10</v>
+      <c r="G99" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -4258,19 +4296,19 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C100" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D100" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E100">
         <v>6</v>
       </c>
       <c r="F100" s="2">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -4281,19 +4319,19 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C101" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D101" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E101">
         <v>6</v>
       </c>
       <c r="F101" s="2">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>10</v>
@@ -4304,19 +4342,19 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C102" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D102" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E102">
         <v>6</v>
       </c>
       <c r="F102" s="2">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>10</v>
@@ -4327,19 +4365,19 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C103" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D103" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E103">
         <v>6</v>
       </c>
       <c r="F103" s="2">
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="G103" s="3" t="s">
         <v>10</v>
@@ -4350,22 +4388,22 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C104" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D104" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E104">
         <v>200</v>
       </c>
-      <c r="F104" s="2">
-        <v>0</v>
-      </c>
-      <c r="G104" s="3" t="s">
-        <v>10</v>
+      <c r="F104" s="4">
+        <v>4</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -4373,19 +4411,19 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C105" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D105" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E105">
         <v>56</v>
       </c>
       <c r="F105" s="2">
-        <v>0</v>
+        <v>354</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>10</v>
@@ -4396,22 +4434,22 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C106" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D106" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E106">
         <v>120</v>
       </c>
-      <c r="F106" s="2">
-        <v>0</v>
-      </c>
-      <c r="G106" s="3" t="s">
-        <v>10</v>
+      <c r="F106" s="4">
+        <v>15</v>
+      </c>
+      <c r="G106" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4419,22 +4457,22 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C107" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D107" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E107">
         <v>120</v>
       </c>
-      <c r="F107" s="2">
-        <v>0</v>
-      </c>
-      <c r="G107" s="3" t="s">
-        <v>10</v>
+      <c r="F107" s="4">
+        <v>1</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -4442,22 +4480,22 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C108" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D108" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E108">
         <v>18</v>
       </c>
-      <c r="F108" s="2">
-        <v>0</v>
-      </c>
-      <c r="G108" s="3" t="s">
-        <v>10</v>
+      <c r="F108" s="4">
+        <v>79</v>
+      </c>
+      <c r="G108" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -4465,22 +4503,22 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C109" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D109" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E109">
         <v>6</v>
       </c>
-      <c r="F109" s="2">
+      <c r="F109" s="6">
         <v>0</v>
       </c>
-      <c r="G109" s="3" t="s">
-        <v>10</v>
+      <c r="G109" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -4488,22 +4526,22 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C110" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D110" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E110">
         <v>54</v>
       </c>
-      <c r="F110" s="2">
-        <v>0</v>
-      </c>
-      <c r="G110" s="3" t="s">
-        <v>10</v>
+      <c r="F110" s="4">
+        <v>93</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -4511,22 +4549,22 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C111" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D111" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E111">
         <v>10</v>
       </c>
-      <c r="F111" s="2">
+      <c r="F111" s="6">
         <v>0</v>
       </c>
-      <c r="G111" s="3" t="s">
-        <v>10</v>
+      <c r="G111" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -4534,22 +4572,22 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C112" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D112" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E112">
         <v>12</v>
       </c>
-      <c r="F112" s="2">
+      <c r="F112" s="6">
         <v>0</v>
       </c>
-      <c r="G112" s="3" t="s">
-        <v>10</v>
+      <c r="G112" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -4557,22 +4595,22 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C113" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D113" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E113">
         <v>12</v>
       </c>
-      <c r="F113" s="2">
+      <c r="F113" s="6">
         <v>0</v>
       </c>
-      <c r="G113" s="3" t="s">
-        <v>10</v>
+      <c r="G113" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -4580,19 +4618,19 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C114" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D114" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E114">
         <v>5</v>
       </c>
       <c r="F114" s="2">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -4603,22 +4641,22 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C115" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D115" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E115">
         <v>800</v>
       </c>
-      <c r="F115" s="2">
-        <v>0</v>
-      </c>
-      <c r="G115" s="3" t="s">
-        <v>10</v>
+      <c r="F115" s="4">
+        <v>312</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -4626,22 +4664,22 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C116" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D116" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E116">
         <v>5</v>
       </c>
-      <c r="F116" s="2">
+      <c r="F116" s="6">
         <v>0</v>
       </c>
-      <c r="G116" s="3" t="s">
-        <v>10</v>
+      <c r="G116" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -4649,22 +4687,22 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C117" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D117" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E117">
         <v>5</v>
       </c>
-      <c r="F117" s="2">
-        <v>0</v>
-      </c>
-      <c r="G117" s="3" t="s">
-        <v>10</v>
+      <c r="F117" s="4">
+        <v>2</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -4672,19 +4710,19 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C118" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D118" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E118">
         <v>10</v>
       </c>
       <c r="F118" s="2">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>10</v>
@@ -4695,22 +4733,22 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C119" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D119" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E119">
         <v>10</v>
       </c>
-      <c r="F119" s="2">
-        <v>0</v>
-      </c>
-      <c r="G119" s="3" t="s">
-        <v>10</v>
+      <c r="F119" s="4">
+        <v>6</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -4718,22 +4756,22 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C120" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D120" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E120">
         <v>10</v>
       </c>
-      <c r="F120" s="2">
-        <v>0</v>
-      </c>
-      <c r="G120" s="3" t="s">
-        <v>10</v>
+      <c r="F120" s="4">
+        <v>36</v>
+      </c>
+      <c r="G120" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -4741,22 +4779,22 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C121" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D121" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E121">
         <v>6</v>
       </c>
-      <c r="F121" s="2">
+      <c r="F121" s="6">
         <v>0</v>
       </c>
-      <c r="G121" s="3" t="s">
-        <v>10</v>
+      <c r="G121" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -4764,22 +4802,22 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C122" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D122" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E122">
         <v>6</v>
       </c>
-      <c r="F122" s="2">
+      <c r="F122" s="6">
         <v>0</v>
       </c>
-      <c r="G122" s="3" t="s">
-        <v>10</v>
+      <c r="G122" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -4787,22 +4825,22 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C123" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D123" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E123">
         <v>40</v>
       </c>
-      <c r="F123" s="2">
-        <v>0</v>
-      </c>
-      <c r="G123" s="3" t="s">
-        <v>10</v>
+      <c r="F123" s="4">
+        <v>127</v>
+      </c>
+      <c r="G123" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -4810,19 +4848,19 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C124" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D124" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E124">
         <v>4</v>
       </c>
       <c r="F124" s="2">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>10</v>
@@ -4833,22 +4871,22 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C125" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D125" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E125">
         <v>1</v>
       </c>
-      <c r="F125" s="2">
+      <c r="F125" s="6">
         <v>0</v>
       </c>
-      <c r="G125" s="3" t="s">
-        <v>10</v>
+      <c r="G125" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -4856,22 +4894,22 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C126" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D126" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E126">
         <v>4</v>
       </c>
-      <c r="F126" s="2">
-        <v>0</v>
-      </c>
-      <c r="G126" s="3" t="s">
-        <v>10</v>
+      <c r="F126" s="4">
+        <v>17</v>
+      </c>
+      <c r="G126" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -4879,19 +4917,19 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C127" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D127" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E127">
         <v>4</v>
       </c>
       <c r="F127" s="2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>10</v>
@@ -4902,22 +4940,22 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C128" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D128" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E128">
         <v>4</v>
       </c>
-      <c r="F128" s="2">
-        <v>0</v>
-      </c>
-      <c r="G128" s="3" t="s">
-        <v>10</v>
+      <c r="F128" s="4">
+        <v>18</v>
+      </c>
+      <c r="G128" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -4925,22 +4963,22 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C129" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D129" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E129">
         <v>1</v>
       </c>
-      <c r="F129" s="2">
-        <v>0</v>
-      </c>
-      <c r="G129" s="3" t="s">
-        <v>10</v>
+      <c r="F129" s="4">
+        <v>4</v>
+      </c>
+      <c r="G129" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -4948,22 +4986,22 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C130" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D130" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E130">
         <v>60</v>
       </c>
-      <c r="F130" s="2">
-        <v>0</v>
-      </c>
-      <c r="G130" s="3" t="s">
-        <v>10</v>
+      <c r="F130" s="4">
+        <v>3</v>
+      </c>
+      <c r="G130" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -4971,19 +5009,19 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C131" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D131" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E131">
         <v>60</v>
       </c>
       <c r="F131" s="2">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>10</v>
@@ -4994,22 +5032,22 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C132" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D132" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E132">
         <v>60</v>
       </c>
-      <c r="F132" s="2">
-        <v>0</v>
-      </c>
-      <c r="G132" s="3" t="s">
-        <v>10</v>
+      <c r="F132" s="4">
+        <v>58</v>
+      </c>
+      <c r="G132" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5017,22 +5055,22 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C133" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D133" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E133">
         <v>60</v>
       </c>
-      <c r="F133" s="2">
-        <v>0</v>
-      </c>
-      <c r="G133" s="3" t="s">
-        <v>10</v>
+      <c r="F133" s="4">
+        <v>138</v>
+      </c>
+      <c r="G133" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5040,19 +5078,19 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C134" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D134" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E134">
         <v>60</v>
       </c>
       <c r="F134" s="2">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>10</v>
@@ -5063,19 +5101,19 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C135" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D135" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E135">
         <v>60</v>
       </c>
       <c r="F135" s="2">
-        <v>0</v>
+        <v>521</v>
       </c>
       <c r="G135" s="3" t="s">
         <v>10</v>
@@ -5086,19 +5124,19 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C136" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D136" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E136">
         <v>60</v>
       </c>
       <c r="F136" s="2">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>10</v>
@@ -5109,19 +5147,19 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C137" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D137" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E137">
         <v>30</v>
       </c>
       <c r="F137" s="2">
-        <v>0</v>
+        <v>1601</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>10</v>
@@ -5132,19 +5170,19 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C138" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D138" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E138">
         <v>40</v>
       </c>
       <c r="F138" s="2">
-        <v>0</v>
+        <v>1130</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>10</v>
@@ -5155,19 +5193,19 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C139" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D139" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E139">
         <v>63</v>
       </c>
       <c r="F139" s="2">
-        <v>0</v>
+        <v>566</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>10</v>
@@ -5178,19 +5216,19 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C140" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D140" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E140">
         <v>10</v>
       </c>
       <c r="F140" s="2">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>10</v>
@@ -5201,22 +5239,22 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C141" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D141" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E141">
         <v>40</v>
       </c>
-      <c r="F141" s="2">
-        <v>0</v>
-      </c>
-      <c r="G141" s="3" t="s">
-        <v>10</v>
+      <c r="F141" s="4">
+        <v>108</v>
+      </c>
+      <c r="G141" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -5224,22 +5262,22 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C142" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D142" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E142">
         <v>60</v>
       </c>
-      <c r="F142" s="2">
-        <v>0</v>
-      </c>
-      <c r="G142" s="3" t="s">
-        <v>10</v>
+      <c r="F142" s="4">
+        <v>122</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -5247,22 +5285,22 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C143" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D143" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E143">
         <v>6</v>
       </c>
-      <c r="F143" s="2">
-        <v>0</v>
-      </c>
-      <c r="G143" s="3" t="s">
-        <v>10</v>
+      <c r="F143" s="4">
+        <v>15</v>
+      </c>
+      <c r="G143" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -5270,22 +5308,22 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C144" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D144" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E144">
         <v>18</v>
       </c>
-      <c r="F144" s="2">
+      <c r="F144" s="6">
         <v>0</v>
       </c>
-      <c r="G144" s="3" t="s">
-        <v>10</v>
+      <c r="G144" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -5293,22 +5331,22 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C145" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D145" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E145">
         <v>8</v>
       </c>
-      <c r="F145" s="2">
-        <v>0</v>
-      </c>
-      <c r="G145" s="3" t="s">
-        <v>10</v>
+      <c r="F145" s="4">
+        <v>10</v>
+      </c>
+      <c r="G145" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -5316,22 +5354,22 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C146" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D146" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E146">
         <v>30</v>
       </c>
-      <c r="F146" s="2">
-        <v>0</v>
-      </c>
-      <c r="G146" s="3" t="s">
-        <v>10</v>
+      <c r="F146" s="4">
+        <v>34</v>
+      </c>
+      <c r="G146" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -5339,22 +5377,22 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C147" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D147" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E147">
         <v>2</v>
       </c>
-      <c r="F147" s="2">
+      <c r="F147" s="6">
         <v>0</v>
       </c>
-      <c r="G147" s="3" t="s">
-        <v>10</v>
+      <c r="G147" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -5362,19 +5400,19 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C148" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D148" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E148">
         <v>5</v>
       </c>
       <c r="F148" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G148" s="3" t="s">
         <v>10</v>
@@ -5385,19 +5423,19 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C149" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D149" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E149">
         <v>5</v>
       </c>
       <c r="F149" s="2">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="G149" s="3" t="s">
         <v>10</v>
@@ -5408,19 +5446,19 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C150" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D150" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E150">
         <v>5</v>
       </c>
       <c r="F150" s="2">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>10</v>
@@ -5431,19 +5469,19 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C151" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D151" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E151">
         <v>5</v>
       </c>
       <c r="F151" s="2">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>10</v>
@@ -5454,22 +5492,22 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C152" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D152" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E152">
         <v>20</v>
       </c>
-      <c r="F152" s="2">
-        <v>0</v>
-      </c>
-      <c r="G152" s="3" t="s">
-        <v>10</v>
+      <c r="F152" s="4">
+        <v>8</v>
+      </c>
+      <c r="G152" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -5477,22 +5515,22 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C153" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D153" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E153">
         <v>240</v>
       </c>
-      <c r="F153" s="2">
-        <v>0</v>
-      </c>
-      <c r="G153" s="3" t="s">
-        <v>10</v>
+      <c r="F153" s="4">
+        <v>640</v>
+      </c>
+      <c r="G153" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -5500,22 +5538,22 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C154" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D154" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E154">
         <v>120</v>
       </c>
-      <c r="F154" s="2">
-        <v>0</v>
-      </c>
-      <c r="G154" s="3" t="s">
-        <v>10</v>
+      <c r="F154" s="4">
+        <v>121</v>
+      </c>
+      <c r="G154" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -5523,19 +5561,19 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C155" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E155">
         <v>60</v>
       </c>
       <c r="F155" s="2">
-        <v>0</v>
+        <v>855</v>
       </c>
       <c r="G155" s="3" t="s">
         <v>10</v>
@@ -5546,22 +5584,22 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C156" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E156">
         <v>120</v>
       </c>
-      <c r="F156" s="2">
+      <c r="F156" s="6">
         <v>0</v>
       </c>
-      <c r="G156" s="3" t="s">
-        <v>10</v>
+      <c r="G156" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -5569,22 +5607,22 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C157" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D157" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E157">
         <v>72</v>
       </c>
-      <c r="F157" s="2">
-        <v>0</v>
-      </c>
-      <c r="G157" s="3" t="s">
-        <v>10</v>
+      <c r="F157" s="4">
+        <v>63</v>
+      </c>
+      <c r="G157" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -5592,22 +5630,22 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C158" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D158" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E158">
         <v>60</v>
       </c>
-      <c r="F158" s="2">
-        <v>0</v>
-      </c>
-      <c r="G158" s="3" t="s">
-        <v>10</v>
+      <c r="F158" s="4">
+        <v>30</v>
+      </c>
+      <c r="G158" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5615,22 +5653,22 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C159" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D159" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E159">
         <v>120</v>
       </c>
-      <c r="F159" s="2">
-        <v>0</v>
-      </c>
-      <c r="G159" s="3" t="s">
-        <v>10</v>
+      <c r="F159" s="4">
+        <v>83</v>
+      </c>
+      <c r="G159" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -5638,22 +5676,22 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C160" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D160" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E160">
         <v>72</v>
       </c>
-      <c r="F160" s="2">
-        <v>0</v>
-      </c>
-      <c r="G160" s="3" t="s">
-        <v>10</v>
+      <c r="F160" s="4">
+        <v>10</v>
+      </c>
+      <c r="G160" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5661,22 +5699,22 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C161" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D161" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E161">
         <v>20</v>
       </c>
-      <c r="F161" s="2">
-        <v>0</v>
-      </c>
-      <c r="G161" s="3" t="s">
-        <v>10</v>
+      <c r="F161" s="4">
+        <v>51</v>
+      </c>
+      <c r="G161" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5684,22 +5722,22 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C162" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D162" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E162">
         <v>100</v>
       </c>
-      <c r="F162" s="2">
-        <v>0</v>
-      </c>
-      <c r="G162" s="3" t="s">
-        <v>10</v>
+      <c r="F162" s="4">
+        <v>74</v>
+      </c>
+      <c r="G162" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -5707,22 +5745,22 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C163" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D163" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E163">
         <v>5</v>
       </c>
-      <c r="F163" s="2">
-        <v>0</v>
-      </c>
-      <c r="G163" s="3" t="s">
-        <v>10</v>
+      <c r="F163" s="4">
+        <v>11</v>
+      </c>
+      <c r="G163" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -5730,22 +5768,22 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C164" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D164" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E164">
         <v>10</v>
       </c>
-      <c r="F164" s="2">
-        <v>0</v>
-      </c>
-      <c r="G164" s="3" t="s">
-        <v>10</v>
+      <c r="F164" s="4">
+        <v>4</v>
+      </c>
+      <c r="G164" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -5753,22 +5791,22 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C165" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D165" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E165">
         <v>20</v>
       </c>
-      <c r="F165" s="2">
-        <v>0</v>
-      </c>
-      <c r="G165" s="3" t="s">
-        <v>10</v>
+      <c r="F165" s="4">
+        <v>35</v>
+      </c>
+      <c r="G165" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -5776,22 +5814,22 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C166" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D166" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E166">
         <v>20</v>
       </c>
-      <c r="F166" s="2">
-        <v>0</v>
-      </c>
-      <c r="G166" s="3" t="s">
-        <v>10</v>
+      <c r="F166" s="4">
+        <v>57</v>
+      </c>
+      <c r="G166" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -5799,22 +5837,22 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C167" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D167" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E167">
         <v>24</v>
       </c>
-      <c r="F167" s="2">
-        <v>0</v>
-      </c>
-      <c r="G167" s="3" t="s">
-        <v>10</v>
+      <c r="F167" s="4">
+        <v>28</v>
+      </c>
+      <c r="G167" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -5822,22 +5860,22 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C168" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D168" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E168">
         <v>240</v>
       </c>
-      <c r="F168" s="2">
-        <v>0</v>
-      </c>
-      <c r="G168" s="3" t="s">
-        <v>10</v>
+      <c r="F168" s="4">
+        <v>920</v>
+      </c>
+      <c r="G168" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -5845,22 +5883,22 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C169" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D169" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E169">
         <v>240</v>
       </c>
-      <c r="F169" s="2">
-        <v>0</v>
-      </c>
-      <c r="G169" s="3" t="s">
-        <v>10</v>
+      <c r="F169" s="4">
+        <v>102</v>
+      </c>
+      <c r="G169" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -5868,22 +5906,22 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C170" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D170" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E170">
         <v>480</v>
       </c>
-      <c r="F170" s="2">
-        <v>0</v>
-      </c>
-      <c r="G170" s="3" t="s">
-        <v>10</v>
+      <c r="F170" s="4">
+        <v>211</v>
+      </c>
+      <c r="G170" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -5891,19 +5929,19 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C171" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D171" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E171">
         <v>120</v>
       </c>
       <c r="F171" s="2">
-        <v>0</v>
+        <v>753</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>10</v>
@@ -5914,22 +5952,22 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C172" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D172" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E172">
         <v>240</v>
       </c>
-      <c r="F172" s="2">
-        <v>0</v>
-      </c>
-      <c r="G172" s="3" t="s">
-        <v>10</v>
+      <c r="F172" s="4">
+        <v>31</v>
+      </c>
+      <c r="G172" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -5937,22 +5975,22 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C173" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D173" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E173">
         <v>240</v>
       </c>
-      <c r="F173" s="2">
-        <v>0</v>
-      </c>
-      <c r="G173" s="3" t="s">
-        <v>10</v>
+      <c r="F173" s="4">
+        <v>93</v>
+      </c>
+      <c r="G173" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -5960,22 +5998,22 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C174" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D174" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E174">
         <v>480</v>
       </c>
-      <c r="F174" s="2">
-        <v>0</v>
-      </c>
-      <c r="G174" s="3" t="s">
-        <v>10</v>
+      <c r="F174" s="4">
+        <v>378</v>
+      </c>
+      <c r="G174" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -5983,22 +6021,22 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C175" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D175" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E175">
         <v>120</v>
       </c>
-      <c r="F175" s="2">
-        <v>0</v>
-      </c>
-      <c r="G175" s="3" t="s">
-        <v>10</v>
+      <c r="F175" s="4">
+        <v>94</v>
+      </c>
+      <c r="G175" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6006,22 +6044,22 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C176" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D176" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E176">
         <v>120</v>
       </c>
-      <c r="F176" s="2">
-        <v>0</v>
-      </c>
-      <c r="G176" s="3" t="s">
-        <v>10</v>
+      <c r="F176" s="4">
+        <v>103</v>
+      </c>
+      <c r="G176" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6029,22 +6067,22 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C177" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D177" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E177">
         <v>120</v>
       </c>
-      <c r="F177" s="2">
-        <v>0</v>
-      </c>
-      <c r="G177" s="3" t="s">
-        <v>10</v>
+      <c r="F177" s="4">
+        <v>93</v>
+      </c>
+      <c r="G177" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6052,19 +6090,19 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C178" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D178" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E178">
         <v>12</v>
       </c>
       <c r="F178" s="2">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>10</v>
@@ -6075,19 +6113,19 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C179" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D179" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E179">
         <v>12</v>
       </c>
       <c r="F179" s="2">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="G179" s="3" t="s">
         <v>10</v>
@@ -6098,22 +6136,22 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C180" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D180" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E180">
         <v>30</v>
       </c>
-      <c r="F180" s="2">
+      <c r="F180" s="6">
         <v>0</v>
       </c>
-      <c r="G180" s="3" t="s">
-        <v>10</v>
+      <c r="G180" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6121,22 +6159,22 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C181" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D181" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E181">
         <v>12</v>
       </c>
-      <c r="F181" s="2">
-        <v>0</v>
-      </c>
-      <c r="G181" s="3" t="s">
-        <v>10</v>
+      <c r="F181" s="4">
+        <v>4</v>
+      </c>
+      <c r="G181" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6144,22 +6182,22 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C182" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D182" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E182">
         <v>6</v>
       </c>
-      <c r="F182" s="2">
-        <v>0</v>
-      </c>
-      <c r="G182" s="3" t="s">
-        <v>10</v>
+      <c r="F182" s="4">
+        <v>6</v>
+      </c>
+      <c r="G182" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6167,19 +6205,19 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C183" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D183" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E183">
         <v>1</v>
       </c>
       <c r="F183" s="2">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>10</v>
@@ -6190,19 +6228,19 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C184" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D184" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E184">
         <v>20</v>
       </c>
       <c r="F184" s="2">
-        <v>0</v>
+        <v>3763</v>
       </c>
       <c r="G184" s="3" t="s">
         <v>10</v>
@@ -6213,19 +6251,19 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C185" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D185" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E185">
         <v>20</v>
       </c>
       <c r="F185" s="2">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>10</v>
@@ -6236,22 +6274,22 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C186" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D186" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E186">
         <v>20</v>
       </c>
-      <c r="F186" s="2">
-        <v>0</v>
-      </c>
-      <c r="G186" s="3" t="s">
-        <v>10</v>
+      <c r="F186" s="4">
+        <v>40</v>
+      </c>
+      <c r="G186" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -6259,22 +6297,22 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C187" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D187" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E187">
         <v>56</v>
       </c>
-      <c r="F187" s="2">
-        <v>0</v>
-      </c>
-      <c r="G187" s="3" t="s">
-        <v>10</v>
+      <c r="F187" s="4">
+        <v>20</v>
+      </c>
+      <c r="G187" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -6282,22 +6320,22 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C188" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D188" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E188">
         <v>50</v>
       </c>
-      <c r="F188" s="2">
-        <v>0</v>
-      </c>
-      <c r="G188" s="3" t="s">
-        <v>10</v>
+      <c r="F188" s="4">
+        <v>17</v>
+      </c>
+      <c r="G188" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -6305,19 +6343,19 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C189" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D189" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E189">
         <v>50</v>
       </c>
       <c r="F189" s="2">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>10</v>
@@ -6328,19 +6366,19 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C190" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D190" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E190">
         <v>50</v>
       </c>
       <c r="F190" s="2">
-        <v>0</v>
+        <v>1181</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>10</v>
@@ -6351,19 +6389,19 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C191" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D191" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E191">
         <v>50</v>
       </c>
       <c r="F191" s="2">
-        <v>0</v>
+        <v>1373</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>10</v>
@@ -6374,19 +6412,19 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C192" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D192" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E192">
         <v>50</v>
       </c>
       <c r="F192" s="2">
-        <v>0</v>
+        <v>710</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>10</v>
@@ -6397,19 +6435,19 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C193" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D193" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E193">
         <v>50</v>
       </c>
       <c r="F193" s="2">
-        <v>0</v>
+        <v>19771</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>10</v>
@@ -6420,19 +6458,19 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C194" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D194" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E194">
         <v>100</v>
       </c>
       <c r="F194" s="2">
-        <v>0</v>
+        <v>1181</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>10</v>
@@ -6443,19 +6481,19 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C195" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D195" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E195">
         <v>60</v>
       </c>
       <c r="F195" s="2">
-        <v>0</v>
+        <v>454</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>10</v>
@@ -6466,19 +6504,19 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C196" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D196" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E196">
         <v>100</v>
       </c>
       <c r="F196" s="2">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>10</v>
@@ -6489,19 +6527,19 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C197" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D197" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E197">
         <v>80</v>
       </c>
       <c r="F197" s="2">
-        <v>0</v>
+        <v>1247</v>
       </c>
       <c r="G197" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -4262,7 +4262,7 @@
         <v>5</v>
       </c>
       <c r="F98" s="2">
-        <v>580</v>
+        <v>530</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2123,7 +2123,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>19989</v>
+        <v>19971</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2192,7 +2192,7 @@
         <v>120</v>
       </c>
       <c r="F8" s="4">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>29</v>
@@ -2514,7 +2514,7 @@
         <v>120</v>
       </c>
       <c r="F22" s="2">
-        <v>1791</v>
+        <v>1671</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -2721,7 +2721,7 @@
         <v>120</v>
       </c>
       <c r="F31" s="2">
-        <v>2811</v>
+        <v>2761</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -2790,7 +2790,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -3020,7 +3020,7 @@
         <v>480</v>
       </c>
       <c r="F44" s="4">
-        <v>1072</v>
+        <v>1048</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>29</v>
@@ -3043,7 +3043,7 @@
         <v>240</v>
       </c>
       <c r="F45" s="4">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>29</v>
@@ -3779,7 +3779,7 @@
         <v>600</v>
       </c>
       <c r="F77" s="4">
-        <v>529</v>
+        <v>509</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>29</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -4032,7 +4032,7 @@
         <v>20</v>
       </c>
       <c r="F88" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>3135</v>
+        <v>2835</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>66068</v>
+        <v>64468</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2169,7 +2169,7 @@
         <v>120</v>
       </c>
       <c r="F7" s="2">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -2284,7 +2284,7 @@
         <v>60</v>
       </c>
       <c r="F12" s="4">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>29</v>
@@ -2376,7 +2376,7 @@
         <v>120</v>
       </c>
       <c r="F16" s="2">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -2491,7 +2491,7 @@
         <v>120</v>
       </c>
       <c r="F21" s="4">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>29</v>
@@ -2583,7 +2583,7 @@
         <v>120</v>
       </c>
       <c r="F25" s="4">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>29</v>
@@ -2652,7 +2652,7 @@
         <v>120</v>
       </c>
       <c r="F28" s="2">
-        <v>8432</v>
+        <v>8426</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -2721,7 +2721,7 @@
         <v>120</v>
       </c>
       <c r="F31" s="2">
-        <v>2761</v>
+        <v>2713</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -2859,7 +2859,7 @@
         <v>240</v>
       </c>
       <c r="F37" s="4">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>29</v>
@@ -3020,7 +3020,7 @@
         <v>480</v>
       </c>
       <c r="F44" s="4">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>29</v>
@@ -3135,7 +3135,7 @@
         <v>120</v>
       </c>
       <c r="F49" s="4">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>29</v>
@@ -3250,7 +3250,7 @@
         <v>720</v>
       </c>
       <c r="F54" s="4">
-        <v>2258</v>
+        <v>2246</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>29</v>
@@ -3595,7 +3595,7 @@
         <v>240</v>
       </c>
       <c r="F69" s="2">
-        <v>4002</v>
+        <v>3984</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -4261,11 +4261,11 @@
       <c r="E98">
         <v>5</v>
       </c>
-      <c r="F98" s="2">
-        <v>70</v>
-      </c>
-      <c r="G98" s="3" t="s">
-        <v>10</v>
+      <c r="F98" s="4">
+        <v>10</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="4">
-        <v>41540</v>
+        <v>40540</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -2514,7 +2514,7 @@
         <v>120</v>
       </c>
       <c r="F22" s="4">
-        <v>1671</v>
+        <v>1650</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>14</v>
@@ -2652,7 +2652,7 @@
         <v>120</v>
       </c>
       <c r="F28" s="4">
-        <v>7826</v>
+        <v>7790</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>14</v>
@@ -2790,7 +2790,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="4">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>14</v>
@@ -2859,7 +2859,7 @@
         <v>240</v>
       </c>
       <c r="F37" s="2">
-        <v>914</v>
+        <v>878</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -3457,7 +3457,7 @@
         <v>240</v>
       </c>
       <c r="F63" s="4">
-        <v>6822</v>
+        <v>6816</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>14</v>
@@ -3480,7 +3480,7 @@
         <v>60</v>
       </c>
       <c r="F64" s="4">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="G64" s="5" t="s">
         <v>14</v>
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="4">
-        <v>10886</v>
+        <v>10646</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>14</v>
@@ -4078,7 +4078,7 @@
         <v>100</v>
       </c>
       <c r="F90" s="4">
-        <v>104671</v>
+        <v>104071</v>
       </c>
       <c r="G90" s="5" t="s">
         <v>14</v>
@@ -4147,7 +4147,7 @@
         <v>2</v>
       </c>
       <c r="F93" s="4">
-        <v>143</v>
+        <v>223</v>
       </c>
       <c r="G93" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2514,7 +2514,7 @@
         <v>120</v>
       </c>
       <c r="F22" s="4">
-        <v>1500</v>
+        <v>1440</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>14</v>
@@ -3457,7 +3457,7 @@
         <v>240</v>
       </c>
       <c r="F63" s="4">
-        <v>6712</v>
+        <v>6688</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>14</v>
@@ -4193,7 +4193,7 @@
         <v>120</v>
       </c>
       <c r="F95" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>10</v>
@@ -4216,7 +4216,7 @@
         <v>120</v>
       </c>
       <c r="F96" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2652,7 +2652,7 @@
         <v>120</v>
       </c>
       <c r="F28" s="4">
-        <v>7766</v>
+        <v>7742</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>14</v>
@@ -3457,7 +3457,7 @@
         <v>240</v>
       </c>
       <c r="F63" s="4">
-        <v>6688</v>
+        <v>6628</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2859,7 +2859,7 @@
         <v>240</v>
       </c>
       <c r="F37" s="4">
-        <v>878</v>
+        <v>854</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>29</v>
@@ -3020,7 +3020,7 @@
         <v>480</v>
       </c>
       <c r="F44" s="4">
-        <v>1042</v>
+        <v>1030</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>29</v>
@@ -3411,7 +3411,7 @@
         <v>240</v>
       </c>
       <c r="F61" s="4">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>29</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>76700</v>
+        <v>60700</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>10480</v>
+        <v>10450</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2422,7 +2422,7 @@
         <v>120</v>
       </c>
       <c r="F18" s="2">
-        <v>953</v>
+        <v>929</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -2445,7 +2445,7 @@
         <v>120</v>
       </c>
       <c r="F19" s="4">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>29</v>
@@ -3250,7 +3250,7 @@
         <v>720</v>
       </c>
       <c r="F54" s="4">
-        <v>2054</v>
+        <v>1694</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>29</v>
@@ -3595,7 +3595,7 @@
         <v>240</v>
       </c>
       <c r="F69" s="2">
-        <v>3864</v>
+        <v>3624</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -4445,11 +4445,11 @@
       <c r="E106">
         <v>120</v>
       </c>
-      <c r="F106" s="4">
-        <v>15</v>
-      </c>
-      <c r="G106" s="5" t="s">
-        <v>29</v>
+      <c r="F106" s="6">
+        <v>0</v>
+      </c>
+      <c r="G106" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>10390</v>
+        <v>11090</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -4032,7 +4032,7 @@
         <v>20</v>
       </c>
       <c r="F88" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>10</v>
@@ -4147,7 +4147,7 @@
         <v>2</v>
       </c>
       <c r="F93" s="2">
-        <v>221</v>
+        <v>271</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -4170,7 +4170,7 @@
         <v>6</v>
       </c>
       <c r="F94" s="2">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>1718</v>
+        <v>1660</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>11090</v>
+        <v>11073</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2951,7 +2951,7 @@
         <v>240</v>
       </c>
       <c r="F41" s="4">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>29</v>
@@ -3319,7 +3319,7 @@
         <v>720</v>
       </c>
       <c r="F57" s="2">
-        <v>4189</v>
+        <v>4117</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>10</v>
@@ -3457,7 +3457,7 @@
         <v>240</v>
       </c>
       <c r="F63" s="2">
-        <v>6568</v>
+        <v>5836</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>11013</v>
+        <v>10973</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2169,7 +2169,7 @@
         <v>120</v>
       </c>
       <c r="F7" s="4">
-        <v>961</v>
+        <v>949</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>14</v>
@@ -2422,7 +2422,7 @@
         <v>120</v>
       </c>
       <c r="F18" s="4">
-        <v>929</v>
+        <v>917</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>14</v>
@@ -2491,7 +2491,7 @@
         <v>120</v>
       </c>
       <c r="F21" s="6">
-        <v>349</v>
+        <v>319</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>30</v>
@@ -2652,7 +2652,7 @@
         <v>120</v>
       </c>
       <c r="F28" s="4">
-        <v>7620</v>
+        <v>7608</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>14</v>
@@ -3319,7 +3319,7 @@
         <v>720</v>
       </c>
       <c r="F57" s="6">
-        <v>3385</v>
+        <v>3325</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>30</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="4">
-        <v>10923</v>
+        <v>10603</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2192,7 +2192,7 @@
         <v>120</v>
       </c>
       <c r="F8" s="6">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>30</v>
@@ -2284,7 +2284,7 @@
         <v>60</v>
       </c>
       <c r="F12" s="6">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>30</v>
@@ -2307,7 +2307,7 @@
         <v>120</v>
       </c>
       <c r="F13" s="6">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>30</v>
@@ -2330,7 +2330,7 @@
         <v>120</v>
       </c>
       <c r="F14" s="6">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>30</v>
@@ -2399,7 +2399,7 @@
         <v>120</v>
       </c>
       <c r="F17" s="6">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>30</v>
@@ -2606,7 +2606,7 @@
         <v>120</v>
       </c>
       <c r="F26" s="6">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>30</v>
@@ -2652,7 +2652,7 @@
         <v>120</v>
       </c>
       <c r="F28" s="4">
-        <v>6888</v>
+        <v>6768</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>14</v>
@@ -3089,7 +3089,7 @@
         <v>240</v>
       </c>
       <c r="F47" s="6">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>30</v>
@@ -3342,7 +3342,7 @@
         <v>240</v>
       </c>
       <c r="F58" s="6">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>30</v>
@@ -3411,7 +3411,7 @@
         <v>240</v>
       </c>
       <c r="F61" s="6">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="G61" s="7" t="s">
         <v>30</v>
@@ -5665,7 +5665,7 @@
         <v>120</v>
       </c>
       <c r="F159" s="6">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="G159" s="7" t="s">
         <v>30</v>
@@ -5941,7 +5941,7 @@
         <v>120</v>
       </c>
       <c r="F171" s="4">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G171" s="5" t="s">
         <v>14</v>
@@ -5987,7 +5987,7 @@
         <v>240</v>
       </c>
       <c r="F173" s="6">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G173" s="7" t="s">
         <v>30</v>
@@ -6079,7 +6079,7 @@
         <v>120</v>
       </c>
       <c r="F177" s="6">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G177" s="7" t="s">
         <v>30</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="4">
-        <v>55370</v>
+        <v>54697</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="4">
-        <v>10323</v>
+        <v>10317</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2652,7 +2652,7 @@
         <v>120</v>
       </c>
       <c r="F28" s="2">
-        <v>6672</v>
+        <v>6648</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>55867</v>
+        <v>55787</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>590</v>
+        <v>540</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>55787</v>
+        <v>55307</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2123,7 +2123,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>14137</v>
+        <v>13837</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2169,7 +2169,7 @@
         <v>120</v>
       </c>
       <c r="F7" s="2">
-        <v>829</v>
+        <v>811</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -2376,7 +2376,7 @@
         <v>120</v>
       </c>
       <c r="F16" s="2">
-        <v>686</v>
+        <v>668</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -2652,7 +2652,7 @@
         <v>120</v>
       </c>
       <c r="F28" s="2">
-        <v>6648</v>
+        <v>6624</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -3595,7 +3595,7 @@
         <v>240</v>
       </c>
       <c r="F69" s="2">
-        <v>3312</v>
+        <v>3288</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>9677</v>
+        <v>9637</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -6447,7 +6447,7 @@
         <v>50</v>
       </c>
       <c r="F193" s="2">
-        <v>19771</v>
+        <v>19721</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>10</v>
@@ -6493,7 +6493,7 @@
         <v>60</v>
       </c>
       <c r="F195" s="2">
-        <v>454</v>
+        <v>394</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>12450</v>
+        <v>11850</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>49627</v>
+        <v>49547</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2146,7 +2146,7 @@
         <v>200</v>
       </c>
       <c r="F6" s="2">
-        <v>28663</v>
+        <v>20463</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -4078,7 +4078,7 @@
         <v>100</v>
       </c>
       <c r="F90" s="2">
-        <v>96270</v>
+        <v>91670</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>3400</v>
+        <v>3040</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>17627</v>
+        <v>10427</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2146,7 +2146,7 @@
         <v>200</v>
       </c>
       <c r="F6" s="2">
-        <v>20463</v>
+        <v>18463</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>8191</v>
+        <v>8071</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -4078,7 +4078,7 @@
         <v>100</v>
       </c>
       <c r="F90" s="2">
-        <v>91670</v>
+        <v>90670</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2169,7 +2169,7 @@
         <v>120</v>
       </c>
       <c r="F7" s="2">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -2307,7 +2307,7 @@
         <v>120</v>
       </c>
       <c r="F13" s="4">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>29</v>
@@ -2330,7 +2330,7 @@
         <v>120</v>
       </c>
       <c r="F14" s="4">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>29</v>
@@ -2514,7 +2514,7 @@
         <v>120</v>
       </c>
       <c r="F22" s="2">
-        <v>1307</v>
+        <v>1187</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -2859,7 +2859,7 @@
         <v>240</v>
       </c>
       <c r="F37" s="4">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>29</v>
@@ -3020,7 +3020,7 @@
         <v>480</v>
       </c>
       <c r="F44" s="4">
-        <v>988</v>
+        <v>976</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>29</v>
@@ -3066,7 +3066,7 @@
         <v>800</v>
       </c>
       <c r="F46" s="4">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>29</v>
@@ -3250,7 +3250,7 @@
         <v>720</v>
       </c>
       <c r="F54" s="4">
-        <v>1562</v>
+        <v>1514</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>29</v>
@@ -3273,7 +3273,7 @@
         <v>120</v>
       </c>
       <c r="F55" s="4">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>29</v>
@@ -3411,7 +3411,7 @@
         <v>240</v>
       </c>
       <c r="F61" s="4">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>29</v>
@@ -3457,7 +3457,7 @@
         <v>240</v>
       </c>
       <c r="F63" s="2">
-        <v>4984</v>
+        <v>4972</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3595,7 +3595,7 @@
         <v>240</v>
       </c>
       <c r="F69" s="2">
-        <v>2806</v>
+        <v>2782</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -43,66 +43,69 @@
     <t>LIGAS N° 18 - 80 MM X 2 MM X 1 LBS - NATURAL - ALLEANZA</t>
   </si>
   <si>
+    <t>✗ AGOTADO</t>
+  </si>
+  <si>
+    <t>85007</t>
+  </si>
+  <si>
+    <t>7754807850063</t>
+  </si>
+  <si>
+    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - NATURAL - ALLEANZA</t>
+  </si>
+  <si>
+    <t>✓ OK</t>
+  </si>
+  <si>
+    <t>85768</t>
+  </si>
+  <si>
+    <t>7754807857680</t>
+  </si>
+  <si>
+    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - VERDE - ALLEANZA</t>
+  </si>
+  <si>
+    <t>85008</t>
+  </si>
+  <si>
+    <t>7754807850087</t>
+  </si>
+  <si>
+    <t>LIGAS N° 78 - 140 MM X 10 MM X 1 LBS - NATURAL - ALLEANZA</t>
+  </si>
+  <si>
+    <t>85801</t>
+  </si>
+  <si>
+    <t>7754807857024</t>
+  </si>
+  <si>
+    <t>ALFILER ALLEANZA 35 MM CAJA X 50 GR</t>
+  </si>
+  <si>
+    <t>85163</t>
+  </si>
+  <si>
+    <t>091511400595</t>
+  </si>
+  <si>
+    <t>CUCHILLA ARTE AK-1/5B</t>
+  </si>
+  <si>
+    <t>85164</t>
+  </si>
+  <si>
+    <t>091511400670</t>
+  </si>
+  <si>
+    <t>CUCHILLA ARTE AK-4</t>
+  </si>
+  <si>
     <t>⚠ BAJO</t>
   </si>
   <si>
-    <t>85007</t>
-  </si>
-  <si>
-    <t>7754807850063</t>
-  </si>
-  <si>
-    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - NATURAL - ALLEANZA</t>
-  </si>
-  <si>
-    <t>✓ OK</t>
-  </si>
-  <si>
-    <t>85768</t>
-  </si>
-  <si>
-    <t>7754807857680</t>
-  </si>
-  <si>
-    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - VERDE - ALLEANZA</t>
-  </si>
-  <si>
-    <t>85008</t>
-  </si>
-  <si>
-    <t>7754807850087</t>
-  </si>
-  <si>
-    <t>LIGAS N° 78 - 140 MM X 10 MM X 1 LBS - NATURAL - ALLEANZA</t>
-  </si>
-  <si>
-    <t>85801</t>
-  </si>
-  <si>
-    <t>7754807857024</t>
-  </si>
-  <si>
-    <t>ALFILER ALLEANZA 35 MM CAJA X 50 GR</t>
-  </si>
-  <si>
-    <t>85163</t>
-  </si>
-  <si>
-    <t>091511400595</t>
-  </si>
-  <si>
-    <t>CUCHILLA ARTE AK-1/5B</t>
-  </si>
-  <si>
-    <t>85164</t>
-  </si>
-  <si>
-    <t>091511400670</t>
-  </si>
-  <si>
-    <t>CUCHILLA ARTE AK-4</t>
-  </si>
-  <si>
     <t>85770</t>
   </si>
   <si>
@@ -125,9 +128,6 @@
   </si>
   <si>
     <t>CUCHILLLA DE ARTE AK-5/5B</t>
-  </si>
-  <si>
-    <t>✗ AGOTADO</t>
   </si>
   <si>
     <t>85166</t>
@@ -1587,7 +1587,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFD97706"/>
+      <color rgb="FFDC2626"/>
       <sz val="12"/>
     </font>
     <font>
@@ -1597,7 +1597,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFDC2626"/>
+      <color rgb="FFD97706"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -1615,7 +1615,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
+        <fgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1625,7 +1625,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
+        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
   </fills>
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2191,11 +2191,11 @@
       <c r="E8">
         <v>120</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="6">
         <v>253</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
+      <c r="G8" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2203,22 +2203,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9">
         <v>240</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="6">
         <v>253</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
+      <c r="G9" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2226,22 +2226,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E10">
         <v>200</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="6">
         <v>49</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>10</v>
+      <c r="G10" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2249,22 +2249,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E11">
         <v>240</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="2">
         <v>0</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>38</v>
+      <c r="G11" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2283,11 +2283,11 @@
       <c r="E12">
         <v>60</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="6">
         <v>105</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
+      <c r="G12" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2306,11 +2306,11 @@
       <c r="E13">
         <v>120</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="6">
         <v>129</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
+      <c r="G13" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2329,11 +2329,11 @@
       <c r="E14">
         <v>120</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="6">
         <v>167</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="G14" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2352,11 +2352,11 @@
       <c r="E15">
         <v>120</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="6">
         <v>84</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>10</v>
+      <c r="G15" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2398,11 +2398,11 @@
       <c r="E17">
         <v>120</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="6">
         <v>250</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>10</v>
+      <c r="G17" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2444,11 +2444,11 @@
       <c r="E19">
         <v>120</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="6">
         <v>129</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>10</v>
+      <c r="G19" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2467,11 +2467,11 @@
       <c r="E20">
         <v>120</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="6">
         <v>75</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>10</v>
+      <c r="G20" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2490,11 +2490,11 @@
       <c r="E21">
         <v>120</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="2">
         <v>0</v>
       </c>
-      <c r="G21" s="7" t="s">
-        <v>38</v>
+      <c r="G21" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2536,11 +2536,11 @@
       <c r="E23">
         <v>60</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="2">
         <v>0</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>38</v>
+      <c r="G23" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2559,11 +2559,11 @@
       <c r="E24">
         <v>120</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="6">
         <v>89</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>10</v>
+      <c r="G24" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2582,11 +2582,11 @@
       <c r="E25">
         <v>120</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="6">
         <v>228</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>10</v>
+      <c r="G25" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2605,11 +2605,11 @@
       <c r="E26">
         <v>120</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="6">
         <v>105</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>10</v>
+      <c r="G26" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2628,11 +2628,11 @@
       <c r="E27">
         <v>120</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="6">
         <v>159</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>10</v>
+      <c r="G27" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2674,11 +2674,11 @@
       <c r="E29">
         <v>72</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="6">
         <v>92</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>10</v>
+      <c r="G29" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2697,11 +2697,11 @@
       <c r="E30">
         <v>120</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="6">
         <v>6</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>10</v>
+      <c r="G30" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2766,11 +2766,11 @@
       <c r="E33">
         <v>144</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="2">
         <v>0</v>
       </c>
-      <c r="G33" s="7" t="s">
-        <v>38</v>
+      <c r="G33" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2812,11 +2812,11 @@
       <c r="E35">
         <v>128</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F35" s="2">
         <v>0</v>
       </c>
-      <c r="G35" s="7" t="s">
-        <v>38</v>
+      <c r="G35" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2835,11 +2835,11 @@
       <c r="E36">
         <v>120</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="6">
         <v>118</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>10</v>
+      <c r="G36" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2858,11 +2858,11 @@
       <c r="E37">
         <v>240</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="6">
         <v>474</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>10</v>
+      <c r="G37" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2881,11 +2881,11 @@
       <c r="E38">
         <v>120</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="6">
         <v>123</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>10</v>
+      <c r="G38" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2904,11 +2904,11 @@
       <c r="E39">
         <v>240</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="6">
         <v>224</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>10</v>
+      <c r="G39" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2927,11 +2927,11 @@
       <c r="E40">
         <v>240</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="6">
         <v>225</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>10</v>
+      <c r="G40" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2950,11 +2950,11 @@
       <c r="E41">
         <v>240</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="6">
         <v>53</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>10</v>
+      <c r="G41" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2973,11 +2973,11 @@
       <c r="E42">
         <v>240</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="6">
         <v>255</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>10</v>
+      <c r="G42" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3019,11 +3019,11 @@
       <c r="E44">
         <v>480</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="6">
         <v>913</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>10</v>
+      <c r="G44" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3042,11 +3042,11 @@
       <c r="E45">
         <v>240</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="6">
         <v>139</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>10</v>
+      <c r="G45" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3065,11 +3065,11 @@
       <c r="E46">
         <v>800</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="6">
         <v>203</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>10</v>
+      <c r="G46" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3088,11 +3088,11 @@
       <c r="E47">
         <v>240</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="6">
         <v>85</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>10</v>
+      <c r="G47" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3111,11 +3111,11 @@
       <c r="E48">
         <v>120</v>
       </c>
-      <c r="F48" s="6">
+      <c r="F48" s="2">
         <v>0</v>
       </c>
-      <c r="G48" s="7" t="s">
-        <v>38</v>
+      <c r="G48" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3134,11 +3134,11 @@
       <c r="E49">
         <v>120</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="6">
         <v>255</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>10</v>
+      <c r="G49" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3157,11 +3157,11 @@
       <c r="E50">
         <v>120</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="6">
         <v>285</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>10</v>
+      <c r="G50" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3180,11 +3180,11 @@
       <c r="E51">
         <v>10</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="6">
         <v>5</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>10</v>
+      <c r="G51" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3203,11 +3203,11 @@
       <c r="E52">
         <v>60</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="6">
         <v>80</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>10</v>
+      <c r="G52" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3226,11 +3226,11 @@
       <c r="E53">
         <v>20</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="6">
         <v>27</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>10</v>
+      <c r="G53" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3249,11 +3249,11 @@
       <c r="E54">
         <v>720</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="6">
         <v>1634</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>10</v>
+      <c r="G54" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3272,11 +3272,11 @@
       <c r="E55">
         <v>120</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="6">
         <v>68</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>10</v>
+      <c r="G55" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -3295,11 +3295,11 @@
       <c r="E56">
         <v>120</v>
       </c>
-      <c r="F56" s="6">
+      <c r="F56" s="2">
         <v>0</v>
       </c>
-      <c r="G56" s="7" t="s">
-        <v>38</v>
+      <c r="G56" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3318,11 +3318,11 @@
       <c r="E57">
         <v>720</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="6">
         <v>828</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>10</v>
+      <c r="G57" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -3341,11 +3341,11 @@
       <c r="E58">
         <v>240</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="6">
         <v>189</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>10</v>
+      <c r="G58" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3364,11 +3364,11 @@
       <c r="E59">
         <v>120</v>
       </c>
-      <c r="F59" s="6">
+      <c r="F59" s="2">
         <v>0</v>
       </c>
-      <c r="G59" s="7" t="s">
-        <v>38</v>
+      <c r="G59" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3387,11 +3387,11 @@
       <c r="E60">
         <v>240</v>
       </c>
-      <c r="F60" s="6">
+      <c r="F60" s="2">
         <v>0</v>
       </c>
-      <c r="G60" s="7" t="s">
-        <v>38</v>
+      <c r="G60" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3410,11 +3410,11 @@
       <c r="E61">
         <v>240</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="6">
         <v>216</v>
       </c>
-      <c r="G61" s="3" t="s">
-        <v>10</v>
+      <c r="G61" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3433,11 +3433,11 @@
       <c r="E62">
         <v>240</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="6">
         <v>198</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>10</v>
+      <c r="G62" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3502,11 +3502,11 @@
       <c r="E65">
         <v>60</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="6">
         <v>53</v>
       </c>
-      <c r="G65" s="3" t="s">
-        <v>10</v>
+      <c r="G65" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3525,11 +3525,11 @@
       <c r="E66">
         <v>120</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="6">
         <v>21</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>10</v>
+      <c r="G66" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3548,11 +3548,11 @@
       <c r="E67">
         <v>240</v>
       </c>
-      <c r="F67" s="6">
+      <c r="F67" s="2">
         <v>0</v>
       </c>
-      <c r="G67" s="7" t="s">
-        <v>38</v>
+      <c r="G67" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3571,11 +3571,11 @@
       <c r="E68">
         <v>240</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="6">
         <v>50</v>
       </c>
-      <c r="G68" s="3" t="s">
-        <v>10</v>
+      <c r="G68" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3617,11 +3617,11 @@
       <c r="E70">
         <v>240</v>
       </c>
-      <c r="F70" s="6">
+      <c r="F70" s="2">
         <v>0</v>
       </c>
-      <c r="G70" s="7" t="s">
-        <v>38</v>
+      <c r="G70" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3640,11 +3640,11 @@
       <c r="E71">
         <v>240</v>
       </c>
-      <c r="F71" s="6">
+      <c r="F71" s="2">
         <v>0</v>
       </c>
-      <c r="G71" s="7" t="s">
-        <v>38</v>
+      <c r="G71" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3663,11 +3663,11 @@
       <c r="E72">
         <v>480</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="6">
         <v>314</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>10</v>
+      <c r="G72" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3686,11 +3686,11 @@
       <c r="E73">
         <v>240</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="6">
         <v>488</v>
       </c>
-      <c r="G73" s="3" t="s">
-        <v>10</v>
+      <c r="G73" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3709,11 +3709,11 @@
       <c r="E74">
         <v>240</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="6">
         <v>606</v>
       </c>
-      <c r="G74" s="3" t="s">
-        <v>10</v>
+      <c r="G74" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -3755,11 +3755,11 @@
       <c r="E76">
         <v>240</v>
       </c>
-      <c r="F76" s="6">
+      <c r="F76" s="2">
         <v>0</v>
       </c>
-      <c r="G76" s="7" t="s">
-        <v>38</v>
+      <c r="G76" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -3778,11 +3778,11 @@
       <c r="E77">
         <v>600</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77" s="6">
         <v>509</v>
       </c>
-      <c r="G77" s="3" t="s">
-        <v>10</v>
+      <c r="G77" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -3801,11 +3801,11 @@
       <c r="E78">
         <v>120</v>
       </c>
-      <c r="F78" s="2">
+      <c r="F78" s="6">
         <v>109</v>
       </c>
-      <c r="G78" s="3" t="s">
-        <v>10</v>
+      <c r="G78" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -3824,11 +3824,11 @@
       <c r="E79">
         <v>120</v>
       </c>
-      <c r="F79" s="6">
+      <c r="F79" s="2">
         <v>0</v>
       </c>
-      <c r="G79" s="7" t="s">
-        <v>38</v>
+      <c r="G79" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3847,11 +3847,11 @@
       <c r="E80">
         <v>60</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80" s="6">
         <v>12</v>
       </c>
-      <c r="G80" s="3" t="s">
-        <v>10</v>
+      <c r="G80" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3916,11 +3916,11 @@
       <c r="E83">
         <v>40</v>
       </c>
-      <c r="F83" s="6">
+      <c r="F83" s="2">
         <v>0</v>
       </c>
-      <c r="G83" s="7" t="s">
-        <v>38</v>
+      <c r="G83" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -3962,11 +3962,11 @@
       <c r="E85">
         <v>40</v>
       </c>
-      <c r="F85" s="6">
+      <c r="F85" s="2">
         <v>0</v>
       </c>
-      <c r="G85" s="7" t="s">
-        <v>38</v>
+      <c r="G85" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -3985,11 +3985,11 @@
       <c r="E86">
         <v>40</v>
       </c>
-      <c r="F86" s="2">
+      <c r="F86" s="6">
         <v>4</v>
       </c>
-      <c r="G86" s="3" t="s">
-        <v>10</v>
+      <c r="G86" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4008,11 +4008,11 @@
       <c r="E87">
         <v>40</v>
       </c>
-      <c r="F87" s="6">
+      <c r="F87" s="2">
         <v>0</v>
       </c>
-      <c r="G87" s="7" t="s">
-        <v>38</v>
+      <c r="G87" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4031,11 +4031,11 @@
       <c r="E88">
         <v>20</v>
       </c>
-      <c r="F88" s="6">
+      <c r="F88" s="2">
         <v>0</v>
       </c>
-      <c r="G88" s="7" t="s">
-        <v>38</v>
+      <c r="G88" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4192,11 +4192,11 @@
       <c r="E95">
         <v>120</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="6">
         <v>38</v>
       </c>
-      <c r="G95" s="3" t="s">
-        <v>10</v>
+      <c r="G95" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4215,11 +4215,11 @@
       <c r="E96">
         <v>120</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="6">
         <v>4</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>10</v>
+      <c r="G96" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -4238,11 +4238,11 @@
       <c r="E97">
         <v>10</v>
       </c>
-      <c r="F97" s="2">
+      <c r="F97" s="6">
         <v>7</v>
       </c>
-      <c r="G97" s="3" t="s">
-        <v>10</v>
+      <c r="G97" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4261,11 +4261,11 @@
       <c r="E98">
         <v>5</v>
       </c>
-      <c r="F98" s="6">
+      <c r="F98" s="2">
         <v>0</v>
       </c>
-      <c r="G98" s="7" t="s">
-        <v>38</v>
+      <c r="G98" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4399,11 +4399,11 @@
       <c r="E104">
         <v>200</v>
       </c>
-      <c r="F104" s="2">
+      <c r="F104" s="6">
         <v>4</v>
       </c>
-      <c r="G104" s="3" t="s">
-        <v>10</v>
+      <c r="G104" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -4445,11 +4445,11 @@
       <c r="E106">
         <v>120</v>
       </c>
-      <c r="F106" s="6">
+      <c r="F106" s="2">
         <v>0</v>
       </c>
-      <c r="G106" s="7" t="s">
-        <v>38</v>
+      <c r="G106" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4468,11 +4468,11 @@
       <c r="E107">
         <v>120</v>
       </c>
-      <c r="F107" s="2">
+      <c r="F107" s="6">
         <v>1</v>
       </c>
-      <c r="G107" s="3" t="s">
-        <v>10</v>
+      <c r="G107" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -4491,11 +4491,11 @@
       <c r="E108">
         <v>18</v>
       </c>
-      <c r="F108" s="2">
+      <c r="F108" s="6">
         <v>79</v>
       </c>
-      <c r="G108" s="3" t="s">
-        <v>10</v>
+      <c r="G108" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -4514,11 +4514,11 @@
       <c r="E109">
         <v>6</v>
       </c>
-      <c r="F109" s="6">
+      <c r="F109" s="2">
         <v>0</v>
       </c>
-      <c r="G109" s="7" t="s">
-        <v>38</v>
+      <c r="G109" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -4537,11 +4537,11 @@
       <c r="E110">
         <v>54</v>
       </c>
-      <c r="F110" s="2">
+      <c r="F110" s="6">
         <v>27</v>
       </c>
-      <c r="G110" s="3" t="s">
-        <v>10</v>
+      <c r="G110" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -4560,11 +4560,11 @@
       <c r="E111">
         <v>10</v>
       </c>
-      <c r="F111" s="6">
+      <c r="F111" s="2">
         <v>0</v>
       </c>
-      <c r="G111" s="7" t="s">
-        <v>38</v>
+      <c r="G111" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -4583,11 +4583,11 @@
       <c r="E112">
         <v>12</v>
       </c>
-      <c r="F112" s="6">
+      <c r="F112" s="2">
         <v>0</v>
       </c>
-      <c r="G112" s="7" t="s">
-        <v>38</v>
+      <c r="G112" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -4606,11 +4606,11 @@
       <c r="E113">
         <v>12</v>
       </c>
-      <c r="F113" s="6">
+      <c r="F113" s="2">
         <v>0</v>
       </c>
-      <c r="G113" s="7" t="s">
-        <v>38</v>
+      <c r="G113" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -4652,11 +4652,11 @@
       <c r="E115">
         <v>800</v>
       </c>
-      <c r="F115" s="2">
+      <c r="F115" s="6">
         <v>262</v>
       </c>
-      <c r="G115" s="3" t="s">
-        <v>10</v>
+      <c r="G115" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -4675,11 +4675,11 @@
       <c r="E116">
         <v>5</v>
       </c>
-      <c r="F116" s="6">
+      <c r="F116" s="2">
         <v>0</v>
       </c>
-      <c r="G116" s="7" t="s">
-        <v>38</v>
+      <c r="G116" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -4698,11 +4698,11 @@
       <c r="E117">
         <v>5</v>
       </c>
-      <c r="F117" s="2">
+      <c r="F117" s="6">
         <v>2</v>
       </c>
-      <c r="G117" s="3" t="s">
-        <v>10</v>
+      <c r="G117" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -4744,11 +4744,11 @@
       <c r="E119">
         <v>10</v>
       </c>
-      <c r="F119" s="2">
+      <c r="F119" s="6">
         <v>6</v>
       </c>
-      <c r="G119" s="3" t="s">
-        <v>10</v>
+      <c r="G119" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -4767,11 +4767,11 @@
       <c r="E120">
         <v>10</v>
       </c>
-      <c r="F120" s="2">
+      <c r="F120" s="6">
         <v>36</v>
       </c>
-      <c r="G120" s="3" t="s">
-        <v>10</v>
+      <c r="G120" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -4790,11 +4790,11 @@
       <c r="E121">
         <v>6</v>
       </c>
-      <c r="F121" s="6">
+      <c r="F121" s="2">
         <v>0</v>
       </c>
-      <c r="G121" s="7" t="s">
-        <v>38</v>
+      <c r="G121" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -4813,11 +4813,11 @@
       <c r="E122">
         <v>6</v>
       </c>
-      <c r="F122" s="6">
+      <c r="F122" s="2">
         <v>0</v>
       </c>
-      <c r="G122" s="7" t="s">
-        <v>38</v>
+      <c r="G122" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -4836,11 +4836,11 @@
       <c r="E123">
         <v>40</v>
       </c>
-      <c r="F123" s="2">
+      <c r="F123" s="6">
         <v>127</v>
       </c>
-      <c r="G123" s="3" t="s">
-        <v>10</v>
+      <c r="G123" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -4882,11 +4882,11 @@
       <c r="E125">
         <v>1</v>
       </c>
-      <c r="F125" s="6">
+      <c r="F125" s="2">
         <v>0</v>
       </c>
-      <c r="G125" s="7" t="s">
-        <v>38</v>
+      <c r="G125" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -4905,11 +4905,11 @@
       <c r="E126">
         <v>4</v>
       </c>
-      <c r="F126" s="2">
+      <c r="F126" s="6">
         <v>17</v>
       </c>
-      <c r="G126" s="3" t="s">
-        <v>10</v>
+      <c r="G126" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -4951,11 +4951,11 @@
       <c r="E128">
         <v>4</v>
       </c>
-      <c r="F128" s="2">
+      <c r="F128" s="6">
         <v>18</v>
       </c>
-      <c r="G128" s="3" t="s">
-        <v>10</v>
+      <c r="G128" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -4974,11 +4974,11 @@
       <c r="E129">
         <v>1</v>
       </c>
-      <c r="F129" s="2">
+      <c r="F129" s="6">
         <v>3</v>
       </c>
-      <c r="G129" s="3" t="s">
-        <v>10</v>
+      <c r="G129" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -4997,11 +4997,11 @@
       <c r="E130">
         <v>60</v>
       </c>
-      <c r="F130" s="2">
+      <c r="F130" s="6">
         <v>3</v>
       </c>
-      <c r="G130" s="3" t="s">
-        <v>10</v>
+      <c r="G130" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5043,11 +5043,11 @@
       <c r="E132">
         <v>60</v>
       </c>
-      <c r="F132" s="2">
+      <c r="F132" s="6">
         <v>58</v>
       </c>
-      <c r="G132" s="3" t="s">
-        <v>10</v>
+      <c r="G132" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5066,11 +5066,11 @@
       <c r="E133">
         <v>60</v>
       </c>
-      <c r="F133" s="2">
+      <c r="F133" s="6">
         <v>138</v>
       </c>
-      <c r="G133" s="3" t="s">
-        <v>10</v>
+      <c r="G133" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5250,11 +5250,11 @@
       <c r="E141">
         <v>40</v>
       </c>
-      <c r="F141" s="2">
+      <c r="F141" s="6">
         <v>108</v>
       </c>
-      <c r="G141" s="3" t="s">
-        <v>10</v>
+      <c r="G141" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -5273,11 +5273,11 @@
       <c r="E142">
         <v>60</v>
       </c>
-      <c r="F142" s="2">
+      <c r="F142" s="6">
         <v>122</v>
       </c>
-      <c r="G142" s="3" t="s">
-        <v>10</v>
+      <c r="G142" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -5296,11 +5296,11 @@
       <c r="E143">
         <v>6</v>
       </c>
-      <c r="F143" s="2">
+      <c r="F143" s="6">
         <v>15</v>
       </c>
-      <c r="G143" s="3" t="s">
-        <v>10</v>
+      <c r="G143" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -5319,11 +5319,11 @@
       <c r="E144">
         <v>18</v>
       </c>
-      <c r="F144" s="6">
+      <c r="F144" s="2">
         <v>0</v>
       </c>
-      <c r="G144" s="7" t="s">
-        <v>38</v>
+      <c r="G144" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -5342,11 +5342,11 @@
       <c r="E145">
         <v>8</v>
       </c>
-      <c r="F145" s="2">
+      <c r="F145" s="6">
         <v>8</v>
       </c>
-      <c r="G145" s="3" t="s">
-        <v>10</v>
+      <c r="G145" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -5365,11 +5365,11 @@
       <c r="E146">
         <v>30</v>
       </c>
-      <c r="F146" s="2">
+      <c r="F146" s="6">
         <v>34</v>
       </c>
-      <c r="G146" s="3" t="s">
-        <v>10</v>
+      <c r="G146" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -5388,11 +5388,11 @@
       <c r="E147">
         <v>2</v>
       </c>
-      <c r="F147" s="6">
+      <c r="F147" s="2">
         <v>0</v>
       </c>
-      <c r="G147" s="7" t="s">
-        <v>38</v>
+      <c r="G147" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -5503,11 +5503,11 @@
       <c r="E152">
         <v>20</v>
       </c>
-      <c r="F152" s="2">
+      <c r="F152" s="6">
         <v>8</v>
       </c>
-      <c r="G152" s="3" t="s">
-        <v>10</v>
+      <c r="G152" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -5526,11 +5526,11 @@
       <c r="E153">
         <v>240</v>
       </c>
-      <c r="F153" s="2">
+      <c r="F153" s="6">
         <v>598</v>
       </c>
-      <c r="G153" s="3" t="s">
-        <v>10</v>
+      <c r="G153" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -5549,11 +5549,11 @@
       <c r="E154">
         <v>120</v>
       </c>
-      <c r="F154" s="2">
+      <c r="F154" s="6">
         <v>121</v>
       </c>
-      <c r="G154" s="3" t="s">
-        <v>10</v>
+      <c r="G154" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -5595,11 +5595,11 @@
       <c r="E156">
         <v>120</v>
       </c>
-      <c r="F156" s="6">
+      <c r="F156" s="2">
         <v>0</v>
       </c>
-      <c r="G156" s="7" t="s">
-        <v>38</v>
+      <c r="G156" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -5618,11 +5618,11 @@
       <c r="E157">
         <v>72</v>
       </c>
-      <c r="F157" s="2">
+      <c r="F157" s="6">
         <v>50</v>
       </c>
-      <c r="G157" s="3" t="s">
-        <v>10</v>
+      <c r="G157" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -5641,11 +5641,11 @@
       <c r="E158">
         <v>60</v>
       </c>
-      <c r="F158" s="2">
-        <v>30</v>
-      </c>
-      <c r="G158" s="3" t="s">
-        <v>10</v>
+      <c r="F158" s="6">
+        <v>30</v>
+      </c>
+      <c r="G158" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5664,11 +5664,11 @@
       <c r="E159">
         <v>120</v>
       </c>
-      <c r="F159" s="2">
+      <c r="F159" s="6">
         <v>71</v>
       </c>
-      <c r="G159" s="3" t="s">
-        <v>10</v>
+      <c r="G159" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -5687,11 +5687,11 @@
       <c r="E160">
         <v>72</v>
       </c>
-      <c r="F160" s="2">
+      <c r="F160" s="6">
         <v>10</v>
       </c>
-      <c r="G160" s="3" t="s">
-        <v>10</v>
+      <c r="G160" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5710,11 +5710,11 @@
       <c r="E161">
         <v>20</v>
       </c>
-      <c r="F161" s="2">
+      <c r="F161" s="6">
         <v>44</v>
       </c>
-      <c r="G161" s="3" t="s">
-        <v>10</v>
+      <c r="G161" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5733,11 +5733,11 @@
       <c r="E162">
         <v>100</v>
       </c>
-      <c r="F162" s="2">
+      <c r="F162" s="6">
         <v>74</v>
       </c>
-      <c r="G162" s="3" t="s">
-        <v>10</v>
+      <c r="G162" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -5756,11 +5756,11 @@
       <c r="E163">
         <v>5</v>
       </c>
-      <c r="F163" s="2">
+      <c r="F163" s="6">
         <v>11</v>
       </c>
-      <c r="G163" s="3" t="s">
-        <v>10</v>
+      <c r="G163" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -5779,11 +5779,11 @@
       <c r="E164">
         <v>10</v>
       </c>
-      <c r="F164" s="2">
+      <c r="F164" s="6">
         <v>4</v>
       </c>
-      <c r="G164" s="3" t="s">
-        <v>10</v>
+      <c r="G164" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -5802,11 +5802,11 @@
       <c r="E165">
         <v>20</v>
       </c>
-      <c r="F165" s="2">
+      <c r="F165" s="6">
         <v>35</v>
       </c>
-      <c r="G165" s="3" t="s">
-        <v>10</v>
+      <c r="G165" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -5825,11 +5825,11 @@
       <c r="E166">
         <v>20</v>
       </c>
-      <c r="F166" s="2">
+      <c r="F166" s="6">
         <v>57</v>
       </c>
-      <c r="G166" s="3" t="s">
-        <v>10</v>
+      <c r="G166" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -5848,11 +5848,11 @@
       <c r="E167">
         <v>24</v>
       </c>
-      <c r="F167" s="2">
+      <c r="F167" s="6">
         <v>28</v>
       </c>
-      <c r="G167" s="3" t="s">
-        <v>10</v>
+      <c r="G167" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -5871,11 +5871,11 @@
       <c r="E168">
         <v>240</v>
       </c>
-      <c r="F168" s="2">
+      <c r="F168" s="6">
         <v>920</v>
       </c>
-      <c r="G168" s="3" t="s">
-        <v>10</v>
+      <c r="G168" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -5894,11 +5894,11 @@
       <c r="E169">
         <v>240</v>
       </c>
-      <c r="F169" s="2">
+      <c r="F169" s="6">
         <v>102</v>
       </c>
-      <c r="G169" s="3" t="s">
-        <v>10</v>
+      <c r="G169" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -5917,11 +5917,11 @@
       <c r="E170">
         <v>480</v>
       </c>
-      <c r="F170" s="2">
+      <c r="F170" s="6">
         <v>211</v>
       </c>
-      <c r="G170" s="3" t="s">
-        <v>10</v>
+      <c r="G170" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -5963,11 +5963,11 @@
       <c r="E172">
         <v>240</v>
       </c>
-      <c r="F172" s="2">
+      <c r="F172" s="6">
         <v>25</v>
       </c>
-      <c r="G172" s="3" t="s">
-        <v>10</v>
+      <c r="G172" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -5986,11 +5986,11 @@
       <c r="E173">
         <v>240</v>
       </c>
-      <c r="F173" s="2">
+      <c r="F173" s="6">
         <v>81</v>
       </c>
-      <c r="G173" s="3" t="s">
-        <v>10</v>
+      <c r="G173" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -6009,11 +6009,11 @@
       <c r="E174">
         <v>480</v>
       </c>
-      <c r="F174" s="2">
+      <c r="F174" s="6">
         <v>378</v>
       </c>
-      <c r="G174" s="3" t="s">
-        <v>10</v>
+      <c r="G174" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6032,11 +6032,11 @@
       <c r="E175">
         <v>120</v>
       </c>
-      <c r="F175" s="2">
+      <c r="F175" s="6">
         <v>94</v>
       </c>
-      <c r="G175" s="3" t="s">
-        <v>10</v>
+      <c r="G175" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6055,11 +6055,11 @@
       <c r="E176">
         <v>120</v>
       </c>
-      <c r="F176" s="2">
-        <v>103</v>
-      </c>
-      <c r="G176" s="3" t="s">
-        <v>10</v>
+      <c r="F176" s="6">
+        <v>103</v>
+      </c>
+      <c r="G176" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6078,11 +6078,11 @@
       <c r="E177">
         <v>120</v>
       </c>
-      <c r="F177" s="2">
+      <c r="F177" s="6">
         <v>72</v>
       </c>
-      <c r="G177" s="3" t="s">
-        <v>10</v>
+      <c r="G177" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6147,11 +6147,11 @@
       <c r="E180">
         <v>30</v>
       </c>
-      <c r="F180" s="6">
+      <c r="F180" s="2">
         <v>0</v>
       </c>
-      <c r="G180" s="7" t="s">
-        <v>38</v>
+      <c r="G180" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6170,11 +6170,11 @@
       <c r="E181">
         <v>12</v>
       </c>
-      <c r="F181" s="2">
+      <c r="F181" s="6">
         <v>4</v>
       </c>
-      <c r="G181" s="3" t="s">
-        <v>10</v>
+      <c r="G181" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6193,11 +6193,11 @@
       <c r="E182">
         <v>6</v>
       </c>
-      <c r="F182" s="2">
+      <c r="F182" s="6">
         <v>6</v>
       </c>
-      <c r="G182" s="3" t="s">
-        <v>10</v>
+      <c r="G182" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6285,11 +6285,11 @@
       <c r="E186">
         <v>20</v>
       </c>
-      <c r="F186" s="2">
+      <c r="F186" s="6">
         <v>40</v>
       </c>
-      <c r="G186" s="3" t="s">
-        <v>10</v>
+      <c r="G186" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -6308,11 +6308,11 @@
       <c r="E187">
         <v>56</v>
       </c>
-      <c r="F187" s="2">
+      <c r="F187" s="6">
         <v>20</v>
       </c>
-      <c r="G187" s="3" t="s">
-        <v>10</v>
+      <c r="G187" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -6331,11 +6331,11 @@
       <c r="E188">
         <v>50</v>
       </c>
-      <c r="F188" s="2">
+      <c r="F188" s="6">
         <v>17</v>
       </c>
-      <c r="G188" s="3" t="s">
-        <v>10</v>
+      <c r="G188" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -43,91 +43,91 @@
     <t>LIGAS N° 18 - 80 MM X 2 MM X 1 LBS - NATURAL - ALLEANZA</t>
   </si>
   <si>
+    <t>⚠ BAJO</t>
+  </si>
+  <si>
+    <t>85007</t>
+  </si>
+  <si>
+    <t>7754807850063</t>
+  </si>
+  <si>
+    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - NATURAL - ALLEANZA</t>
+  </si>
+  <si>
+    <t>✓ OK</t>
+  </si>
+  <si>
+    <t>85768</t>
+  </si>
+  <si>
+    <t>7754807857680</t>
+  </si>
+  <si>
+    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - VERDE - ALLEANZA</t>
+  </si>
+  <si>
+    <t>85008</t>
+  </si>
+  <si>
+    <t>7754807850087</t>
+  </si>
+  <si>
+    <t>LIGAS N° 78 - 140 MM X 10 MM X 1 LBS - NATURAL - ALLEANZA</t>
+  </si>
+  <si>
+    <t>85801</t>
+  </si>
+  <si>
+    <t>7754807857024</t>
+  </si>
+  <si>
+    <t>ALFILER ALLEANZA 35 MM CAJA X 50 GR</t>
+  </si>
+  <si>
+    <t>85163</t>
+  </si>
+  <si>
+    <t>091511400595</t>
+  </si>
+  <si>
+    <t>CUCHILLA ARTE AK-1/5B</t>
+  </si>
+  <si>
+    <t>85164</t>
+  </si>
+  <si>
+    <t>091511400670</t>
+  </si>
+  <si>
+    <t>CUCHILLA ARTE AK-4</t>
+  </si>
+  <si>
+    <t>85770</t>
+  </si>
+  <si>
+    <t>091511220292</t>
+  </si>
+  <si>
+    <t>CUCHILLA ARTE AK-5 + KB-5/30B</t>
+  </si>
+  <si>
+    <t>85868</t>
+  </si>
+  <si>
+    <t>4901165202925</t>
+  </si>
+  <si>
+    <t>CUCHILLLA ARTE AK-5 PINK</t>
+  </si>
+  <si>
+    <t>85871</t>
+  </si>
+  <si>
+    <t>CUCHILLLA DE ARTE AK-5/5B</t>
+  </si>
+  <si>
     <t>✗ AGOTADO</t>
-  </si>
-  <si>
-    <t>85007</t>
-  </si>
-  <si>
-    <t>7754807850063</t>
-  </si>
-  <si>
-    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - NATURAL - ALLEANZA</t>
-  </si>
-  <si>
-    <t>✓ OK</t>
-  </si>
-  <si>
-    <t>85768</t>
-  </si>
-  <si>
-    <t>7754807857680</t>
-  </si>
-  <si>
-    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - VERDE - ALLEANZA</t>
-  </si>
-  <si>
-    <t>85008</t>
-  </si>
-  <si>
-    <t>7754807850087</t>
-  </si>
-  <si>
-    <t>LIGAS N° 78 - 140 MM X 10 MM X 1 LBS - NATURAL - ALLEANZA</t>
-  </si>
-  <si>
-    <t>85801</t>
-  </si>
-  <si>
-    <t>7754807857024</t>
-  </si>
-  <si>
-    <t>ALFILER ALLEANZA 35 MM CAJA X 50 GR</t>
-  </si>
-  <si>
-    <t>85163</t>
-  </si>
-  <si>
-    <t>091511400595</t>
-  </si>
-  <si>
-    <t>CUCHILLA ARTE AK-1/5B</t>
-  </si>
-  <si>
-    <t>85164</t>
-  </si>
-  <si>
-    <t>091511400670</t>
-  </si>
-  <si>
-    <t>CUCHILLA ARTE AK-4</t>
-  </si>
-  <si>
-    <t>⚠ BAJO</t>
-  </si>
-  <si>
-    <t>85770</t>
-  </si>
-  <si>
-    <t>091511220292</t>
-  </si>
-  <si>
-    <t>CUCHILLA ARTE AK-5 + KB-5/30B</t>
-  </si>
-  <si>
-    <t>85868</t>
-  </si>
-  <si>
-    <t>4901165202925</t>
-  </si>
-  <si>
-    <t>CUCHILLLA ARTE AK-5 PINK</t>
-  </si>
-  <si>
-    <t>85871</t>
-  </si>
-  <si>
-    <t>CUCHILLLA DE ARTE AK-5/5B</t>
   </si>
   <si>
     <t>85166</t>
@@ -1587,7 +1587,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFDC2626"/>
+      <color rgb="FFD97706"/>
       <sz val="12"/>
     </font>
     <font>
@@ -1597,7 +1597,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFD97706"/>
+      <color rgb="FFDC2626"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -1615,7 +1615,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
+        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -1625,7 +1625,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
+        <fgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2169,7 +2169,7 @@
         <v>120</v>
       </c>
       <c r="F7" s="4">
-        <v>712</v>
+        <v>688</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>14</v>
@@ -2191,11 +2191,11 @@
       <c r="E8">
         <v>120</v>
       </c>
-      <c r="F8" s="6">
-        <v>253</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>30</v>
+      <c r="F8" s="2">
+        <v>247</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2203,22 +2203,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
         <v>31</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>33</v>
       </c>
       <c r="E9">
         <v>240</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="2">
         <v>253</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>30</v>
+      <c r="G9" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2226,22 +2226,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
         <v>34</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>36</v>
       </c>
       <c r="E10">
         <v>200</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="2">
         <v>49</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>30</v>
+      <c r="G10" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2249,22 +2249,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" t="s">
         <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" t="s">
-        <v>38</v>
       </c>
       <c r="E11">
         <v>240</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="6">
         <v>0</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>10</v>
+      <c r="G11" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2283,11 +2283,11 @@
       <c r="E12">
         <v>60</v>
       </c>
-      <c r="F12" s="6">
-        <v>105</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>30</v>
+      <c r="F12" s="2">
+        <v>103</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2306,11 +2306,11 @@
       <c r="E13">
         <v>120</v>
       </c>
-      <c r="F13" s="6">
-        <v>129</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>30</v>
+      <c r="F13" s="2">
+        <v>117</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2329,11 +2329,11 @@
       <c r="E14">
         <v>120</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="2">
         <v>167</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>30</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2352,11 +2352,11 @@
       <c r="E15">
         <v>120</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="2">
         <v>84</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>30</v>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2375,11 +2375,11 @@
       <c r="E16">
         <v>120</v>
       </c>
-      <c r="F16" s="4">
-        <v>623</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>14</v>
+      <c r="F16" s="2">
+        <v>587</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2398,11 +2398,11 @@
       <c r="E17">
         <v>120</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="2">
         <v>250</v>
       </c>
-      <c r="G17" s="7" t="s">
-        <v>30</v>
+      <c r="G17" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2444,11 +2444,11 @@
       <c r="E19">
         <v>120</v>
       </c>
-      <c r="F19" s="6">
-        <v>129</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>30</v>
+      <c r="F19" s="2">
+        <v>105</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2467,11 +2467,11 @@
       <c r="E20">
         <v>120</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="2">
         <v>75</v>
       </c>
-      <c r="G20" s="7" t="s">
-        <v>30</v>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2490,11 +2490,11 @@
       <c r="E21">
         <v>120</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="6">
         <v>0</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>10</v>
+      <c r="G21" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2536,11 +2536,11 @@
       <c r="E23">
         <v>60</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="6">
         <v>0</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>10</v>
+      <c r="G23" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2559,11 +2559,11 @@
       <c r="E24">
         <v>120</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="2">
         <v>89</v>
       </c>
-      <c r="G24" s="7" t="s">
-        <v>30</v>
+      <c r="G24" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2582,11 +2582,11 @@
       <c r="E25">
         <v>120</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="2">
         <v>228</v>
       </c>
-      <c r="G25" s="7" t="s">
-        <v>30</v>
+      <c r="G25" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2605,11 +2605,11 @@
       <c r="E26">
         <v>120</v>
       </c>
-      <c r="F26" s="6">
-        <v>105</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>30</v>
+      <c r="F26" s="2">
+        <v>93</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2628,11 +2628,11 @@
       <c r="E27">
         <v>120</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="2">
         <v>159</v>
       </c>
-      <c r="G27" s="7" t="s">
-        <v>30</v>
+      <c r="G27" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2674,11 +2674,11 @@
       <c r="E29">
         <v>72</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="2">
         <v>92</v>
       </c>
-      <c r="G29" s="7" t="s">
-        <v>30</v>
+      <c r="G29" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2697,11 +2697,11 @@
       <c r="E30">
         <v>120</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="2">
         <v>6</v>
       </c>
-      <c r="G30" s="7" t="s">
-        <v>30</v>
+      <c r="G30" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2766,11 +2766,11 @@
       <c r="E33">
         <v>144</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="6">
         <v>0</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>10</v>
+      <c r="G33" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2812,11 +2812,11 @@
       <c r="E35">
         <v>128</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="6">
         <v>0</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>10</v>
+      <c r="G35" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2835,11 +2835,11 @@
       <c r="E36">
         <v>120</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F36" s="2">
         <v>118</v>
       </c>
-      <c r="G36" s="7" t="s">
-        <v>30</v>
+      <c r="G36" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2858,11 +2858,11 @@
       <c r="E37">
         <v>240</v>
       </c>
-      <c r="F37" s="6">
+      <c r="F37" s="2">
         <v>474</v>
       </c>
-      <c r="G37" s="7" t="s">
-        <v>30</v>
+      <c r="G37" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2881,11 +2881,11 @@
       <c r="E38">
         <v>120</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F38" s="2">
         <v>123</v>
       </c>
-      <c r="G38" s="7" t="s">
-        <v>30</v>
+      <c r="G38" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2904,11 +2904,11 @@
       <c r="E39">
         <v>240</v>
       </c>
-      <c r="F39" s="6">
+      <c r="F39" s="2">
         <v>224</v>
       </c>
-      <c r="G39" s="7" t="s">
-        <v>30</v>
+      <c r="G39" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2927,11 +2927,11 @@
       <c r="E40">
         <v>240</v>
       </c>
-      <c r="F40" s="6">
+      <c r="F40" s="2">
         <v>225</v>
       </c>
-      <c r="G40" s="7" t="s">
-        <v>30</v>
+      <c r="G40" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2950,11 +2950,11 @@
       <c r="E41">
         <v>240</v>
       </c>
-      <c r="F41" s="6">
+      <c r="F41" s="2">
         <v>53</v>
       </c>
-      <c r="G41" s="7" t="s">
-        <v>30</v>
+      <c r="G41" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2973,11 +2973,11 @@
       <c r="E42">
         <v>240</v>
       </c>
-      <c r="F42" s="6">
+      <c r="F42" s="2">
         <v>255</v>
       </c>
-      <c r="G42" s="7" t="s">
-        <v>30</v>
+      <c r="G42" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3019,11 +3019,11 @@
       <c r="E44">
         <v>480</v>
       </c>
-      <c r="F44" s="6">
+      <c r="F44" s="2">
         <v>913</v>
       </c>
-      <c r="G44" s="7" t="s">
-        <v>30</v>
+      <c r="G44" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3042,11 +3042,11 @@
       <c r="E45">
         <v>240</v>
       </c>
-      <c r="F45" s="6">
-        <v>139</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>30</v>
+      <c r="F45" s="2">
+        <v>127</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3065,11 +3065,11 @@
       <c r="E46">
         <v>800</v>
       </c>
-      <c r="F46" s="6">
-        <v>203</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>30</v>
+      <c r="F46" s="2">
+        <v>179</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3088,11 +3088,11 @@
       <c r="E47">
         <v>240</v>
       </c>
-      <c r="F47" s="6">
+      <c r="F47" s="2">
         <v>85</v>
       </c>
-      <c r="G47" s="7" t="s">
-        <v>30</v>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3111,11 +3111,11 @@
       <c r="E48">
         <v>120</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="6">
         <v>0</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>10</v>
+      <c r="G48" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3134,11 +3134,11 @@
       <c r="E49">
         <v>120</v>
       </c>
-      <c r="F49" s="6">
+      <c r="F49" s="2">
         <v>255</v>
       </c>
-      <c r="G49" s="7" t="s">
-        <v>30</v>
+      <c r="G49" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3157,11 +3157,11 @@
       <c r="E50">
         <v>120</v>
       </c>
-      <c r="F50" s="6">
+      <c r="F50" s="2">
         <v>285</v>
       </c>
-      <c r="G50" s="7" t="s">
-        <v>30</v>
+      <c r="G50" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3180,11 +3180,11 @@
       <c r="E51">
         <v>10</v>
       </c>
-      <c r="F51" s="6">
+      <c r="F51" s="2">
         <v>5</v>
       </c>
-      <c r="G51" s="7" t="s">
-        <v>30</v>
+      <c r="G51" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3203,11 +3203,11 @@
       <c r="E52">
         <v>60</v>
       </c>
-      <c r="F52" s="6">
+      <c r="F52" s="2">
         <v>80</v>
       </c>
-      <c r="G52" s="7" t="s">
-        <v>30</v>
+      <c r="G52" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3226,11 +3226,11 @@
       <c r="E53">
         <v>20</v>
       </c>
-      <c r="F53" s="6">
+      <c r="F53" s="2">
         <v>27</v>
       </c>
-      <c r="G53" s="7" t="s">
-        <v>30</v>
+      <c r="G53" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3249,11 +3249,11 @@
       <c r="E54">
         <v>720</v>
       </c>
-      <c r="F54" s="6">
+      <c r="F54" s="2">
         <v>1634</v>
       </c>
-      <c r="G54" s="7" t="s">
-        <v>30</v>
+      <c r="G54" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3272,11 +3272,11 @@
       <c r="E55">
         <v>120</v>
       </c>
-      <c r="F55" s="6">
+      <c r="F55" s="2">
         <v>68</v>
       </c>
-      <c r="G55" s="7" t="s">
-        <v>30</v>
+      <c r="G55" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -3295,11 +3295,11 @@
       <c r="E56">
         <v>120</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="6">
         <v>0</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>10</v>
+      <c r="G56" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3318,11 +3318,11 @@
       <c r="E57">
         <v>720</v>
       </c>
-      <c r="F57" s="6">
+      <c r="F57" s="2">
         <v>828</v>
       </c>
-      <c r="G57" s="7" t="s">
-        <v>30</v>
+      <c r="G57" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -3341,11 +3341,11 @@
       <c r="E58">
         <v>240</v>
       </c>
-      <c r="F58" s="6">
+      <c r="F58" s="2">
         <v>189</v>
       </c>
-      <c r="G58" s="7" t="s">
-        <v>30</v>
+      <c r="G58" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3364,11 +3364,11 @@
       <c r="E59">
         <v>120</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="6">
         <v>0</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>10</v>
+      <c r="G59" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3387,11 +3387,11 @@
       <c r="E60">
         <v>240</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="6">
         <v>0</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>10</v>
+      <c r="G60" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3410,11 +3410,11 @@
       <c r="E61">
         <v>240</v>
       </c>
-      <c r="F61" s="6">
+      <c r="F61" s="2">
         <v>216</v>
       </c>
-      <c r="G61" s="7" t="s">
-        <v>30</v>
+      <c r="G61" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3433,11 +3433,11 @@
       <c r="E62">
         <v>240</v>
       </c>
-      <c r="F62" s="6">
+      <c r="F62" s="2">
         <v>198</v>
       </c>
-      <c r="G62" s="7" t="s">
-        <v>30</v>
+      <c r="G62" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3502,11 +3502,11 @@
       <c r="E65">
         <v>60</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F65" s="2">
         <v>53</v>
       </c>
-      <c r="G65" s="7" t="s">
-        <v>30</v>
+      <c r="G65" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3525,11 +3525,11 @@
       <c r="E66">
         <v>120</v>
       </c>
-      <c r="F66" s="6">
+      <c r="F66" s="2">
         <v>21</v>
       </c>
-      <c r="G66" s="7" t="s">
-        <v>30</v>
+      <c r="G66" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3548,11 +3548,11 @@
       <c r="E67">
         <v>240</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="6">
         <v>0</v>
       </c>
-      <c r="G67" s="3" t="s">
-        <v>10</v>
+      <c r="G67" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3571,11 +3571,11 @@
       <c r="E68">
         <v>240</v>
       </c>
-      <c r="F68" s="6">
+      <c r="F68" s="2">
         <v>50</v>
       </c>
-      <c r="G68" s="7" t="s">
-        <v>30</v>
+      <c r="G68" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3617,11 +3617,11 @@
       <c r="E70">
         <v>240</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="6">
         <v>0</v>
       </c>
-      <c r="G70" s="3" t="s">
-        <v>10</v>
+      <c r="G70" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3640,11 +3640,11 @@
       <c r="E71">
         <v>240</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="6">
         <v>0</v>
       </c>
-      <c r="G71" s="3" t="s">
-        <v>10</v>
+      <c r="G71" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3663,11 +3663,11 @@
       <c r="E72">
         <v>480</v>
       </c>
-      <c r="F72" s="6">
+      <c r="F72" s="2">
         <v>314</v>
       </c>
-      <c r="G72" s="7" t="s">
-        <v>30</v>
+      <c r="G72" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3686,11 +3686,11 @@
       <c r="E73">
         <v>240</v>
       </c>
-      <c r="F73" s="6">
+      <c r="F73" s="2">
         <v>488</v>
       </c>
-      <c r="G73" s="7" t="s">
-        <v>30</v>
+      <c r="G73" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3709,11 +3709,11 @@
       <c r="E74">
         <v>240</v>
       </c>
-      <c r="F74" s="6">
+      <c r="F74" s="2">
         <v>606</v>
       </c>
-      <c r="G74" s="7" t="s">
-        <v>30</v>
+      <c r="G74" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -3755,11 +3755,11 @@
       <c r="E76">
         <v>240</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="6">
         <v>0</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>10</v>
+      <c r="G76" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -3778,11 +3778,11 @@
       <c r="E77">
         <v>600</v>
       </c>
-      <c r="F77" s="6">
+      <c r="F77" s="2">
         <v>509</v>
       </c>
-      <c r="G77" s="7" t="s">
-        <v>30</v>
+      <c r="G77" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -3801,11 +3801,11 @@
       <c r="E78">
         <v>120</v>
       </c>
-      <c r="F78" s="6">
+      <c r="F78" s="2">
         <v>109</v>
       </c>
-      <c r="G78" s="7" t="s">
-        <v>30</v>
+      <c r="G78" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -3824,11 +3824,11 @@
       <c r="E79">
         <v>120</v>
       </c>
-      <c r="F79" s="2">
+      <c r="F79" s="6">
         <v>0</v>
       </c>
-      <c r="G79" s="3" t="s">
-        <v>10</v>
+      <c r="G79" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3847,11 +3847,11 @@
       <c r="E80">
         <v>60</v>
       </c>
-      <c r="F80" s="6">
+      <c r="F80" s="2">
         <v>12</v>
       </c>
-      <c r="G80" s="7" t="s">
-        <v>30</v>
+      <c r="G80" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3916,11 +3916,11 @@
       <c r="E83">
         <v>40</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83" s="6">
         <v>0</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>10</v>
+      <c r="G83" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -3962,11 +3962,11 @@
       <c r="E85">
         <v>40</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="6">
         <v>0</v>
       </c>
-      <c r="G85" s="3" t="s">
-        <v>10</v>
+      <c r="G85" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -3985,11 +3985,11 @@
       <c r="E86">
         <v>40</v>
       </c>
-      <c r="F86" s="6">
+      <c r="F86" s="2">
         <v>4</v>
       </c>
-      <c r="G86" s="7" t="s">
-        <v>30</v>
+      <c r="G86" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4008,11 +4008,11 @@
       <c r="E87">
         <v>40</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="6">
         <v>0</v>
       </c>
-      <c r="G87" s="3" t="s">
-        <v>10</v>
+      <c r="G87" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4031,11 +4031,11 @@
       <c r="E88">
         <v>20</v>
       </c>
-      <c r="F88" s="2">
+      <c r="F88" s="6">
         <v>0</v>
       </c>
-      <c r="G88" s="3" t="s">
-        <v>10</v>
+      <c r="G88" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4192,11 +4192,11 @@
       <c r="E95">
         <v>120</v>
       </c>
-      <c r="F95" s="6">
+      <c r="F95" s="2">
         <v>38</v>
       </c>
-      <c r="G95" s="7" t="s">
-        <v>30</v>
+      <c r="G95" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4215,11 +4215,11 @@
       <c r="E96">
         <v>120</v>
       </c>
-      <c r="F96" s="6">
+      <c r="F96" s="2">
         <v>4</v>
       </c>
-      <c r="G96" s="7" t="s">
-        <v>30</v>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -4238,11 +4238,11 @@
       <c r="E97">
         <v>10</v>
       </c>
-      <c r="F97" s="6">
+      <c r="F97" s="2">
         <v>7</v>
       </c>
-      <c r="G97" s="7" t="s">
-        <v>30</v>
+      <c r="G97" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4261,11 +4261,11 @@
       <c r="E98">
         <v>5</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F98" s="6">
         <v>0</v>
       </c>
-      <c r="G98" s="3" t="s">
-        <v>10</v>
+      <c r="G98" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4399,11 +4399,11 @@
       <c r="E104">
         <v>200</v>
       </c>
-      <c r="F104" s="6">
+      <c r="F104" s="2">
         <v>4</v>
       </c>
-      <c r="G104" s="7" t="s">
-        <v>30</v>
+      <c r="G104" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -4445,11 +4445,11 @@
       <c r="E106">
         <v>120</v>
       </c>
-      <c r="F106" s="2">
+      <c r="F106" s="6">
         <v>0</v>
       </c>
-      <c r="G106" s="3" t="s">
-        <v>10</v>
+      <c r="G106" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4468,11 +4468,11 @@
       <c r="E107">
         <v>120</v>
       </c>
-      <c r="F107" s="6">
+      <c r="F107" s="2">
         <v>1</v>
       </c>
-      <c r="G107" s="7" t="s">
-        <v>30</v>
+      <c r="G107" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -4491,11 +4491,11 @@
       <c r="E108">
         <v>18</v>
       </c>
-      <c r="F108" s="6">
+      <c r="F108" s="2">
         <v>79</v>
       </c>
-      <c r="G108" s="7" t="s">
-        <v>30</v>
+      <c r="G108" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -4514,11 +4514,11 @@
       <c r="E109">
         <v>6</v>
       </c>
-      <c r="F109" s="2">
+      <c r="F109" s="6">
         <v>0</v>
       </c>
-      <c r="G109" s="3" t="s">
-        <v>10</v>
+      <c r="G109" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -4537,11 +4537,11 @@
       <c r="E110">
         <v>54</v>
       </c>
-      <c r="F110" s="6">
+      <c r="F110" s="2">
         <v>27</v>
       </c>
-      <c r="G110" s="7" t="s">
-        <v>30</v>
+      <c r="G110" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -4560,11 +4560,11 @@
       <c r="E111">
         <v>10</v>
       </c>
-      <c r="F111" s="2">
+      <c r="F111" s="6">
         <v>0</v>
       </c>
-      <c r="G111" s="3" t="s">
-        <v>10</v>
+      <c r="G111" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -4583,11 +4583,11 @@
       <c r="E112">
         <v>12</v>
       </c>
-      <c r="F112" s="2">
+      <c r="F112" s="6">
         <v>0</v>
       </c>
-      <c r="G112" s="3" t="s">
-        <v>10</v>
+      <c r="G112" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -4606,11 +4606,11 @@
       <c r="E113">
         <v>12</v>
       </c>
-      <c r="F113" s="2">
+      <c r="F113" s="6">
         <v>0</v>
       </c>
-      <c r="G113" s="3" t="s">
-        <v>10</v>
+      <c r="G113" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -4652,11 +4652,11 @@
       <c r="E115">
         <v>800</v>
       </c>
-      <c r="F115" s="6">
+      <c r="F115" s="2">
         <v>262</v>
       </c>
-      <c r="G115" s="7" t="s">
-        <v>30</v>
+      <c r="G115" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -4675,11 +4675,11 @@
       <c r="E116">
         <v>5</v>
       </c>
-      <c r="F116" s="2">
+      <c r="F116" s="6">
         <v>0</v>
       </c>
-      <c r="G116" s="3" t="s">
-        <v>10</v>
+      <c r="G116" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -4698,11 +4698,11 @@
       <c r="E117">
         <v>5</v>
       </c>
-      <c r="F117" s="6">
+      <c r="F117" s="2">
         <v>2</v>
       </c>
-      <c r="G117" s="7" t="s">
-        <v>30</v>
+      <c r="G117" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -4744,11 +4744,11 @@
       <c r="E119">
         <v>10</v>
       </c>
-      <c r="F119" s="6">
+      <c r="F119" s="2">
         <v>6</v>
       </c>
-      <c r="G119" s="7" t="s">
-        <v>30</v>
+      <c r="G119" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -4767,11 +4767,11 @@
       <c r="E120">
         <v>10</v>
       </c>
-      <c r="F120" s="6">
+      <c r="F120" s="2">
         <v>36</v>
       </c>
-      <c r="G120" s="7" t="s">
-        <v>30</v>
+      <c r="G120" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -4790,11 +4790,11 @@
       <c r="E121">
         <v>6</v>
       </c>
-      <c r="F121" s="2">
+      <c r="F121" s="6">
         <v>0</v>
       </c>
-      <c r="G121" s="3" t="s">
-        <v>10</v>
+      <c r="G121" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -4813,11 +4813,11 @@
       <c r="E122">
         <v>6</v>
       </c>
-      <c r="F122" s="2">
+      <c r="F122" s="6">
         <v>0</v>
       </c>
-      <c r="G122" s="3" t="s">
-        <v>10</v>
+      <c r="G122" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -4836,11 +4836,11 @@
       <c r="E123">
         <v>40</v>
       </c>
-      <c r="F123" s="6">
+      <c r="F123" s="2">
         <v>127</v>
       </c>
-      <c r="G123" s="7" t="s">
-        <v>30</v>
+      <c r="G123" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -4882,11 +4882,11 @@
       <c r="E125">
         <v>1</v>
       </c>
-      <c r="F125" s="2">
+      <c r="F125" s="6">
         <v>0</v>
       </c>
-      <c r="G125" s="3" t="s">
-        <v>10</v>
+      <c r="G125" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -4905,11 +4905,11 @@
       <c r="E126">
         <v>4</v>
       </c>
-      <c r="F126" s="6">
+      <c r="F126" s="2">
         <v>17</v>
       </c>
-      <c r="G126" s="7" t="s">
-        <v>30</v>
+      <c r="G126" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -4951,11 +4951,11 @@
       <c r="E128">
         <v>4</v>
       </c>
-      <c r="F128" s="6">
+      <c r="F128" s="2">
         <v>18</v>
       </c>
-      <c r="G128" s="7" t="s">
-        <v>30</v>
+      <c r="G128" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -4974,11 +4974,11 @@
       <c r="E129">
         <v>1</v>
       </c>
-      <c r="F129" s="6">
+      <c r="F129" s="2">
         <v>3</v>
       </c>
-      <c r="G129" s="7" t="s">
-        <v>30</v>
+      <c r="G129" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -4997,11 +4997,11 @@
       <c r="E130">
         <v>60</v>
       </c>
-      <c r="F130" s="6">
+      <c r="F130" s="2">
         <v>3</v>
       </c>
-      <c r="G130" s="7" t="s">
-        <v>30</v>
+      <c r="G130" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5043,11 +5043,11 @@
       <c r="E132">
         <v>60</v>
       </c>
-      <c r="F132" s="6">
+      <c r="F132" s="2">
         <v>58</v>
       </c>
-      <c r="G132" s="7" t="s">
-        <v>30</v>
+      <c r="G132" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5066,11 +5066,11 @@
       <c r="E133">
         <v>60</v>
       </c>
-      <c r="F133" s="6">
+      <c r="F133" s="2">
         <v>138</v>
       </c>
-      <c r="G133" s="7" t="s">
-        <v>30</v>
+      <c r="G133" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5250,11 +5250,11 @@
       <c r="E141">
         <v>40</v>
       </c>
-      <c r="F141" s="6">
+      <c r="F141" s="2">
         <v>108</v>
       </c>
-      <c r="G141" s="7" t="s">
-        <v>30</v>
+      <c r="G141" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -5273,11 +5273,11 @@
       <c r="E142">
         <v>60</v>
       </c>
-      <c r="F142" s="6">
+      <c r="F142" s="2">
         <v>122</v>
       </c>
-      <c r="G142" s="7" t="s">
-        <v>30</v>
+      <c r="G142" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -5296,11 +5296,11 @@
       <c r="E143">
         <v>6</v>
       </c>
-      <c r="F143" s="6">
+      <c r="F143" s="2">
         <v>15</v>
       </c>
-      <c r="G143" s="7" t="s">
-        <v>30</v>
+      <c r="G143" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -5319,11 +5319,11 @@
       <c r="E144">
         <v>18</v>
       </c>
-      <c r="F144" s="2">
+      <c r="F144" s="6">
         <v>0</v>
       </c>
-      <c r="G144" s="3" t="s">
-        <v>10</v>
+      <c r="G144" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -5342,11 +5342,11 @@
       <c r="E145">
         <v>8</v>
       </c>
-      <c r="F145" s="6">
+      <c r="F145" s="2">
         <v>8</v>
       </c>
-      <c r="G145" s="7" t="s">
-        <v>30</v>
+      <c r="G145" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -5365,11 +5365,11 @@
       <c r="E146">
         <v>30</v>
       </c>
-      <c r="F146" s="6">
+      <c r="F146" s="2">
         <v>34</v>
       </c>
-      <c r="G146" s="7" t="s">
-        <v>30</v>
+      <c r="G146" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -5388,11 +5388,11 @@
       <c r="E147">
         <v>2</v>
       </c>
-      <c r="F147" s="2">
+      <c r="F147" s="6">
         <v>0</v>
       </c>
-      <c r="G147" s="3" t="s">
-        <v>10</v>
+      <c r="G147" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -5503,11 +5503,11 @@
       <c r="E152">
         <v>20</v>
       </c>
-      <c r="F152" s="6">
+      <c r="F152" s="2">
         <v>8</v>
       </c>
-      <c r="G152" s="7" t="s">
-        <v>30</v>
+      <c r="G152" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -5526,11 +5526,11 @@
       <c r="E153">
         <v>240</v>
       </c>
-      <c r="F153" s="6">
+      <c r="F153" s="2">
         <v>598</v>
       </c>
-      <c r="G153" s="7" t="s">
-        <v>30</v>
+      <c r="G153" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -5549,11 +5549,11 @@
       <c r="E154">
         <v>120</v>
       </c>
-      <c r="F154" s="6">
+      <c r="F154" s="2">
         <v>121</v>
       </c>
-      <c r="G154" s="7" t="s">
-        <v>30</v>
+      <c r="G154" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -5573,7 +5573,7 @@
         <v>60</v>
       </c>
       <c r="F155" s="4">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="G155" s="5" t="s">
         <v>14</v>
@@ -5595,11 +5595,11 @@
       <c r="E156">
         <v>120</v>
       </c>
-      <c r="F156" s="2">
+      <c r="F156" s="6">
         <v>0</v>
       </c>
-      <c r="G156" s="3" t="s">
-        <v>10</v>
+      <c r="G156" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -5618,11 +5618,11 @@
       <c r="E157">
         <v>72</v>
       </c>
-      <c r="F157" s="6">
+      <c r="F157" s="2">
         <v>50</v>
       </c>
-      <c r="G157" s="7" t="s">
-        <v>30</v>
+      <c r="G157" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -5641,11 +5641,11 @@
       <c r="E158">
         <v>60</v>
       </c>
-      <c r="F158" s="6">
+      <c r="F158" s="2">
         <v>30</v>
       </c>
-      <c r="G158" s="7" t="s">
-        <v>30</v>
+      <c r="G158" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5664,11 +5664,11 @@
       <c r="E159">
         <v>120</v>
       </c>
-      <c r="F159" s="6">
+      <c r="F159" s="2">
         <v>71</v>
       </c>
-      <c r="G159" s="7" t="s">
-        <v>30</v>
+      <c r="G159" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -5687,11 +5687,11 @@
       <c r="E160">
         <v>72</v>
       </c>
-      <c r="F160" s="6">
-        <v>10</v>
-      </c>
-      <c r="G160" s="7" t="s">
-        <v>30</v>
+      <c r="F160" s="2">
+        <v>10</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5710,11 +5710,11 @@
       <c r="E161">
         <v>20</v>
       </c>
-      <c r="F161" s="6">
+      <c r="F161" s="2">
         <v>44</v>
       </c>
-      <c r="G161" s="7" t="s">
-        <v>30</v>
+      <c r="G161" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5733,11 +5733,11 @@
       <c r="E162">
         <v>100</v>
       </c>
-      <c r="F162" s="6">
+      <c r="F162" s="2">
         <v>74</v>
       </c>
-      <c r="G162" s="7" t="s">
-        <v>30</v>
+      <c r="G162" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -5756,11 +5756,11 @@
       <c r="E163">
         <v>5</v>
       </c>
-      <c r="F163" s="6">
+      <c r="F163" s="2">
         <v>11</v>
       </c>
-      <c r="G163" s="7" t="s">
-        <v>30</v>
+      <c r="G163" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -5779,11 +5779,11 @@
       <c r="E164">
         <v>10</v>
       </c>
-      <c r="F164" s="6">
+      <c r="F164" s="2">
         <v>4</v>
       </c>
-      <c r="G164" s="7" t="s">
-        <v>30</v>
+      <c r="G164" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -5802,11 +5802,11 @@
       <c r="E165">
         <v>20</v>
       </c>
-      <c r="F165" s="6">
+      <c r="F165" s="2">
         <v>35</v>
       </c>
-      <c r="G165" s="7" t="s">
-        <v>30</v>
+      <c r="G165" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -5825,11 +5825,11 @@
       <c r="E166">
         <v>20</v>
       </c>
-      <c r="F166" s="6">
+      <c r="F166" s="2">
         <v>57</v>
       </c>
-      <c r="G166" s="7" t="s">
-        <v>30</v>
+      <c r="G166" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -5848,11 +5848,11 @@
       <c r="E167">
         <v>24</v>
       </c>
-      <c r="F167" s="6">
+      <c r="F167" s="2">
         <v>28</v>
       </c>
-      <c r="G167" s="7" t="s">
-        <v>30</v>
+      <c r="G167" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -5871,11 +5871,11 @@
       <c r="E168">
         <v>240</v>
       </c>
-      <c r="F168" s="6">
+      <c r="F168" s="2">
         <v>920</v>
       </c>
-      <c r="G168" s="7" t="s">
-        <v>30</v>
+      <c r="G168" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -5894,11 +5894,11 @@
       <c r="E169">
         <v>240</v>
       </c>
-      <c r="F169" s="6">
+      <c r="F169" s="2">
         <v>102</v>
       </c>
-      <c r="G169" s="7" t="s">
-        <v>30</v>
+      <c r="G169" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -5917,11 +5917,11 @@
       <c r="E170">
         <v>480</v>
       </c>
-      <c r="F170" s="6">
+      <c r="F170" s="2">
         <v>211</v>
       </c>
-      <c r="G170" s="7" t="s">
-        <v>30</v>
+      <c r="G170" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -5963,11 +5963,11 @@
       <c r="E172">
         <v>240</v>
       </c>
-      <c r="F172" s="6">
+      <c r="F172" s="2">
         <v>25</v>
       </c>
-      <c r="G172" s="7" t="s">
-        <v>30</v>
+      <c r="G172" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -5986,11 +5986,11 @@
       <c r="E173">
         <v>240</v>
       </c>
-      <c r="F173" s="6">
+      <c r="F173" s="2">
         <v>81</v>
       </c>
-      <c r="G173" s="7" t="s">
-        <v>30</v>
+      <c r="G173" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -6009,11 +6009,11 @@
       <c r="E174">
         <v>480</v>
       </c>
-      <c r="F174" s="6">
+      <c r="F174" s="2">
         <v>378</v>
       </c>
-      <c r="G174" s="7" t="s">
-        <v>30</v>
+      <c r="G174" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6032,11 +6032,11 @@
       <c r="E175">
         <v>120</v>
       </c>
-      <c r="F175" s="6">
+      <c r="F175" s="2">
         <v>94</v>
       </c>
-      <c r="G175" s="7" t="s">
-        <v>30</v>
+      <c r="G175" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6055,11 +6055,11 @@
       <c r="E176">
         <v>120</v>
       </c>
-      <c r="F176" s="6">
-        <v>103</v>
-      </c>
-      <c r="G176" s="7" t="s">
-        <v>30</v>
+      <c r="F176" s="2">
+        <v>103</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6078,11 +6078,11 @@
       <c r="E177">
         <v>120</v>
       </c>
-      <c r="F177" s="6">
+      <c r="F177" s="2">
         <v>72</v>
       </c>
-      <c r="G177" s="7" t="s">
-        <v>30</v>
+      <c r="G177" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6147,11 +6147,11 @@
       <c r="E180">
         <v>30</v>
       </c>
-      <c r="F180" s="2">
+      <c r="F180" s="6">
         <v>0</v>
       </c>
-      <c r="G180" s="3" t="s">
-        <v>10</v>
+      <c r="G180" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6170,11 +6170,11 @@
       <c r="E181">
         <v>12</v>
       </c>
-      <c r="F181" s="6">
+      <c r="F181" s="2">
         <v>4</v>
       </c>
-      <c r="G181" s="7" t="s">
-        <v>30</v>
+      <c r="G181" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6193,11 +6193,11 @@
       <c r="E182">
         <v>6</v>
       </c>
-      <c r="F182" s="6">
+      <c r="F182" s="2">
         <v>6</v>
       </c>
-      <c r="G182" s="7" t="s">
-        <v>30</v>
+      <c r="G182" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6285,11 +6285,11 @@
       <c r="E186">
         <v>20</v>
       </c>
-      <c r="F186" s="6">
+      <c r="F186" s="2">
         <v>40</v>
       </c>
-      <c r="G186" s="7" t="s">
-        <v>30</v>
+      <c r="G186" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -6308,11 +6308,11 @@
       <c r="E187">
         <v>56</v>
       </c>
-      <c r="F187" s="6">
+      <c r="F187" s="2">
         <v>20</v>
       </c>
-      <c r="G187" s="7" t="s">
-        <v>30</v>
+      <c r="G187" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -6331,11 +6331,11 @@
       <c r="E188">
         <v>50</v>
       </c>
-      <c r="F188" s="6">
+      <c r="F188" s="2">
         <v>17</v>
       </c>
-      <c r="G188" s="7" t="s">
-        <v>30</v>
+      <c r="G188" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -43,66 +43,69 @@
     <t>LIGAS N° 18 - 80 MM X 2 MM X 1 LBS - NATURAL - ALLEANZA</t>
   </si>
   <si>
+    <t>✗ AGOTADO</t>
+  </si>
+  <si>
+    <t>85007</t>
+  </si>
+  <si>
+    <t>7754807850063</t>
+  </si>
+  <si>
+    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - NATURAL - ALLEANZA</t>
+  </si>
+  <si>
+    <t>✓ OK</t>
+  </si>
+  <si>
+    <t>85768</t>
+  </si>
+  <si>
+    <t>7754807857680</t>
+  </si>
+  <si>
+    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - VERDE - ALLEANZA</t>
+  </si>
+  <si>
+    <t>85008</t>
+  </si>
+  <si>
+    <t>7754807850087</t>
+  </si>
+  <si>
+    <t>LIGAS N° 78 - 140 MM X 10 MM X 1 LBS - NATURAL - ALLEANZA</t>
+  </si>
+  <si>
+    <t>85801</t>
+  </si>
+  <si>
+    <t>7754807857024</t>
+  </si>
+  <si>
+    <t>ALFILER ALLEANZA 35 MM CAJA X 50 GR</t>
+  </si>
+  <si>
+    <t>85163</t>
+  </si>
+  <si>
+    <t>091511400595</t>
+  </si>
+  <si>
+    <t>CUCHILLA ARTE AK-1/5B</t>
+  </si>
+  <si>
+    <t>85164</t>
+  </si>
+  <si>
+    <t>091511400670</t>
+  </si>
+  <si>
+    <t>CUCHILLA ARTE AK-4</t>
+  </si>
+  <si>
     <t>⚠ BAJO</t>
   </si>
   <si>
-    <t>85007</t>
-  </si>
-  <si>
-    <t>7754807850063</t>
-  </si>
-  <si>
-    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - NATURAL - ALLEANZA</t>
-  </si>
-  <si>
-    <t>✓ OK</t>
-  </si>
-  <si>
-    <t>85768</t>
-  </si>
-  <si>
-    <t>7754807857680</t>
-  </si>
-  <si>
-    <t>LIGAS N° 18 - 80 MM X 2 MM X 1/4 LBS - VERDE - ALLEANZA</t>
-  </si>
-  <si>
-    <t>85008</t>
-  </si>
-  <si>
-    <t>7754807850087</t>
-  </si>
-  <si>
-    <t>LIGAS N° 78 - 140 MM X 10 MM X 1 LBS - NATURAL - ALLEANZA</t>
-  </si>
-  <si>
-    <t>85801</t>
-  </si>
-  <si>
-    <t>7754807857024</t>
-  </si>
-  <si>
-    <t>ALFILER ALLEANZA 35 MM CAJA X 50 GR</t>
-  </si>
-  <si>
-    <t>85163</t>
-  </si>
-  <si>
-    <t>091511400595</t>
-  </si>
-  <si>
-    <t>CUCHILLA ARTE AK-1/5B</t>
-  </si>
-  <si>
-    <t>85164</t>
-  </si>
-  <si>
-    <t>091511400670</t>
-  </si>
-  <si>
-    <t>CUCHILLA ARTE AK-4</t>
-  </si>
-  <si>
     <t>85770</t>
   </si>
   <si>
@@ -125,9 +128,6 @@
   </si>
   <si>
     <t>CUCHILLLA DE ARTE AK-5/5B</t>
-  </si>
-  <si>
-    <t>✗ AGOTADO</t>
   </si>
   <si>
     <t>85166</t>
@@ -1587,7 +1587,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFD97706"/>
+      <color rgb="FFDC2626"/>
       <sz val="12"/>
     </font>
     <font>
@@ -1597,7 +1597,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFDC2626"/>
+      <color rgb="FFD97706"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -1615,7 +1615,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
+        <fgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1625,7 +1625,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
+        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
   </fills>
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2191,11 +2191,11 @@
       <c r="E8">
         <v>120</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="6">
         <v>247</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
+      <c r="G8" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2203,22 +2203,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9">
         <v>240</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="6">
         <v>253</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
+      <c r="G9" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2226,22 +2226,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E10">
         <v>200</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="6">
         <v>49</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>10</v>
+      <c r="G10" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2249,22 +2249,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E11">
         <v>240</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="2">
         <v>0</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>38</v>
+      <c r="G11" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2283,11 +2283,11 @@
       <c r="E12">
         <v>60</v>
       </c>
-      <c r="F12" s="2">
-        <v>103</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
+      <c r="F12" s="6">
+        <v>103</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2306,11 +2306,11 @@
       <c r="E13">
         <v>120</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="6">
         <v>117</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
+      <c r="G13" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2329,11 +2329,11 @@
       <c r="E14">
         <v>120</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="6">
         <v>167</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="G14" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2352,11 +2352,11 @@
       <c r="E15">
         <v>120</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="6">
         <v>84</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>10</v>
+      <c r="G15" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2375,11 +2375,11 @@
       <c r="E16">
         <v>120</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="6">
         <v>587</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>10</v>
+      <c r="G16" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2398,11 +2398,11 @@
       <c r="E17">
         <v>120</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="6">
         <v>250</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>10</v>
+      <c r="G17" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2444,11 +2444,11 @@
       <c r="E19">
         <v>120</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="6">
         <v>105</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>10</v>
+      <c r="G19" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2467,11 +2467,11 @@
       <c r="E20">
         <v>120</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="6">
         <v>75</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>10</v>
+      <c r="G20" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2490,11 +2490,11 @@
       <c r="E21">
         <v>120</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="2">
         <v>0</v>
       </c>
-      <c r="G21" s="7" t="s">
-        <v>38</v>
+      <c r="G21" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2536,11 +2536,11 @@
       <c r="E23">
         <v>60</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="2">
         <v>0</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>38</v>
+      <c r="G23" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2559,11 +2559,11 @@
       <c r="E24">
         <v>120</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="6">
         <v>89</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>10</v>
+      <c r="G24" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2582,11 +2582,11 @@
       <c r="E25">
         <v>120</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="6">
         <v>228</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>10</v>
+      <c r="G25" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2605,11 +2605,11 @@
       <c r="E26">
         <v>120</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="6">
         <v>93</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>10</v>
+      <c r="G26" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2628,11 +2628,11 @@
       <c r="E27">
         <v>120</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="6">
         <v>159</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>10</v>
+      <c r="G27" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2674,11 +2674,11 @@
       <c r="E29">
         <v>72</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="6">
         <v>92</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>10</v>
+      <c r="G29" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2697,11 +2697,11 @@
       <c r="E30">
         <v>120</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="6">
         <v>6</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>10</v>
+      <c r="G30" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2766,11 +2766,11 @@
       <c r="E33">
         <v>144</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="2">
         <v>0</v>
       </c>
-      <c r="G33" s="7" t="s">
-        <v>38</v>
+      <c r="G33" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2812,11 +2812,11 @@
       <c r="E35">
         <v>128</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F35" s="2">
         <v>0</v>
       </c>
-      <c r="G35" s="7" t="s">
-        <v>38</v>
+      <c r="G35" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2835,11 +2835,11 @@
       <c r="E36">
         <v>120</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="6">
         <v>118</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>10</v>
+      <c r="G36" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2858,11 +2858,11 @@
       <c r="E37">
         <v>240</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="6">
         <v>474</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>10</v>
+      <c r="G37" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2881,11 +2881,11 @@
       <c r="E38">
         <v>120</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="6">
         <v>123</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>10</v>
+      <c r="G38" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2904,11 +2904,11 @@
       <c r="E39">
         <v>240</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="6">
         <v>224</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>10</v>
+      <c r="G39" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2927,11 +2927,11 @@
       <c r="E40">
         <v>240</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="6">
         <v>225</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>10</v>
+      <c r="G40" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2950,11 +2950,11 @@
       <c r="E41">
         <v>240</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="6">
         <v>53</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>10</v>
+      <c r="G41" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2973,11 +2973,11 @@
       <c r="E42">
         <v>240</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="6">
         <v>255</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>10</v>
+      <c r="G42" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3019,11 +3019,11 @@
       <c r="E44">
         <v>480</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="6">
         <v>913</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>10</v>
+      <c r="G44" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3042,11 +3042,11 @@
       <c r="E45">
         <v>240</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="6">
         <v>127</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>10</v>
+      <c r="G45" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3065,11 +3065,11 @@
       <c r="E46">
         <v>800</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="6">
         <v>179</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>10</v>
+      <c r="G46" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3088,11 +3088,11 @@
       <c r="E47">
         <v>240</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="6">
         <v>85</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>10</v>
+      <c r="G47" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3111,11 +3111,11 @@
       <c r="E48">
         <v>120</v>
       </c>
-      <c r="F48" s="6">
+      <c r="F48" s="2">
         <v>0</v>
       </c>
-      <c r="G48" s="7" t="s">
-        <v>38</v>
+      <c r="G48" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3134,11 +3134,11 @@
       <c r="E49">
         <v>120</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="6">
         <v>255</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>10</v>
+      <c r="G49" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3157,11 +3157,11 @@
       <c r="E50">
         <v>120</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="6">
         <v>285</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>10</v>
+      <c r="G50" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3180,11 +3180,11 @@
       <c r="E51">
         <v>10</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="6">
         <v>5</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>10</v>
+      <c r="G51" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3203,11 +3203,11 @@
       <c r="E52">
         <v>60</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="6">
         <v>80</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>10</v>
+      <c r="G52" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3226,11 +3226,11 @@
       <c r="E53">
         <v>20</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="6">
         <v>27</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>10</v>
+      <c r="G53" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3249,11 +3249,11 @@
       <c r="E54">
         <v>720</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="6">
         <v>1634</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>10</v>
+      <c r="G54" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3272,11 +3272,11 @@
       <c r="E55">
         <v>120</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="6">
         <v>68</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>10</v>
+      <c r="G55" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -3295,11 +3295,11 @@
       <c r="E56">
         <v>120</v>
       </c>
-      <c r="F56" s="6">
+      <c r="F56" s="2">
         <v>0</v>
       </c>
-      <c r="G56" s="7" t="s">
-        <v>38</v>
+      <c r="G56" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3318,11 +3318,11 @@
       <c r="E57">
         <v>720</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="6">
         <v>828</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>10</v>
+      <c r="G57" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -3341,11 +3341,11 @@
       <c r="E58">
         <v>240</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="6">
         <v>189</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>10</v>
+      <c r="G58" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3364,11 +3364,11 @@
       <c r="E59">
         <v>120</v>
       </c>
-      <c r="F59" s="6">
+      <c r="F59" s="2">
         <v>0</v>
       </c>
-      <c r="G59" s="7" t="s">
-        <v>38</v>
+      <c r="G59" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3387,11 +3387,11 @@
       <c r="E60">
         <v>240</v>
       </c>
-      <c r="F60" s="6">
+      <c r="F60" s="2">
         <v>0</v>
       </c>
-      <c r="G60" s="7" t="s">
-        <v>38</v>
+      <c r="G60" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3410,11 +3410,11 @@
       <c r="E61">
         <v>240</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="6">
         <v>216</v>
       </c>
-      <c r="G61" s="3" t="s">
-        <v>10</v>
+      <c r="G61" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3433,11 +3433,11 @@
       <c r="E62">
         <v>240</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="6">
         <v>198</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>10</v>
+      <c r="G62" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3502,11 +3502,11 @@
       <c r="E65">
         <v>60</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="6">
         <v>53</v>
       </c>
-      <c r="G65" s="3" t="s">
-        <v>10</v>
+      <c r="G65" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3525,11 +3525,11 @@
       <c r="E66">
         <v>120</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="6">
         <v>21</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>10</v>
+      <c r="G66" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3548,11 +3548,11 @@
       <c r="E67">
         <v>240</v>
       </c>
-      <c r="F67" s="6">
+      <c r="F67" s="2">
         <v>0</v>
       </c>
-      <c r="G67" s="7" t="s">
-        <v>38</v>
+      <c r="G67" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3571,11 +3571,11 @@
       <c r="E68">
         <v>240</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="6">
         <v>50</v>
       </c>
-      <c r="G68" s="3" t="s">
-        <v>10</v>
+      <c r="G68" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3617,11 +3617,11 @@
       <c r="E70">
         <v>240</v>
       </c>
-      <c r="F70" s="6">
+      <c r="F70" s="2">
         <v>0</v>
       </c>
-      <c r="G70" s="7" t="s">
-        <v>38</v>
+      <c r="G70" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3640,11 +3640,11 @@
       <c r="E71">
         <v>240</v>
       </c>
-      <c r="F71" s="6">
+      <c r="F71" s="2">
         <v>0</v>
       </c>
-      <c r="G71" s="7" t="s">
-        <v>38</v>
+      <c r="G71" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3663,11 +3663,11 @@
       <c r="E72">
         <v>480</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="6">
         <v>314</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>10</v>
+      <c r="G72" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3686,11 +3686,11 @@
       <c r="E73">
         <v>240</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="6">
         <v>488</v>
       </c>
-      <c r="G73" s="3" t="s">
-        <v>10</v>
+      <c r="G73" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3709,11 +3709,11 @@
       <c r="E74">
         <v>240</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="6">
         <v>606</v>
       </c>
-      <c r="G74" s="3" t="s">
-        <v>10</v>
+      <c r="G74" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -3755,11 +3755,11 @@
       <c r="E76">
         <v>240</v>
       </c>
-      <c r="F76" s="6">
+      <c r="F76" s="2">
         <v>0</v>
       </c>
-      <c r="G76" s="7" t="s">
-        <v>38</v>
+      <c r="G76" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -3778,11 +3778,11 @@
       <c r="E77">
         <v>600</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77" s="6">
         <v>509</v>
       </c>
-      <c r="G77" s="3" t="s">
-        <v>10</v>
+      <c r="G77" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -3801,11 +3801,11 @@
       <c r="E78">
         <v>120</v>
       </c>
-      <c r="F78" s="2">
+      <c r="F78" s="6">
         <v>109</v>
       </c>
-      <c r="G78" s="3" t="s">
-        <v>10</v>
+      <c r="G78" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -3824,11 +3824,11 @@
       <c r="E79">
         <v>120</v>
       </c>
-      <c r="F79" s="6">
+      <c r="F79" s="2">
         <v>0</v>
       </c>
-      <c r="G79" s="7" t="s">
-        <v>38</v>
+      <c r="G79" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3847,11 +3847,11 @@
       <c r="E80">
         <v>60</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80" s="6">
         <v>12</v>
       </c>
-      <c r="G80" s="3" t="s">
-        <v>10</v>
+      <c r="G80" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3916,11 +3916,11 @@
       <c r="E83">
         <v>40</v>
       </c>
-      <c r="F83" s="6">
+      <c r="F83" s="2">
         <v>0</v>
       </c>
-      <c r="G83" s="7" t="s">
-        <v>38</v>
+      <c r="G83" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -3962,11 +3962,11 @@
       <c r="E85">
         <v>40</v>
       </c>
-      <c r="F85" s="6">
+      <c r="F85" s="2">
         <v>0</v>
       </c>
-      <c r="G85" s="7" t="s">
-        <v>38</v>
+      <c r="G85" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -3985,11 +3985,11 @@
       <c r="E86">
         <v>40</v>
       </c>
-      <c r="F86" s="2">
+      <c r="F86" s="6">
         <v>4</v>
       </c>
-      <c r="G86" s="3" t="s">
-        <v>10</v>
+      <c r="G86" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4008,11 +4008,11 @@
       <c r="E87">
         <v>40</v>
       </c>
-      <c r="F87" s="6">
+      <c r="F87" s="2">
         <v>0</v>
       </c>
-      <c r="G87" s="7" t="s">
-        <v>38</v>
+      <c r="G87" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4031,11 +4031,11 @@
       <c r="E88">
         <v>20</v>
       </c>
-      <c r="F88" s="6">
+      <c r="F88" s="2">
         <v>0</v>
       </c>
-      <c r="G88" s="7" t="s">
-        <v>38</v>
+      <c r="G88" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4192,11 +4192,11 @@
       <c r="E95">
         <v>120</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="6">
         <v>38</v>
       </c>
-      <c r="G95" s="3" t="s">
-        <v>10</v>
+      <c r="G95" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4215,11 +4215,11 @@
       <c r="E96">
         <v>120</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="6">
         <v>4</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>10</v>
+      <c r="G96" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -4238,11 +4238,11 @@
       <c r="E97">
         <v>10</v>
       </c>
-      <c r="F97" s="2">
+      <c r="F97" s="6">
         <v>7</v>
       </c>
-      <c r="G97" s="3" t="s">
-        <v>10</v>
+      <c r="G97" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4261,11 +4261,11 @@
       <c r="E98">
         <v>5</v>
       </c>
-      <c r="F98" s="6">
+      <c r="F98" s="2">
         <v>0</v>
       </c>
-      <c r="G98" s="7" t="s">
-        <v>38</v>
+      <c r="G98" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4399,11 +4399,11 @@
       <c r="E104">
         <v>200</v>
       </c>
-      <c r="F104" s="2">
+      <c r="F104" s="6">
         <v>4</v>
       </c>
-      <c r="G104" s="3" t="s">
-        <v>10</v>
+      <c r="G104" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -4445,11 +4445,11 @@
       <c r="E106">
         <v>120</v>
       </c>
-      <c r="F106" s="6">
+      <c r="F106" s="2">
         <v>0</v>
       </c>
-      <c r="G106" s="7" t="s">
-        <v>38</v>
+      <c r="G106" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4468,11 +4468,11 @@
       <c r="E107">
         <v>120</v>
       </c>
-      <c r="F107" s="2">
+      <c r="F107" s="6">
         <v>1</v>
       </c>
-      <c r="G107" s="3" t="s">
-        <v>10</v>
+      <c r="G107" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -4491,11 +4491,11 @@
       <c r="E108">
         <v>18</v>
       </c>
-      <c r="F108" s="2">
+      <c r="F108" s="6">
         <v>79</v>
       </c>
-      <c r="G108" s="3" t="s">
-        <v>10</v>
+      <c r="G108" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -4514,11 +4514,11 @@
       <c r="E109">
         <v>6</v>
       </c>
-      <c r="F109" s="6">
+      <c r="F109" s="2">
         <v>0</v>
       </c>
-      <c r="G109" s="7" t="s">
-        <v>38</v>
+      <c r="G109" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -4537,11 +4537,11 @@
       <c r="E110">
         <v>54</v>
       </c>
-      <c r="F110" s="2">
+      <c r="F110" s="6">
         <v>27</v>
       </c>
-      <c r="G110" s="3" t="s">
-        <v>10</v>
+      <c r="G110" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -4560,11 +4560,11 @@
       <c r="E111">
         <v>10</v>
       </c>
-      <c r="F111" s="6">
+      <c r="F111" s="2">
         <v>0</v>
       </c>
-      <c r="G111" s="7" t="s">
-        <v>38</v>
+      <c r="G111" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -4583,11 +4583,11 @@
       <c r="E112">
         <v>12</v>
       </c>
-      <c r="F112" s="6">
+      <c r="F112" s="2">
         <v>0</v>
       </c>
-      <c r="G112" s="7" t="s">
-        <v>38</v>
+      <c r="G112" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -4606,11 +4606,11 @@
       <c r="E113">
         <v>12</v>
       </c>
-      <c r="F113" s="6">
+      <c r="F113" s="2">
         <v>0</v>
       </c>
-      <c r="G113" s="7" t="s">
-        <v>38</v>
+      <c r="G113" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -4652,11 +4652,11 @@
       <c r="E115">
         <v>800</v>
       </c>
-      <c r="F115" s="2">
+      <c r="F115" s="6">
         <v>262</v>
       </c>
-      <c r="G115" s="3" t="s">
-        <v>10</v>
+      <c r="G115" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -4675,11 +4675,11 @@
       <c r="E116">
         <v>5</v>
       </c>
-      <c r="F116" s="6">
+      <c r="F116" s="2">
         <v>0</v>
       </c>
-      <c r="G116" s="7" t="s">
-        <v>38</v>
+      <c r="G116" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -4698,11 +4698,11 @@
       <c r="E117">
         <v>5</v>
       </c>
-      <c r="F117" s="2">
+      <c r="F117" s="6">
         <v>2</v>
       </c>
-      <c r="G117" s="3" t="s">
-        <v>10</v>
+      <c r="G117" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -4744,11 +4744,11 @@
       <c r="E119">
         <v>10</v>
       </c>
-      <c r="F119" s="2">
+      <c r="F119" s="6">
         <v>6</v>
       </c>
-      <c r="G119" s="3" t="s">
-        <v>10</v>
+      <c r="G119" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -4767,11 +4767,11 @@
       <c r="E120">
         <v>10</v>
       </c>
-      <c r="F120" s="2">
+      <c r="F120" s="6">
         <v>36</v>
       </c>
-      <c r="G120" s="3" t="s">
-        <v>10</v>
+      <c r="G120" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -4790,11 +4790,11 @@
       <c r="E121">
         <v>6</v>
       </c>
-      <c r="F121" s="6">
+      <c r="F121" s="2">
         <v>0</v>
       </c>
-      <c r="G121" s="7" t="s">
-        <v>38</v>
+      <c r="G121" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -4813,11 +4813,11 @@
       <c r="E122">
         <v>6</v>
       </c>
-      <c r="F122" s="6">
+      <c r="F122" s="2">
         <v>0</v>
       </c>
-      <c r="G122" s="7" t="s">
-        <v>38</v>
+      <c r="G122" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -4836,11 +4836,11 @@
       <c r="E123">
         <v>40</v>
       </c>
-      <c r="F123" s="2">
+      <c r="F123" s="6">
         <v>127</v>
       </c>
-      <c r="G123" s="3" t="s">
-        <v>10</v>
+      <c r="G123" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -4882,11 +4882,11 @@
       <c r="E125">
         <v>1</v>
       </c>
-      <c r="F125" s="6">
+      <c r="F125" s="2">
         <v>0</v>
       </c>
-      <c r="G125" s="7" t="s">
-        <v>38</v>
+      <c r="G125" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -4905,11 +4905,11 @@
       <c r="E126">
         <v>4</v>
       </c>
-      <c r="F126" s="2">
+      <c r="F126" s="6">
         <v>17</v>
       </c>
-      <c r="G126" s="3" t="s">
-        <v>10</v>
+      <c r="G126" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -4951,11 +4951,11 @@
       <c r="E128">
         <v>4</v>
       </c>
-      <c r="F128" s="2">
+      <c r="F128" s="6">
         <v>18</v>
       </c>
-      <c r="G128" s="3" t="s">
-        <v>10</v>
+      <c r="G128" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -4974,11 +4974,11 @@
       <c r="E129">
         <v>1</v>
       </c>
-      <c r="F129" s="2">
+      <c r="F129" s="6">
         <v>3</v>
       </c>
-      <c r="G129" s="3" t="s">
-        <v>10</v>
+      <c r="G129" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -4997,11 +4997,11 @@
       <c r="E130">
         <v>60</v>
       </c>
-      <c r="F130" s="2">
+      <c r="F130" s="6">
         <v>3</v>
       </c>
-      <c r="G130" s="3" t="s">
-        <v>10</v>
+      <c r="G130" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5043,11 +5043,11 @@
       <c r="E132">
         <v>60</v>
       </c>
-      <c r="F132" s="2">
+      <c r="F132" s="6">
         <v>58</v>
       </c>
-      <c r="G132" s="3" t="s">
-        <v>10</v>
+      <c r="G132" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -5066,11 +5066,11 @@
       <c r="E133">
         <v>60</v>
       </c>
-      <c r="F133" s="2">
+      <c r="F133" s="6">
         <v>138</v>
       </c>
-      <c r="G133" s="3" t="s">
-        <v>10</v>
+      <c r="G133" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5250,11 +5250,11 @@
       <c r="E141">
         <v>40</v>
       </c>
-      <c r="F141" s="2">
+      <c r="F141" s="6">
         <v>108</v>
       </c>
-      <c r="G141" s="3" t="s">
-        <v>10</v>
+      <c r="G141" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -5273,11 +5273,11 @@
       <c r="E142">
         <v>60</v>
       </c>
-      <c r="F142" s="2">
+      <c r="F142" s="6">
         <v>122</v>
       </c>
-      <c r="G142" s="3" t="s">
-        <v>10</v>
+      <c r="G142" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -5296,11 +5296,11 @@
       <c r="E143">
         <v>6</v>
       </c>
-      <c r="F143" s="2">
+      <c r="F143" s="6">
         <v>15</v>
       </c>
-      <c r="G143" s="3" t="s">
-        <v>10</v>
+      <c r="G143" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -5319,11 +5319,11 @@
       <c r="E144">
         <v>18</v>
       </c>
-      <c r="F144" s="6">
+      <c r="F144" s="2">
         <v>0</v>
       </c>
-      <c r="G144" s="7" t="s">
-        <v>38</v>
+      <c r="G144" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -5342,11 +5342,11 @@
       <c r="E145">
         <v>8</v>
       </c>
-      <c r="F145" s="2">
+      <c r="F145" s="6">
         <v>8</v>
       </c>
-      <c r="G145" s="3" t="s">
-        <v>10</v>
+      <c r="G145" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -5365,11 +5365,11 @@
       <c r="E146">
         <v>30</v>
       </c>
-      <c r="F146" s="2">
+      <c r="F146" s="6">
         <v>34</v>
       </c>
-      <c r="G146" s="3" t="s">
-        <v>10</v>
+      <c r="G146" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -5388,11 +5388,11 @@
       <c r="E147">
         <v>2</v>
       </c>
-      <c r="F147" s="6">
+      <c r="F147" s="2">
         <v>0</v>
       </c>
-      <c r="G147" s="7" t="s">
-        <v>38</v>
+      <c r="G147" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -5503,11 +5503,11 @@
       <c r="E152">
         <v>20</v>
       </c>
-      <c r="F152" s="2">
+      <c r="F152" s="6">
         <v>8</v>
       </c>
-      <c r="G152" s="3" t="s">
-        <v>10</v>
+      <c r="G152" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -5526,11 +5526,11 @@
       <c r="E153">
         <v>240</v>
       </c>
-      <c r="F153" s="2">
+      <c r="F153" s="6">
         <v>598</v>
       </c>
-      <c r="G153" s="3" t="s">
-        <v>10</v>
+      <c r="G153" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -5549,11 +5549,11 @@
       <c r="E154">
         <v>120</v>
       </c>
-      <c r="F154" s="2">
+      <c r="F154" s="6">
         <v>121</v>
       </c>
-      <c r="G154" s="3" t="s">
-        <v>10</v>
+      <c r="G154" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -5595,11 +5595,11 @@
       <c r="E156">
         <v>120</v>
       </c>
-      <c r="F156" s="6">
+      <c r="F156" s="2">
         <v>0</v>
       </c>
-      <c r="G156" s="7" t="s">
-        <v>38</v>
+      <c r="G156" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -5618,11 +5618,11 @@
       <c r="E157">
         <v>72</v>
       </c>
-      <c r="F157" s="2">
+      <c r="F157" s="6">
         <v>50</v>
       </c>
-      <c r="G157" s="3" t="s">
-        <v>10</v>
+      <c r="G157" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -5641,11 +5641,11 @@
       <c r="E158">
         <v>60</v>
       </c>
-      <c r="F158" s="2">
-        <v>30</v>
-      </c>
-      <c r="G158" s="3" t="s">
-        <v>10</v>
+      <c r="F158" s="6">
+        <v>30</v>
+      </c>
+      <c r="G158" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -5664,11 +5664,11 @@
       <c r="E159">
         <v>120</v>
       </c>
-      <c r="F159" s="2">
+      <c r="F159" s="6">
         <v>71</v>
       </c>
-      <c r="G159" s="3" t="s">
-        <v>10</v>
+      <c r="G159" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -5687,11 +5687,11 @@
       <c r="E160">
         <v>72</v>
       </c>
-      <c r="F160" s="2">
+      <c r="F160" s="6">
         <v>10</v>
       </c>
-      <c r="G160" s="3" t="s">
-        <v>10</v>
+      <c r="G160" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -5710,11 +5710,11 @@
       <c r="E161">
         <v>20</v>
       </c>
-      <c r="F161" s="2">
+      <c r="F161" s="6">
         <v>44</v>
       </c>
-      <c r="G161" s="3" t="s">
-        <v>10</v>
+      <c r="G161" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -5733,11 +5733,11 @@
       <c r="E162">
         <v>100</v>
       </c>
-      <c r="F162" s="2">
+      <c r="F162" s="6">
         <v>74</v>
       </c>
-      <c r="G162" s="3" t="s">
-        <v>10</v>
+      <c r="G162" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -5756,11 +5756,11 @@
       <c r="E163">
         <v>5</v>
       </c>
-      <c r="F163" s="2">
+      <c r="F163" s="6">
         <v>11</v>
       </c>
-      <c r="G163" s="3" t="s">
-        <v>10</v>
+      <c r="G163" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -5779,11 +5779,11 @@
       <c r="E164">
         <v>10</v>
       </c>
-      <c r="F164" s="2">
+      <c r="F164" s="6">
         <v>4</v>
       </c>
-      <c r="G164" s="3" t="s">
-        <v>10</v>
+      <c r="G164" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -5802,11 +5802,11 @@
       <c r="E165">
         <v>20</v>
       </c>
-      <c r="F165" s="2">
+      <c r="F165" s="6">
         <v>35</v>
       </c>
-      <c r="G165" s="3" t="s">
-        <v>10</v>
+      <c r="G165" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -5825,11 +5825,11 @@
       <c r="E166">
         <v>20</v>
       </c>
-      <c r="F166" s="2">
+      <c r="F166" s="6">
         <v>57</v>
       </c>
-      <c r="G166" s="3" t="s">
-        <v>10</v>
+      <c r="G166" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -5848,11 +5848,11 @@
       <c r="E167">
         <v>24</v>
       </c>
-      <c r="F167" s="2">
+      <c r="F167" s="6">
         <v>28</v>
       </c>
-      <c r="G167" s="3" t="s">
-        <v>10</v>
+      <c r="G167" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -5871,11 +5871,11 @@
       <c r="E168">
         <v>240</v>
       </c>
-      <c r="F168" s="2">
+      <c r="F168" s="6">
         <v>920</v>
       </c>
-      <c r="G168" s="3" t="s">
-        <v>10</v>
+      <c r="G168" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -5894,11 +5894,11 @@
       <c r="E169">
         <v>240</v>
       </c>
-      <c r="F169" s="2">
+      <c r="F169" s="6">
         <v>102</v>
       </c>
-      <c r="G169" s="3" t="s">
-        <v>10</v>
+      <c r="G169" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -5917,11 +5917,11 @@
       <c r="E170">
         <v>480</v>
       </c>
-      <c r="F170" s="2">
+      <c r="F170" s="6">
         <v>211</v>
       </c>
-      <c r="G170" s="3" t="s">
-        <v>10</v>
+      <c r="G170" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -5963,11 +5963,11 @@
       <c r="E172">
         <v>240</v>
       </c>
-      <c r="F172" s="2">
+      <c r="F172" s="6">
         <v>25</v>
       </c>
-      <c r="G172" s="3" t="s">
-        <v>10</v>
+      <c r="G172" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -5986,11 +5986,11 @@
       <c r="E173">
         <v>240</v>
       </c>
-      <c r="F173" s="2">
+      <c r="F173" s="6">
         <v>81</v>
       </c>
-      <c r="G173" s="3" t="s">
-        <v>10</v>
+      <c r="G173" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -6009,11 +6009,11 @@
       <c r="E174">
         <v>480</v>
       </c>
-      <c r="F174" s="2">
+      <c r="F174" s="6">
         <v>378</v>
       </c>
-      <c r="G174" s="3" t="s">
-        <v>10</v>
+      <c r="G174" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -6032,11 +6032,11 @@
       <c r="E175">
         <v>120</v>
       </c>
-      <c r="F175" s="2">
+      <c r="F175" s="6">
         <v>94</v>
       </c>
-      <c r="G175" s="3" t="s">
-        <v>10</v>
+      <c r="G175" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -6055,11 +6055,11 @@
       <c r="E176">
         <v>120</v>
       </c>
-      <c r="F176" s="2">
-        <v>103</v>
-      </c>
-      <c r="G176" s="3" t="s">
-        <v>10</v>
+      <c r="F176" s="6">
+        <v>103</v>
+      </c>
+      <c r="G176" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -6078,11 +6078,11 @@
       <c r="E177">
         <v>120</v>
       </c>
-      <c r="F177" s="2">
+      <c r="F177" s="6">
         <v>72</v>
       </c>
-      <c r="G177" s="3" t="s">
-        <v>10</v>
+      <c r="G177" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -6147,11 +6147,11 @@
       <c r="E180">
         <v>30</v>
       </c>
-      <c r="F180" s="6">
+      <c r="F180" s="2">
         <v>0</v>
       </c>
-      <c r="G180" s="7" t="s">
-        <v>38</v>
+      <c r="G180" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -6170,11 +6170,11 @@
       <c r="E181">
         <v>12</v>
       </c>
-      <c r="F181" s="2">
+      <c r="F181" s="6">
         <v>4</v>
       </c>
-      <c r="G181" s="3" t="s">
-        <v>10</v>
+      <c r="G181" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -6193,11 +6193,11 @@
       <c r="E182">
         <v>6</v>
       </c>
-      <c r="F182" s="2">
+      <c r="F182" s="6">
         <v>6</v>
       </c>
-      <c r="G182" s="3" t="s">
-        <v>10</v>
+      <c r="G182" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -6285,11 +6285,11 @@
       <c r="E186">
         <v>20</v>
       </c>
-      <c r="F186" s="2">
+      <c r="F186" s="6">
         <v>40</v>
       </c>
-      <c r="G186" s="3" t="s">
-        <v>10</v>
+      <c r="G186" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -6308,11 +6308,11 @@
       <c r="E187">
         <v>56</v>
       </c>
-      <c r="F187" s="2">
+      <c r="F187" s="6">
         <v>20</v>
       </c>
-      <c r="G187" s="3" t="s">
-        <v>10</v>
+      <c r="G187" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -6331,11 +6331,11 @@
       <c r="E188">
         <v>50</v>
       </c>
-      <c r="F188" s="2">
+      <c r="F188" s="6">
         <v>17</v>
       </c>
-      <c r="G188" s="3" t="s">
-        <v>10</v>
+      <c r="G188" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="4">
-        <v>6451</v>
+        <v>6331</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>14</v>
@@ -4055,7 +4055,7 @@
         <v>20</v>
       </c>
       <c r="F89" s="4">
-        <v>1461</v>
+        <v>1450</v>
       </c>
       <c r="G89" s="5" t="s">
         <v>14</v>
@@ -4078,7 +4078,7 @@
         <v>100</v>
       </c>
       <c r="F90" s="4">
-        <v>78470</v>
+        <v>78432</v>
       </c>
       <c r="G90" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="4">
-        <v>16217</v>
+        <v>16137</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2583,7 +2583,7 @@
         <v>120</v>
       </c>
       <c r="F25" s="6">
-        <v>228</v>
+        <v>168</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>30</v>
@@ -3020,7 +3020,7 @@
         <v>480</v>
       </c>
       <c r="F44" s="6">
-        <v>901</v>
+        <v>841</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>30</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2721,7 +2721,7 @@
         <v>120</v>
       </c>
       <c r="F31" s="4">
-        <v>1265</v>
+        <v>1256</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>14</v>
@@ -3319,7 +3319,7 @@
         <v>720</v>
       </c>
       <c r="F57" s="6">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>30</v>
@@ -3733,7 +3733,7 @@
         <v>240</v>
       </c>
       <c r="F75" s="4">
-        <v>3255</v>
+        <v>3238</v>
       </c>
       <c r="G75" s="5" t="s">
         <v>14</v>
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="4">
-        <v>6201</v>
+        <v>6041</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>14</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2169,7 +2169,7 @@
         <v>120</v>
       </c>
       <c r="F7" s="4">
-        <v>688</v>
+        <v>652</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>14</v>
@@ -2422,7 +2422,7 @@
         <v>120</v>
       </c>
       <c r="F18" s="4">
-        <v>834</v>
+        <v>774</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>14</v>
@@ -2514,7 +2514,7 @@
         <v>120</v>
       </c>
       <c r="F22" s="4">
-        <v>1175</v>
+        <v>1151</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>14</v>
@@ -2790,7 +2790,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="6">
-        <v>490</v>
+        <v>250</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>30</v>
@@ -3824,11 +3824,11 @@
       <c r="E79">
         <v>120</v>
       </c>
-      <c r="F79" s="2">
-        <v>0</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>10</v>
+      <c r="F79" s="6">
+        <v>110</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -4031,11 +4031,11 @@
       <c r="E88">
         <v>20</v>
       </c>
-      <c r="F88" s="2">
-        <v>0</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>10</v>
+      <c r="F88" s="4">
+        <v>244</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2123,7 +2123,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="4">
-        <v>6645</v>
+        <v>6782</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>14</v>
@@ -2652,7 +2652,7 @@
         <v>120</v>
       </c>
       <c r="F28" s="4">
-        <v>2997</v>
+        <v>2991</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>14</v>
@@ -2698,7 +2698,7 @@
         <v>120</v>
       </c>
       <c r="F30" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>30</v>
@@ -2744,7 +2744,7 @@
         <v>120</v>
       </c>
       <c r="F32" s="4">
-        <v>1191</v>
+        <v>1171</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>14</v>
@@ -3020,7 +3020,7 @@
         <v>480</v>
       </c>
       <c r="F44" s="6">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>30</v>
@@ -3089,7 +3089,7 @@
         <v>240</v>
       </c>
       <c r="F47" s="6">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>30</v>
@@ -3572,7 +3572,7 @@
         <v>240</v>
       </c>
       <c r="F68" s="6">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G68" s="7" t="s">
         <v>30</v>
@@ -3687,7 +3687,7 @@
         <v>240</v>
       </c>
       <c r="F73" s="6">
-        <v>488</v>
+        <v>468</v>
       </c>
       <c r="G73" s="7" t="s">
         <v>30</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>9488</v>
+        <v>15488</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>39467</v>
+        <v>48347</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2422,7 +2422,7 @@
         <v>120</v>
       </c>
       <c r="F18" s="2">
-        <v>702</v>
+        <v>690</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -2652,7 +2652,7 @@
         <v>120</v>
       </c>
       <c r="F28" s="2">
-        <v>2577</v>
+        <v>2457</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -2859,7 +2859,7 @@
         <v>240</v>
       </c>
       <c r="F37" s="4">
-        <v>474</v>
+        <v>350</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>29</v>
@@ -3020,7 +3020,7 @@
         <v>480</v>
       </c>
       <c r="F44" s="4">
-        <v>823</v>
+        <v>805</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>29</v>
@@ -3250,7 +3250,7 @@
         <v>720</v>
       </c>
       <c r="F54" s="4">
-        <v>1574</v>
+        <v>1550</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>29</v>
@@ -3595,7 +3595,7 @@
         <v>240</v>
       </c>
       <c r="F69" s="2">
-        <v>2714</v>
+        <v>2642</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>5699</v>
+        <v>5619</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>5619</v>
+        <v>5579</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2652,7 +2652,7 @@
         <v>120</v>
       </c>
       <c r="F28" s="2">
-        <v>2457</v>
+        <v>2421</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -2744,7 +2744,7 @@
         <v>120</v>
       </c>
       <c r="F32" s="2">
-        <v>1165</v>
+        <v>1159</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -3457,7 +3457,7 @@
         <v>240</v>
       </c>
       <c r="F63" s="2">
-        <v>1894</v>
+        <v>1870</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -3733,7 +3733,7 @@
         <v>240</v>
       </c>
       <c r="F75" s="2">
-        <v>3202</v>
+        <v>3166</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>5579</v>
+        <v>5559</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -5688,7 +5688,7 @@
         <v>72</v>
       </c>
       <c r="F160" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G160" s="5" t="s">
         <v>29</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2376,7 +2376,7 @@
         <v>120</v>
       </c>
       <c r="F16" s="4">
-        <v>563</v>
+        <v>527</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>29</v>
@@ -2422,7 +2422,7 @@
         <v>120</v>
       </c>
       <c r="F18" s="2">
-        <v>690</v>
+        <v>666</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -2652,7 +2652,7 @@
         <v>120</v>
       </c>
       <c r="F28" s="2">
-        <v>2391</v>
+        <v>2355</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -3595,7 +3595,7 @@
         <v>240</v>
       </c>
       <c r="F69" s="2">
-        <v>2606</v>
+        <v>2558</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>48027</v>
+        <v>47547</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>14887</v>
+        <v>14707</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>45067</v>
+        <v>44587</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>5336</v>
+        <v>5296</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -4078,7 +4078,7 @@
         <v>100</v>
       </c>
       <c r="F90" s="2">
-        <v>77432</v>
+        <v>77632</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>39307</v>
+        <v>37787</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -3456,11 +3456,11 @@
       <c r="E63">
         <v>240</v>
       </c>
-      <c r="F63" s="2">
-        <v>1315</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>10</v>
+      <c r="F63" s="4">
+        <v>1015</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>4176</v>
+        <v>3576</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -4101,7 +4101,7 @@
         <v>10</v>
       </c>
       <c r="F91" s="2">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -4147,7 +4147,7 @@
         <v>2</v>
       </c>
       <c r="F93" s="2">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -4078,7 +4078,7 @@
         <v>100</v>
       </c>
       <c r="F90" s="2">
-        <v>73932</v>
+        <v>73532</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>13257</v>
+        <v>13007</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>36987</v>
+        <v>36787</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2123,7 +2123,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>6152</v>
+        <v>5897</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -2652,7 +2652,7 @@
         <v>120</v>
       </c>
       <c r="F28" s="2">
-        <v>2055</v>
+        <v>2037</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -3319,7 +3319,7 @@
         <v>720</v>
       </c>
       <c r="F57" s="4">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>29</v>
@@ -3457,7 +3457,7 @@
         <v>240</v>
       </c>
       <c r="F63" s="4">
-        <v>1015</v>
+        <v>1003</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>29</v>
@@ -4170,7 +4170,7 @@
         <v>6</v>
       </c>
       <c r="F94" s="2">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -4261,11 +4261,11 @@
       <c r="E98">
         <v>5</v>
       </c>
-      <c r="F98" s="6">
-        <v>0</v>
-      </c>
-      <c r="G98" s="7" t="s">
-        <v>38</v>
+      <c r="F98" s="4">
+        <v>5</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2514,7 +2514,7 @@
         <v>120</v>
       </c>
       <c r="F22" s="2">
-        <v>933</v>
+        <v>873</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -3457,7 +3457,7 @@
         <v>240</v>
       </c>
       <c r="F63" s="4">
-        <v>979</v>
+        <v>907</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>29</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>11933</v>
+        <v>11843</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>100282</v>
+        <v>99882</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2744,7 +2744,7 @@
         <v>120</v>
       </c>
       <c r="F32" s="2">
-        <v>1114</v>
+        <v>1102</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -6056,7 +6056,7 @@
         <v>120</v>
       </c>
       <c r="F176" s="4">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G176" s="5" t="s">
         <v>29</v>
@@ -6079,7 +6079,7 @@
         <v>120</v>
       </c>
       <c r="F177" s="4">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="G177" s="5" t="s">
         <v>29</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>99882</v>
+        <v>99822</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2123,7 +2123,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>5597</v>
+        <v>5585</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -3250,7 +3250,7 @@
         <v>720</v>
       </c>
       <c r="F54" s="4">
-        <v>1382</v>
+        <v>1046</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>29</v>
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>3435</v>
+        <v>3395</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -4193,7 +4193,7 @@
         <v>120</v>
       </c>
       <c r="F95" s="4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G95" s="5" t="s">
         <v>29</v>
@@ -4215,11 +4215,11 @@
       <c r="E96">
         <v>120</v>
       </c>
-      <c r="F96" s="4">
-        <v>3</v>
-      </c>
-      <c r="G96" s="5" t="s">
-        <v>29</v>
+      <c r="F96" s="6">
+        <v>0</v>
+      </c>
+      <c r="G96" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2192,7 +2192,7 @@
         <v>120</v>
       </c>
       <c r="F8" s="4">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>29</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>99822</v>
+        <v>99022</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2376,7 +2376,7 @@
         <v>120</v>
       </c>
       <c r="F16" s="4">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>29</v>
@@ -3043,7 +3043,7 @@
         <v>240</v>
       </c>
       <c r="F45" s="4">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>29</v>
@@ -3595,7 +3595,7 @@
         <v>240</v>
       </c>
       <c r="F69" s="2">
-        <v>1748</v>
+        <v>1688</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>99022</v>
+        <v>99012</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2376,7 +2376,7 @@
         <v>120</v>
       </c>
       <c r="F16" s="4">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>29</v>
@@ -2422,7 +2422,7 @@
         <v>120</v>
       </c>
       <c r="F18" s="4">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>29</v>
@@ -2652,7 +2652,7 @@
         <v>120</v>
       </c>
       <c r="F28" s="2">
-        <v>1977</v>
+        <v>1965</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2123,7 +2123,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>5585</v>
+        <v>5435</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>3366</v>
+        <v>3350</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>99012</v>
+        <v>99072</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2376,7 +2376,7 @@
         <v>120</v>
       </c>
       <c r="F16" s="4">
-        <v>448</v>
+        <v>412</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>29</v>
@@ -2859,7 +2859,7 @@
         <v>240</v>
       </c>
       <c r="F37" s="4">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>29</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>11543</v>
+        <v>11343</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>99072</v>
+        <v>97392</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2721,7 +2721,7 @@
         <v>120</v>
       </c>
       <c r="F31" s="2">
-        <v>1175</v>
+        <v>1075</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -2744,7 +2744,7 @@
         <v>120</v>
       </c>
       <c r="F32" s="2">
-        <v>1102</v>
+        <v>1042</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -3733,7 +3733,7 @@
         <v>240</v>
       </c>
       <c r="F75" s="2">
-        <v>3001</v>
+        <v>2881</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -4078,7 +4078,7 @@
         <v>100</v>
       </c>
       <c r="F90" s="2">
-        <v>73432</v>
+        <v>72432</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>11343</v>
+        <v>11253</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>97392</v>
+        <v>97232</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>3350</v>
+        <v>3270</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2100,7 +2100,7 @@
         <v>80</v>
       </c>
       <c r="F4" s="2">
-        <v>7881</v>
+        <v>7879</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -2215,7 +2215,7 @@
         <v>240</v>
       </c>
       <c r="F9" s="4">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>29</v>
@@ -2560,7 +2560,7 @@
         <v>120</v>
       </c>
       <c r="F24" s="4">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>29</v>
@@ -2583,7 +2583,7 @@
         <v>120</v>
       </c>
       <c r="F25" s="4">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>29</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>11253</v>
+        <v>11193</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>97232</v>
+        <v>97072</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2123,7 +2123,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>5435</v>
+        <v>5335</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -4147,7 +4147,7 @@
         <v>2</v>
       </c>
       <c r="F93" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2123,7 +2123,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>5335</v>
+        <v>5185</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2054,7 +2054,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="2">
-        <v>11193</v>
+        <v>10893</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2744,7 +2744,7 @@
         <v>120</v>
       </c>
       <c r="F32" s="2">
-        <v>1042</v>
+        <v>946</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -3457,7 +3457,7 @@
         <v>240</v>
       </c>
       <c r="F63" s="4">
-        <v>907</v>
+        <v>889</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>29</v>
@@ -3779,7 +3779,7 @@
         <v>600</v>
       </c>
       <c r="F77" s="4">
-        <v>509</v>
+        <v>489</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>29</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2790,7 +2790,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="4">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>29</v>
@@ -3687,7 +3687,7 @@
         <v>240</v>
       </c>
       <c r="F73" s="4">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>29</v>
@@ -3939,11 +3939,11 @@
       <c r="E84">
         <v>40</v>
       </c>
-      <c r="F84" s="4">
-        <v>5</v>
-      </c>
-      <c r="G84" s="5" t="s">
-        <v>29</v>
+      <c r="F84" s="2">
+        <v>605</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2123,7 +2123,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>5185</v>
+        <v>5153</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -2077,7 +2077,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="2">
-        <v>97072</v>
+        <v>89072</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -2123,7 +2123,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>5153</v>
+        <v>5185</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -3894,7 +3894,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="2">
-        <v>3270</v>
+        <v>3240</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>

--- a/reports/StockPulse_REPRESENTADAS.xlsx
+++ b/reports/StockPulse_REPRESENTADAS.xlsx
@@ -6217,7 +6217,7 @@
         <v>1</v>
       </c>
       <c r="F183" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>10</v>
@@ -6470,7 +6470,7 @@
         <v>100</v>
       </c>
       <c r="F194" s="2">
-        <v>1181</v>
+        <v>981</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>10</v>
